--- a/storage/news_db.xlsx
+++ b/storage/news_db.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="뉴스DB" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="뉴스DB" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2320"/>
+  <dimension ref="A1:H2381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -72789,8 +72789,6 @@
           <t>https://www.yonhapnewstv.co.kr/news/MYH20260426130746Xls</t>
         </is>
       </c>
-      <c r="G2263" t="inlineStr"/>
-      <c r="H2263" t="inlineStr"/>
     </row>
     <row r="2264">
       <c r="A2264" t="inlineStr">
@@ -72823,8 +72821,6 @@
           <t>https://www.yonhapnewstv.co.kr/news/MYH20260426120325LdF</t>
         </is>
       </c>
-      <c r="G2264" t="inlineStr"/>
-      <c r="H2264" t="inlineStr"/>
     </row>
     <row r="2265">
       <c r="A2265" t="inlineStr">
@@ -72857,8 +72853,6 @@
           <t>https://www.yonhapnewstv.co.kr/news/AKR20260426112713Pxy</t>
         </is>
       </c>
-      <c r="G2265" t="inlineStr"/>
-      <c r="H2265" t="inlineStr"/>
     </row>
     <row r="2266">
       <c r="A2266" t="inlineStr">
@@ -72891,8 +72885,6 @@
           <t>https://www.yonhapnewstv.co.kr/news/MYH20260426130410IWu</t>
         </is>
       </c>
-      <c r="G2266" t="inlineStr"/>
-      <c r="H2266" t="inlineStr"/>
     </row>
     <row r="2267">
       <c r="A2267" t="inlineStr">
@@ -72925,8 +72917,6 @@
           <t>https://www.yonhapnewstv.co.kr/news/MYH20260426130231vwW</t>
         </is>
       </c>
-      <c r="G2267" t="inlineStr"/>
-      <c r="H2267" t="inlineStr"/>
     </row>
     <row r="2268">
       <c r="A2268" t="inlineStr">
@@ -72959,8 +72949,6 @@
           <t>https://www.hani.co.kr/arti/economy/it/1255899.html</t>
         </is>
       </c>
-      <c r="G2268" t="inlineStr"/>
-      <c r="H2268" t="inlineStr"/>
     </row>
     <row r="2269">
       <c r="A2269" t="inlineStr">
@@ -72993,8 +72981,6 @@
           <t>https://www.hani.co.kr/arti/culture/music/1255898.html</t>
         </is>
       </c>
-      <c r="G2269" t="inlineStr"/>
-      <c r="H2269" t="inlineStr"/>
     </row>
     <row r="2270">
       <c r="A2270" t="inlineStr">
@@ -73027,8 +73013,6 @@
           <t>https://www.hani.co.kr/arti/society/society_general/1255897.html</t>
         </is>
       </c>
-      <c r="G2270" t="inlineStr"/>
-      <c r="H2270" t="inlineStr"/>
     </row>
     <row r="2271">
       <c r="A2271" t="inlineStr">
@@ -73061,8 +73045,6 @@
           <t>https://www.hani.co.kr/arti/society/society_general/1255896.html</t>
         </is>
       </c>
-      <c r="G2271" t="inlineStr"/>
-      <c r="H2271" t="inlineStr"/>
     </row>
     <row r="2272">
       <c r="A2272" t="inlineStr">
@@ -73095,8 +73077,6 @@
           <t>https://www.hani.co.kr/arti/area/gangwon/1255895.html</t>
         </is>
       </c>
-      <c r="G2272" t="inlineStr"/>
-      <c r="H2272" t="inlineStr"/>
     </row>
     <row r="2273">
       <c r="A2273" t="inlineStr">
@@ -73129,8 +73109,6 @@
           <t>https://www.hani.co.kr/arti/culture/culture_general/1255894.html</t>
         </is>
       </c>
-      <c r="G2273" t="inlineStr"/>
-      <c r="H2273" t="inlineStr"/>
     </row>
     <row r="2274">
       <c r="A2274" t="inlineStr">
@@ -73163,8 +73141,6 @@
           <t>https://www.hani.co.kr/arti/sports/baseball/1255893.html</t>
         </is>
       </c>
-      <c r="G2274" t="inlineStr"/>
-      <c r="H2274" t="inlineStr"/>
     </row>
     <row r="2275">
       <c r="A2275" t="inlineStr">
@@ -73197,8 +73173,6 @@
           <t>https://www.hani.co.kr/arti/international/international_general/1255892.html</t>
         </is>
       </c>
-      <c r="G2275" t="inlineStr"/>
-      <c r="H2275" t="inlineStr"/>
     </row>
     <row r="2276">
       <c r="A2276" t="inlineStr">
@@ -73231,8 +73205,6 @@
           <t>https://www.hankyung.com/article/202604267047i</t>
         </is>
       </c>
-      <c r="G2276" t="inlineStr"/>
-      <c r="H2276" t="inlineStr"/>
     </row>
     <row r="2277">
       <c r="A2277" t="inlineStr">
@@ -73265,8 +73237,6 @@
           <t>https://www.hankyung.com/article/202604267077g</t>
         </is>
       </c>
-      <c r="G2277" t="inlineStr"/>
-      <c r="H2277" t="inlineStr"/>
     </row>
     <row r="2278">
       <c r="A2278" t="inlineStr">
@@ -73299,8 +73269,6 @@
           <t>https://www.hankyung.com/article/2026042670987</t>
         </is>
       </c>
-      <c r="G2278" t="inlineStr"/>
-      <c r="H2278" t="inlineStr"/>
     </row>
     <row r="2279">
       <c r="A2279" t="inlineStr">
@@ -73333,8 +73301,6 @@
           <t>https://www.hankyung.com/article/202604267037g</t>
         </is>
       </c>
-      <c r="G2279" t="inlineStr"/>
-      <c r="H2279" t="inlineStr"/>
     </row>
     <row r="2280">
       <c r="A2280" t="inlineStr">
@@ -73367,8 +73333,6 @@
           <t>https://www.hankyung.com/article/202604267026i</t>
         </is>
       </c>
-      <c r="G2280" t="inlineStr"/>
-      <c r="H2280" t="inlineStr"/>
     </row>
     <row r="2281">
       <c r="A2281" t="inlineStr">
@@ -73401,8 +73365,6 @@
           <t>https://www.hankyung.com/article/202604266755i</t>
         </is>
       </c>
-      <c r="G2281" t="inlineStr"/>
-      <c r="H2281" t="inlineStr"/>
     </row>
     <row r="2282">
       <c r="A2282" t="inlineStr">
@@ -73435,8 +73397,6 @@
           <t>https://www.hankyung.com/article/202604267000i</t>
         </is>
       </c>
-      <c r="G2282" t="inlineStr"/>
-      <c r="H2282" t="inlineStr"/>
     </row>
     <row r="2283">
       <c r="A2283" t="inlineStr">
@@ -73469,8 +73429,6 @@
           <t>https://www.hankyung.com/article/202604266967i</t>
         </is>
       </c>
-      <c r="G2283" t="inlineStr"/>
-      <c r="H2283" t="inlineStr"/>
     </row>
     <row r="2284">
       <c r="A2284" t="inlineStr">
@@ -73503,8 +73461,6 @@
           <t>https://www.mk.co.kr/news/business/12027475</t>
         </is>
       </c>
-      <c r="G2284" t="inlineStr"/>
-      <c r="H2284" t="inlineStr"/>
     </row>
     <row r="2285">
       <c r="A2285" t="inlineStr">
@@ -73537,8 +73493,6 @@
           <t>https://www.mk.co.kr/news/society/12027473</t>
         </is>
       </c>
-      <c r="G2285" t="inlineStr"/>
-      <c r="H2285" t="inlineStr"/>
     </row>
     <row r="2286">
       <c r="A2286" t="inlineStr">
@@ -73571,8 +73525,6 @@
           <t>https://www.mk.co.kr/news/society/12027472</t>
         </is>
       </c>
-      <c r="G2286" t="inlineStr"/>
-      <c r="H2286" t="inlineStr"/>
     </row>
     <row r="2287">
       <c r="A2287" t="inlineStr">
@@ -73605,8 +73557,6 @@
           <t>https://www.mk.co.kr/news/business/12027470</t>
         </is>
       </c>
-      <c r="G2287" t="inlineStr"/>
-      <c r="H2287" t="inlineStr"/>
     </row>
     <row r="2288">
       <c r="A2288" t="inlineStr">
@@ -73639,8 +73589,6 @@
           <t>https://www.mk.co.kr/news/sports/12027468</t>
         </is>
       </c>
-      <c r="G2288" t="inlineStr"/>
-      <c r="H2288" t="inlineStr"/>
     </row>
     <row r="2289">
       <c r="A2289" t="inlineStr">
@@ -73673,8 +73621,6 @@
           <t>https://www.mk.co.kr/news/culture/12027467</t>
         </is>
       </c>
-      <c r="G2289" t="inlineStr"/>
-      <c r="H2289" t="inlineStr"/>
     </row>
     <row r="2290">
       <c r="A2290" t="inlineStr">
@@ -73707,8 +73653,6 @@
           <t>https://www.mk.co.kr/news/economy/12027466</t>
         </is>
       </c>
-      <c r="G2290" t="inlineStr"/>
-      <c r="H2290" t="inlineStr"/>
     </row>
     <row r="2291">
       <c r="A2291" t="inlineStr">
@@ -73741,8 +73685,6 @@
           <t>https://www.mk.co.kr/news/society/12027465</t>
         </is>
       </c>
-      <c r="G2291" t="inlineStr"/>
-      <c r="H2291" t="inlineStr"/>
     </row>
     <row r="2292">
       <c r="A2292" t="inlineStr">
@@ -73775,8 +73717,6 @@
           <t>https://news.einfomax.co.kr/news/articleView.html?idxno=4411732</t>
         </is>
       </c>
-      <c r="G2292" t="inlineStr"/>
-      <c r="H2292" t="inlineStr"/>
     </row>
     <row r="2293">
       <c r="A2293" t="inlineStr">
@@ -73809,8 +73749,6 @@
           <t>https://news.einfomax.co.kr/news/articleView.html?idxno=4411731</t>
         </is>
       </c>
-      <c r="G2293" t="inlineStr"/>
-      <c r="H2293" t="inlineStr"/>
     </row>
     <row r="2294">
       <c r="A2294" t="inlineStr">
@@ -73843,8 +73781,6 @@
           <t>https://news.einfomax.co.kr/news/articleView.html?idxno=4411730</t>
         </is>
       </c>
-      <c r="G2294" t="inlineStr"/>
-      <c r="H2294" t="inlineStr"/>
     </row>
     <row r="2295">
       <c r="A2295" t="inlineStr">
@@ -73877,8 +73813,6 @@
           <t>https://news.einfomax.co.kr/news/articleView.html?idxno=4411729</t>
         </is>
       </c>
-      <c r="G2295" t="inlineStr"/>
-      <c r="H2295" t="inlineStr"/>
     </row>
     <row r="2296">
       <c r="A2296" t="inlineStr">
@@ -73911,8 +73845,6 @@
           <t>https://news.einfomax.co.kr/news/articleView.html?idxno=4411728</t>
         </is>
       </c>
-      <c r="G2296" t="inlineStr"/>
-      <c r="H2296" t="inlineStr"/>
     </row>
     <row r="2297">
       <c r="A2297" t="inlineStr">
@@ -73945,8 +73877,6 @@
           <t>https://news.einfomax.co.kr/news/articleView.html?idxno=4411727</t>
         </is>
       </c>
-      <c r="G2297" t="inlineStr"/>
-      <c r="H2297" t="inlineStr"/>
     </row>
     <row r="2298">
       <c r="A2298" t="inlineStr">
@@ -73979,8 +73909,6 @@
           <t>https://news.einfomax.co.kr/news/articleView.html?idxno=4411726</t>
         </is>
       </c>
-      <c r="G2298" t="inlineStr"/>
-      <c r="H2298" t="inlineStr"/>
     </row>
     <row r="2299">
       <c r="A2299" t="inlineStr">
@@ -74013,8 +73941,6 @@
           <t>https://news.einfomax.co.kr/news/articleView.html?idxno=4411725</t>
         </is>
       </c>
-      <c r="G2299" t="inlineStr"/>
-      <c r="H2299" t="inlineStr"/>
     </row>
     <row r="2300">
       <c r="A2300" t="inlineStr">
@@ -74047,8 +73973,6 @@
           <t>https://www.etnews.com/20260426000086</t>
         </is>
       </c>
-      <c r="G2300" t="inlineStr"/>
-      <c r="H2300" t="inlineStr"/>
     </row>
     <row r="2301">
       <c r="A2301" t="inlineStr">
@@ -74081,8 +74005,6 @@
           <t>https://www.etnews.com/20260426000038</t>
         </is>
       </c>
-      <c r="G2301" t="inlineStr"/>
-      <c r="H2301" t="inlineStr"/>
     </row>
     <row r="2302">
       <c r="A2302" t="inlineStr">
@@ -74115,8 +74037,6 @@
           <t>https://www.etnews.com/20260424000188</t>
         </is>
       </c>
-      <c r="G2302" t="inlineStr"/>
-      <c r="H2302" t="inlineStr"/>
     </row>
     <row r="2303">
       <c r="A2303" t="inlineStr">
@@ -74149,8 +74069,6 @@
           <t>https://www.etnews.com/20260424000157</t>
         </is>
       </c>
-      <c r="G2303" t="inlineStr"/>
-      <c r="H2303" t="inlineStr"/>
     </row>
     <row r="2304">
       <c r="A2304" t="inlineStr">
@@ -74183,8 +74101,6 @@
           <t>https://www.etnews.com/20260426000078</t>
         </is>
       </c>
-      <c r="G2304" t="inlineStr"/>
-      <c r="H2304" t="inlineStr"/>
     </row>
     <row r="2305">
       <c r="A2305" t="inlineStr">
@@ -74217,8 +74133,6 @@
           <t>https://www.etnews.com/20260426000066</t>
         </is>
       </c>
-      <c r="G2305" t="inlineStr"/>
-      <c r="H2305" t="inlineStr"/>
     </row>
     <row r="2306">
       <c r="A2306" t="inlineStr">
@@ -74251,8 +74165,6 @@
           <t>https://www.etnews.com/20260426000013</t>
         </is>
       </c>
-      <c r="G2306" t="inlineStr"/>
-      <c r="H2306" t="inlineStr"/>
     </row>
     <row r="2307">
       <c r="A2307" t="inlineStr">
@@ -74285,8 +74197,6 @@
           <t>https://www.etnews.com/20260424000214</t>
         </is>
       </c>
-      <c r="G2307" t="inlineStr"/>
-      <c r="H2307" t="inlineStr"/>
     </row>
     <row r="2308">
       <c r="A2308" t="inlineStr">
@@ -74319,8 +74229,6 @@
           <t>https://www.aitimes.com/news/articleView.html?idxno=209749</t>
         </is>
       </c>
-      <c r="G2308" t="inlineStr"/>
-      <c r="H2308" t="inlineStr"/>
     </row>
     <row r="2309">
       <c r="A2309" t="inlineStr">
@@ -74353,8 +74261,6 @@
           <t>https://www.aitimes.com/news/articleView.html?idxno=209746</t>
         </is>
       </c>
-      <c r="G2309" t="inlineStr"/>
-      <c r="H2309" t="inlineStr"/>
     </row>
     <row r="2310">
       <c r="A2310" t="inlineStr">
@@ -74387,8 +74293,6 @@
           <t>https://www.aitimes.com/news/articleView.html?idxno=209747</t>
         </is>
       </c>
-      <c r="G2310" t="inlineStr"/>
-      <c r="H2310" t="inlineStr"/>
     </row>
     <row r="2311">
       <c r="A2311" t="inlineStr">
@@ -74421,8 +74325,6 @@
           <t>https://www.aitimes.com/news/articleView.html?idxno=209750</t>
         </is>
       </c>
-      <c r="G2311" t="inlineStr"/>
-      <c r="H2311" t="inlineStr"/>
     </row>
     <row r="2312">
       <c r="A2312" t="inlineStr">
@@ -74455,8 +74357,6 @@
           <t>https://www.aitimes.com/news/articleView.html?idxno=209745</t>
         </is>
       </c>
-      <c r="G2312" t="inlineStr"/>
-      <c r="H2312" t="inlineStr"/>
     </row>
     <row r="2313">
       <c r="A2313" t="inlineStr">
@@ -74489,8 +74389,6 @@
           <t>https://www.aitimes.com/news/articleView.html?idxno=209707</t>
         </is>
       </c>
-      <c r="G2313" t="inlineStr"/>
-      <c r="H2313" t="inlineStr"/>
     </row>
     <row r="2314">
       <c r="A2314" t="inlineStr">
@@ -74523,8 +74421,6 @@
           <t>https://www.aitimes.com/news/articleView.html?idxno=209744</t>
         </is>
       </c>
-      <c r="G2314" t="inlineStr"/>
-      <c r="H2314" t="inlineStr"/>
     </row>
     <row r="2315">
       <c r="A2315" t="inlineStr">
@@ -74557,8 +74453,6 @@
           <t>https://www.aitimes.com/news/articleView.html?idxno=209505</t>
         </is>
       </c>
-      <c r="G2315" t="inlineStr"/>
-      <c r="H2315" t="inlineStr"/>
     </row>
     <row r="2316">
       <c r="A2316" t="inlineStr">
@@ -74591,8 +74485,6 @@
           <t>https://www.hankyung.com/article/2026042457146</t>
         </is>
       </c>
-      <c r="G2316" t="inlineStr"/>
-      <c r="H2316" t="inlineStr"/>
     </row>
     <row r="2317">
       <c r="A2317" t="inlineStr">
@@ -74625,8 +74517,6 @@
           <t>https://www.hankyung.com/article/202604266929i</t>
         </is>
       </c>
-      <c r="G2317" t="inlineStr"/>
-      <c r="H2317" t="inlineStr"/>
     </row>
     <row r="2318">
       <c r="A2318" t="inlineStr">
@@ -74659,8 +74549,6 @@
           <t>https://www.hankyung.com/article/2026042667957</t>
         </is>
       </c>
-      <c r="G2318" t="inlineStr"/>
-      <c r="H2318" t="inlineStr"/>
     </row>
     <row r="2319">
       <c r="A2319" t="inlineStr">
@@ -74693,8 +74581,6 @@
           <t>https://www.hankyung.com/article/2026042444996</t>
         </is>
       </c>
-      <c r="G2319" t="inlineStr"/>
-      <c r="H2319" t="inlineStr"/>
     </row>
     <row r="2320">
       <c r="A2320" t="inlineStr">
@@ -74727,8 +74613,2436 @@
           <t>https://www.hankyung.com/article/202604256481i</t>
         </is>
       </c>
-      <c r="G2320" t="inlineStr"/>
-      <c r="H2320" t="inlineStr"/>
+    </row>
+    <row r="2321">
+      <c r="A2321" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2321" t="inlineStr">
+        <is>
+          <t>korean_general</t>
+        </is>
+      </c>
+      <c r="C2321" t="inlineStr">
+        <is>
+          <t>국내 종합</t>
+        </is>
+      </c>
+      <c r="D2321" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2321" t="inlineStr">
+        <is>
+          <t>김범석 '쿠팡 총수' 지정…"동생 경영참여 확인"</t>
+        </is>
+      </c>
+      <c r="F2321" t="inlineStr">
+        <is>
+          <t>https://www.yonhapnewstv.co.kr/news/MYH20260429124522Cfz</t>
+        </is>
+      </c>
+      <c r="G2321" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 12:45:46 +0900</t>
+        </is>
+      </c>
+      <c r="H2321" t="inlineStr">
+        <is>
+          <t>[앵커] 공정거래위원회가 김범석 쿠팡Inc(아이앤씨) 의장을 쿠팡의 '총수'로 지정했습니다. 김 의장 동생인 김유석 부사장의 실질적 경영 참여 활동을 확인한 건데요. 쿠팡은 앞으로 여러 공시 의무와 사익편취 규제 등을 적용받게 됩니다. 장한별 기자입니다. [기자] 지난...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2322">
+      <c r="A2322" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2322" t="inlineStr">
+        <is>
+          <t>korean_general</t>
+        </is>
+      </c>
+      <c r="C2322" t="inlineStr">
+        <is>
+          <t>국내 종합</t>
+        </is>
+      </c>
+      <c r="D2322" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2322" t="inlineStr">
+        <is>
+          <t>WSJ "트럼프, 이란 해상봉쇄 장기화 대비 지시"</t>
+        </is>
+      </c>
+      <c r="F2322" t="inlineStr">
+        <is>
+          <t>https://www.yonhapnewstv.co.kr/news/AKR202604291353261Wk</t>
+        </is>
+      </c>
+      <c r="G2322" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 13:53:27 +0900</t>
+        </is>
+      </c>
+      <c r="H2322" t="inlineStr">
+        <is>
+          <t>도널드 트럼프 미국 대통령[로이터=연합뉴스 제공][로이터=연합뉴스 제공] 도널드 트럼프 미국 대통령이 이란의 핵 포기를 받아내기 위해 이란에 대한 장기적인 해상 봉쇄를 준비하라고 보좌진에게 지시했다고 미국 월스트리트저널(WSJ)이 현지 시각 28일 보도했습니다. WSJ...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2323">
+      <c r="A2323" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2323" t="inlineStr">
+        <is>
+          <t>korean_general</t>
+        </is>
+      </c>
+      <c r="C2323" t="inlineStr">
+        <is>
+          <t>국내 종합</t>
+        </is>
+      </c>
+      <c r="D2323" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2323" t="inlineStr">
+        <is>
+          <t>민주, 靑 하정우 인재영입…국힘 장동혁 체제 균열</t>
+        </is>
+      </c>
+      <c r="F2323" t="inlineStr">
+        <is>
+          <t>https://www.yonhapnewstv.co.kr/news/MYH20260429120255UuE</t>
+        </is>
+      </c>
+      <c r="G2323" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 12:03:37 +0900</t>
+        </is>
+      </c>
+      <c r="H2323" t="inlineStr">
+        <is>
+          <t>[앵커] 6·3 지방선거 광역단체장 후보로 선출된 현역 의원들이 오늘 의원직을 일괄 사퇴합니다. 국회의원 재보선 선거전도 본격화할 전망인데요. 민주당 소식부터 전해주시죠. 양소리 기자. [기자] 네, 국회입니다. 지방선거 광역단체장 후보로 선출된 현역 국회의원들, 오늘...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2324">
+      <c r="A2324" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2324" t="inlineStr">
+        <is>
+          <t>korean_general</t>
+        </is>
+      </c>
+      <c r="C2324" t="inlineStr">
+        <is>
+          <t>국내 종합</t>
+        </is>
+      </c>
+      <c r="D2324" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2324" t="inlineStr">
+        <is>
+          <t>민주 국조특위 위원들 "검찰 자정능력 한계…이제 특검 필요"</t>
+        </is>
+      </c>
+      <c r="F2324" t="inlineStr">
+        <is>
+          <t>https://www.yonhapnewstv.co.kr/news/AKR20260429133227fbL</t>
+        </is>
+      </c>
+      <c r="G2324" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 13:32:28 +0900</t>
+        </is>
+      </c>
+      <c r="H2324" t="inlineStr">
+        <is>
+          <t>조작기소 국조특위 성과 밝히는 서영교 위원장[연합뉴스 자료제공][연합뉴스 자료제공] 윤석열 정치검찰 조작기소 국정조사 특별위원회가 종합 청문회를 끝으로 활동을 마무리지은 가운데, 더불어민주당은 "검찰과 감사원 등의 자정 능력이 한계에 달했음이 드러났다"며 특검 공세를 ...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2325">
+      <c r="A2325" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2325" t="inlineStr">
+        <is>
+          <t>korean_general</t>
+        </is>
+      </c>
+      <c r="C2325" t="inlineStr">
+        <is>
+          <t>국내 종합</t>
+        </is>
+      </c>
+      <c r="D2325" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2325" t="inlineStr">
+        <is>
+          <t>UAE, OPEC 탈퇴…미국에 밀착 시도?</t>
+        </is>
+      </c>
+      <c r="F2325" t="inlineStr">
+        <is>
+          <t>https://www.yonhapnewstv.co.kr/news/MYH20260429133604Bz4</t>
+        </is>
+      </c>
+      <c r="G2325" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 13:36:38 +0900</t>
+        </is>
+      </c>
+      <c r="H2325" t="inlineStr">
+        <is>
+          <t>[앵커] 아랍에미리트 UAE가 석유수출국기구 OPEC을 탈퇴하기로 했습니다. 파키스탄 현지에 나가 있는 특파원 연결해 자세한 내용 알아보겠습니다. 문형민 특파원. (네, 파키스탄 이슬라마바드입니다.) UAE의 이번 결정으로 사우디아라비아 주도의 '오일 카르텔'이 타격을...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2326">
+      <c r="A2326" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2326" t="inlineStr">
+        <is>
+          <t>korean_general</t>
+        </is>
+      </c>
+      <c r="C2326" t="inlineStr">
+        <is>
+          <t>국내 종합</t>
+        </is>
+      </c>
+      <c r="D2326" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2326" t="inlineStr">
+        <is>
+          <t>국힘 최고위원, ‘장동혁 비판’ 배현진에 “암적 존재”</t>
+        </is>
+      </c>
+      <c r="F2326" t="inlineStr">
+        <is>
+          <t>https://www.hani.co.kr/arti/politics/politics_general/1256430.html</t>
+        </is>
+      </c>
+      <c r="G2326" t="inlineStr"/>
+      <c r="H2326" t="inlineStr"/>
+    </row>
+    <row r="2327">
+      <c r="A2327" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2327" t="inlineStr">
+        <is>
+          <t>korean_general</t>
+        </is>
+      </c>
+      <c r="C2327" t="inlineStr">
+        <is>
+          <t>국내 종합</t>
+        </is>
+      </c>
+      <c r="D2327" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2327" t="inlineStr">
+        <is>
+          <t>서울시 공무원, ‘미성년자 성추행 혐의’로 경찰 수사 받아</t>
+        </is>
+      </c>
+      <c r="F2327" t="inlineStr">
+        <is>
+          <t>https://www.hani.co.kr/arti/society/society_general/1256429.html</t>
+        </is>
+      </c>
+      <c r="G2327" t="inlineStr"/>
+      <c r="H2327" t="inlineStr"/>
+    </row>
+    <row r="2328">
+      <c r="A2328" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2328" t="inlineStr">
+        <is>
+          <t>korean_general</t>
+        </is>
+      </c>
+      <c r="C2328" t="inlineStr">
+        <is>
+          <t>국내 종합</t>
+        </is>
+      </c>
+      <c r="D2328" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2328" t="inlineStr">
+        <is>
+          <t>매출 상위 500곳 CEO, 3명 중 1명 강남3구에 산다</t>
+        </is>
+      </c>
+      <c r="F2328" t="inlineStr">
+        <is>
+          <t>https://www.hani.co.kr/arti/economy/economy_general/1256428.html</t>
+        </is>
+      </c>
+      <c r="G2328" t="inlineStr"/>
+      <c r="H2328" t="inlineStr"/>
+    </row>
+    <row r="2329">
+      <c r="A2329" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2329" t="inlineStr">
+        <is>
+          <t>korean_general</t>
+        </is>
+      </c>
+      <c r="C2329" t="inlineStr">
+        <is>
+          <t>국내 종합</t>
+        </is>
+      </c>
+      <c r="D2329" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2329" t="inlineStr">
+        <is>
+          <t>한국도 미국도 손놓은 ‘탈화석연료’ 논의, 콜롬비아에서 불씨</t>
+        </is>
+      </c>
+      <c r="F2329" t="inlineStr">
+        <is>
+          <t>https://www.hani.co.kr/arti/society/environment/1256427.html</t>
+        </is>
+      </c>
+      <c r="G2329" t="inlineStr"/>
+      <c r="H2329" t="inlineStr"/>
+    </row>
+    <row r="2330">
+      <c r="A2330" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2330" t="inlineStr">
+        <is>
+          <t>korean_general</t>
+        </is>
+      </c>
+      <c r="C2330" t="inlineStr">
+        <is>
+          <t>국내 종합</t>
+        </is>
+      </c>
+      <c r="D2330" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2330" t="inlineStr">
+        <is>
+          <t>‘이례적’ 회사채 잔액 감소…기업들 불확실성에 만기 1년 미만으로 돈 조달</t>
+        </is>
+      </c>
+      <c r="F2330" t="inlineStr">
+        <is>
+          <t>https://www.hani.co.kr/arti/economy/finance/1256426.html</t>
+        </is>
+      </c>
+      <c r="G2330" t="inlineStr"/>
+      <c r="H2330" t="inlineStr"/>
+    </row>
+    <row r="2331">
+      <c r="A2331" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2331" t="inlineStr">
+        <is>
+          <t>korean_general</t>
+        </is>
+      </c>
+      <c r="C2331" t="inlineStr">
+        <is>
+          <t>국내 종합</t>
+        </is>
+      </c>
+      <c r="D2331" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2331" t="inlineStr">
+        <is>
+          <t>유정복 인천시장 3선 도전 공식화…민주당 박찬대와 대결</t>
+        </is>
+      </c>
+      <c r="F2331" t="inlineStr">
+        <is>
+          <t>https://www.hani.co.kr/arti/area/capital/1256425.html</t>
+        </is>
+      </c>
+      <c r="G2331" t="inlineStr"/>
+      <c r="H2331" t="inlineStr"/>
+    </row>
+    <row r="2332">
+      <c r="A2332" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2332" t="inlineStr">
+        <is>
+          <t>korean_general</t>
+        </is>
+      </c>
+      <c r="C2332" t="inlineStr">
+        <is>
+          <t>국내 종합</t>
+        </is>
+      </c>
+      <c r="D2332" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2332" t="inlineStr">
+        <is>
+          <t>‘필라테스 가맹 사기 의혹’ 양정원, 경찰 출석…남편, 수사무마 의혹도</t>
+        </is>
+      </c>
+      <c r="F2332" t="inlineStr">
+        <is>
+          <t>https://www.hani.co.kr/arti/society/society_general/1256424.html</t>
+        </is>
+      </c>
+      <c r="G2332" t="inlineStr"/>
+      <c r="H2332" t="inlineStr"/>
+    </row>
+    <row r="2333">
+      <c r="A2333" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2333" t="inlineStr">
+        <is>
+          <t>korean_general</t>
+        </is>
+      </c>
+      <c r="C2333" t="inlineStr">
+        <is>
+          <t>국내 종합</t>
+        </is>
+      </c>
+      <c r="D2333" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2333" t="inlineStr">
+        <is>
+          <t>‘1억 공천헌금’ 의혹 강선우·김경 첫 재판…김 “혐의 전부 인정”</t>
+        </is>
+      </c>
+      <c r="F2333" t="inlineStr">
+        <is>
+          <t>https://www.hani.co.kr/arti/society/society_general/1256423.html</t>
+        </is>
+      </c>
+      <c r="G2333" t="inlineStr"/>
+      <c r="H2333" t="inlineStr"/>
+    </row>
+    <row r="2334">
+      <c r="A2334" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2334" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2334" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2334" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2334" t="inlineStr">
+        <is>
+          <t>"K-라이프스타일 체험해보세요" 외국인 마케팅 나선 '자주'</t>
+        </is>
+      </c>
+      <c r="F2334" t="inlineStr">
+        <is>
+          <t>https://www.hankyung.com/article/202604295420i</t>
+        </is>
+      </c>
+      <c r="G2334" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 14:08:53 +0900</t>
+        </is>
+      </c>
+      <c r="H2334" t="inlineStr"/>
+    </row>
+    <row r="2335">
+      <c r="A2335" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2335" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2335" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2335" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2335" t="inlineStr">
+        <is>
+          <t>[속보] LG전자 1분기 영업이익 1조6737억원…전년 대비 32.9%↑</t>
+        </is>
+      </c>
+      <c r="F2335" t="inlineStr">
+        <is>
+          <t>https://www.hankyung.com/article/202604295419g</t>
+        </is>
+      </c>
+      <c r="G2335" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 14:04:00 +0900</t>
+        </is>
+      </c>
+      <c r="H2335" t="inlineStr"/>
+    </row>
+    <row r="2336">
+      <c r="A2336" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2336" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2336" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2336" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2336" t="inlineStr">
+        <is>
+          <t>이녹스리튬, LX인터내셔널에 600톤 수산화리튬 판매</t>
+        </is>
+      </c>
+      <c r="F2336" t="inlineStr">
+        <is>
+          <t>https://www.hankyung.com/article/202604295364i</t>
+        </is>
+      </c>
+      <c r="G2336" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 13:55:58 +0900</t>
+        </is>
+      </c>
+      <c r="H2336" t="inlineStr"/>
+    </row>
+    <row r="2337">
+      <c r="A2337" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2337" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2337" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2337" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2337" t="inlineStr">
+        <is>
+          <t>방글라데시 임직원 1만2000명에 안경 지원한 이 회사</t>
+        </is>
+      </c>
+      <c r="F2337" t="inlineStr">
+        <is>
+          <t>https://www.hankyung.com/article/202604295331i</t>
+        </is>
+      </c>
+      <c r="G2337" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 13:44:22 +0900</t>
+        </is>
+      </c>
+      <c r="H2337" t="inlineStr"/>
+    </row>
+    <row r="2338">
+      <c r="A2338" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2338" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2338" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2338" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2338" t="inlineStr">
+        <is>
+          <t>공정위, 쿠팡 동일인 김범석으로 변경…쿠팡 "이중 규제" 반발</t>
+        </is>
+      </c>
+      <c r="F2338" t="inlineStr">
+        <is>
+          <t>https://www.hankyung.com/article/202604295195g</t>
+        </is>
+      </c>
+      <c r="G2338" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 13:34:40 +0900</t>
+        </is>
+      </c>
+      <c r="H2338" t="inlineStr"/>
+    </row>
+    <row r="2339">
+      <c r="A2339" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2339" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2339" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2339" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2339" t="inlineStr">
+        <is>
+          <t>"240만원짜리 아이패드가 83만원에?"…쿠팡 오류에 '주문 대란'</t>
+        </is>
+      </c>
+      <c r="F2339" t="inlineStr">
+        <is>
+          <t>https://www.hankyung.com/article/2026042952007</t>
+        </is>
+      </c>
+      <c r="G2339" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 12:26:55 +0900</t>
+        </is>
+      </c>
+      <c r="H2339" t="inlineStr"/>
+    </row>
+    <row r="2340">
+      <c r="A2340" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2340" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2340" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2340" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2340" t="inlineStr">
+        <is>
+          <t>4월 28일 외신 에스프레소 영상</t>
+        </is>
+      </c>
+      <c r="F2340" t="inlineStr">
+        <is>
+          <t>https://www.hankyung.com/article/202604295199i</t>
+        </is>
+      </c>
+      <c r="G2340" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 12:23:25 +0900</t>
+        </is>
+      </c>
+      <c r="H2340" t="inlineStr"/>
+    </row>
+    <row r="2341">
+      <c r="A2341" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2341" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2341" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2341" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2341" t="inlineStr">
+        <is>
+          <t>공정위 "쿠팡 총수는 김범석"…5년 만에 동일인 변경</t>
+        </is>
+      </c>
+      <c r="F2341" t="inlineStr">
+        <is>
+          <t>https://www.hankyung.com/article/2026042951917</t>
+        </is>
+      </c>
+      <c r="G2341" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 12:21:15 +0900</t>
+        </is>
+      </c>
+      <c r="H2341" t="inlineStr"/>
+    </row>
+    <row r="2342">
+      <c r="A2342" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2342" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2342" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2342" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2342" t="inlineStr">
+        <is>
+          <t>동그라미재단 ‘AI 아카데미 3기 성료’ 실무 인재 131명 배출</t>
+        </is>
+      </c>
+      <c r="F2342" t="inlineStr">
+        <is>
+          <t>https://www.mk.co.kr/news/business/12030730</t>
+        </is>
+      </c>
+      <c r="G2342" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 14:20:00 +09:00</t>
+        </is>
+      </c>
+      <c r="H2342" t="inlineStr">
+        <is>
+          <t>비영리 공익법인 동그라미재단(이사장 장순흥)은 지난 28일 서울 종로구 동그라미재단 오픈챌린지랩에서 ‘동그라미재단 AI Academy 3기’ 수료식을 성공적으로 개최하고, 총 13..</t>
+        </is>
+      </c>
+    </row>
+    <row r="2343">
+      <c r="A2343" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2343" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2343" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2343" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2343" t="inlineStr">
+        <is>
+          <t>SBVA, 홍콩 입법회 ICT 기술 의원단과 글로벌 AI 투자 트렌드 간담회 열어</t>
+        </is>
+      </c>
+      <c r="F2343" t="inlineStr">
+        <is>
+          <t>https://www.mk.co.kr/news/it/12030756</t>
+        </is>
+      </c>
+      <c r="G2343" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 14:17:05 +09:00</t>
+        </is>
+      </c>
+      <c r="H2343" t="inlineStr">
+        <is>
+          <t>에이전틱·피지컬AI 부상 등 한·중·홍콩 AI 생태계 현황 공유SBVA가 27일 서울 서초구 SBVA 사무실에서 홍콩 입법회 ICT 위원장 던컨 치우 의원, 엘리자베스 쿼트 의원 ..</t>
+        </is>
+      </c>
+    </row>
+    <row r="2344">
+      <c r="A2344" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2344" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2344" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2344" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2344" t="inlineStr">
+        <is>
+          <t>인재유출 걱정에 파업 한다는데…삼성전자 노조가 고민해야 할 2가지 [기자24시]</t>
+        </is>
+      </c>
+      <c r="F2344" t="inlineStr">
+        <is>
+          <t>https://www.mk.co.kr/news/business/12030755</t>
+        </is>
+      </c>
+      <c r="G2344" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 14:16:03 +09:00</t>
+        </is>
+      </c>
+      <c r="H2344" t="inlineStr">
+        <is>
+          <t>우수 인재확보가 목표라면 5년 내 퇴사자는 지급 줄여야 적자 사업부와 함께 가려면 메모리 사업부 직원 양보 필요삼성전자 노조의 파업 예고 시점이 다가오고 있다. 지난 23일 평택캠..</t>
+        </is>
+      </c>
+    </row>
+    <row r="2345">
+      <c r="A2345" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2345" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2345" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2345" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2345" t="inlineStr">
+        <is>
+          <t>[속보] LG전자 1분기 영업이익 1조6737억원…젼년대비 32.9%↑</t>
+        </is>
+      </c>
+      <c r="F2345" t="inlineStr">
+        <is>
+          <t>https://www.mk.co.kr/news/business/12030754</t>
+        </is>
+      </c>
+      <c r="G2345" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 14:15:21 +09:00</t>
+        </is>
+      </c>
+      <c r="H2345" t="inlineStr">
+        <is>
+          <t>LG전자가 경기 불확실성 속에서도 역대 1분기 최대 매출을 기록하며 ‘실적 어닝 서프라이즈’를 달성했다. 주력 사업인 생활가전의 견고한 리더십에 더해 미래 먹거리인 전장 사업과 구..</t>
+        </is>
+      </c>
+    </row>
+    <row r="2346">
+      <c r="A2346" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2346" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2346" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2346" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2346" t="inlineStr">
+        <is>
+          <t>[속보] ‘김건희 집사’ 김예성 횡령 혐의 2심도 무죄·공소기각</t>
+        </is>
+      </c>
+      <c r="F2346" t="inlineStr">
+        <is>
+          <t>https://www.mk.co.kr/news/society/12030753</t>
+        </is>
+      </c>
+      <c r="G2346" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 14:12:59 +09:00</t>
+        </is>
+      </c>
+      <c r="H2346" t="inlineStr"/>
+    </row>
+    <row r="2347">
+      <c r="A2347" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2347" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2347" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2347" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2347" t="inlineStr">
+        <is>
+          <t>[동정]이숙자 서울시의회 운영위원장</t>
+        </is>
+      </c>
+      <c r="F2347" t="inlineStr">
+        <is>
+          <t>https://www.mk.co.kr/news/society/12030752</t>
+        </is>
+      </c>
+      <c r="G2347" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 14:10:28 +09:00</t>
+        </is>
+      </c>
+      <c r="H2347" t="inlineStr">
+        <is>
+          <t>이숙자 서울시의회 운영위원장(국민의힘)이 29일 한국여성단체협의회로부터 ‘대한민국을 이끌 여성지도자상’을 받았다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2348">
+      <c r="A2348" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2348" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2348" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2348" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2348" t="inlineStr">
+        <is>
+          <t>[부고] 김현수 수원시 제1부시장 모친상</t>
+        </is>
+      </c>
+      <c r="F2348" t="inlineStr">
+        <is>
+          <t>https://www.mk.co.kr/news/society/12030748</t>
+        </is>
+      </c>
+      <c r="G2348" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 14:05:44 +09:00</t>
+        </is>
+      </c>
+      <c r="H2348" t="inlineStr">
+        <is>
+          <t>최연승씨(향년 91세) 별세, 김현수 수원시 제1부시장 모친상 = 29일 오전 4시 50분, 수원시 연화장 장례식장 201호(29일 오후 3시부터 조문 가능), 발인 5월 1일, ..</t>
+        </is>
+      </c>
+    </row>
+    <row r="2349">
+      <c r="A2349" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2349" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2349" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2349" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2349" t="inlineStr">
+        <is>
+          <t>법인카드도 해외서 쓰면 혜택 더 준다…현대카드 ‘마이컴퍼니글로벌’ 출시</t>
+        </is>
+      </c>
+      <c r="F2349" t="inlineStr">
+        <is>
+          <t>https://www.mk.co.kr/news/economy/12030741</t>
+        </is>
+      </c>
+      <c r="G2349" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 14:02:45 +09:00</t>
+        </is>
+      </c>
+      <c r="H2349" t="inlineStr">
+        <is>
+          <t>해외 결제시 수수료 전면 면제 소기업은 최대 2% 리워드 혜택현대카드가 해외 결제시 더 혜택을 주는 법인카드 마이컴퍼니글로벌‘을 공개했다고 29일 밝혔다. ‘마이컴퍼니글로벌’은 법..</t>
+        </is>
+      </c>
+    </row>
+    <row r="2350">
+      <c r="A2350" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2350" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2350" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2350" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2350" t="inlineStr">
+        <is>
+          <t>박홍근, 재정정책자문회의 간담회…&amp;quot;상시 소통체계 구축&amp;quot;</t>
+        </is>
+      </c>
+      <c r="F2350" t="inlineStr">
+        <is>
+          <t>https://news.einfomax.co.kr/news/articleView.html?idxno=4412377</t>
+        </is>
+      </c>
+      <c r="G2350" t="inlineStr">
+        <is>
+          <t>2026-04-29 14:18:27</t>
+        </is>
+      </c>
+      <c r="H2350" t="inlineStr">
+        <is>
+          <t>박홍근 기획예산처 장관은 29일 "재정정책자문회의도 정례회의 중심에서 벗어나 상시적인 의사소통 체계를 구축할 계획"이라고 밝혔다.박 장관은 이날 서울 중구 컨퍼런스하우스 달개비에서 재정정책자문회의 민간위원들과 오찬 간담회를 열고 "상시적인 소통이 가능하도록 단체 대화방...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2351">
+      <c r="A2351" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2351" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2351" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2351" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2351" t="inlineStr">
+        <is>
+          <t>장동혁 &amp;quot;외교 천재 李대통령 어디서 뭘 하시나&amp;quot;</t>
+        </is>
+      </c>
+      <c r="F2351" t="inlineStr">
+        <is>
+          <t>https://news.einfomax.co.kr/news/articleView.html?idxno=4412376</t>
+        </is>
+      </c>
+      <c r="G2351" t="inlineStr">
+        <is>
+          <t>2026-04-29 14:15:51</t>
+        </is>
+      </c>
+      <c r="H2351" t="inlineStr">
+        <is>
+          <t>국민의힘 장동혁 대표는 일본 유조선 한 척이 이란 당국 허가를 받아 호르무즈 해협을 통과했다는 소식과 관련해 "외교 천재 이재명 대통령은 어디서 뭘 하시나"라고 비꼬았다.장 대표는 29일 페이스북에 관련 기사를 공유하고 "원유를 실은 일본 유조선이 호르무즈 해협을 통과...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2352">
+      <c r="A2352" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2352" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2352" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2352" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2352" t="inlineStr">
+        <is>
+          <t>현대차 로보틱스랩, AVP본부로 이관…로보틱스-AI-자율주행 연계 강화</t>
+        </is>
+      </c>
+      <c r="F2352" t="inlineStr">
+        <is>
+          <t>https://news.einfomax.co.kr/news/articleView.html?idxno=4412375</t>
+        </is>
+      </c>
+      <c r="G2352" t="inlineStr">
+        <is>
+          <t>2026-04-29 14:13:45</t>
+        </is>
+      </c>
+      <c r="H2352" t="inlineStr">
+        <is>
+          <t>현대자동차[005380]그룹이 산하 로봇 전문 연구소 '로보틱스랩'을 첨단차플랫폼(AVP) 본부로 이관하기로 결정했다. 로보틱스 기술과 인공지능(AI), 자율주행의 연계를 강화하기 위해서다.29일 업계에 따르면 현대차는 로보틱스랩을 기존 R&amp;amp;D 본부에서 AVP ...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2353">
+      <c r="A2353" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2353" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2353" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2353" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2353" t="inlineStr">
+        <is>
+          <t>'재정상태 팍팍하다' 미국인 비중 25년내 최고…중간선거 부담</t>
+        </is>
+      </c>
+      <c r="F2353" t="inlineStr">
+        <is>
+          <t>https://news.einfomax.co.kr/news/articleView.html?idxno=4412374</t>
+        </is>
+      </c>
+      <c r="G2353" t="inlineStr">
+        <is>
+          <t>2026-04-29 14:11:55</t>
+        </is>
+      </c>
+      <c r="H2353" t="inlineStr">
+        <is>
+          <t>중동사태 장기화 중 진행된 설문에서 재정 상태가 악화했다고 답한 미국인들이 사상 최고치를 나타냈다.29일 악시오스에 따르면 갤럽은 자신의 재정 상태가 점점 나빠지고 있다고 말한 미국인 비중이 55%로 지난 25년내 최고치로 올랐다는 설문 결과를 발표했다. 이 수치는 작...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2354">
+      <c r="A2354" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2354" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2354" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2354" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2354" t="inlineStr">
+        <is>
+          <t>1분기 실적 거꾸로 돌린 현대건설…자산재평가 시점도 '의문'</t>
+        </is>
+      </c>
+      <c r="F2354" t="inlineStr">
+        <is>
+          <t>https://news.einfomax.co.kr/news/articleView.html?idxno=4412373</t>
+        </is>
+      </c>
+      <c r="G2354" t="inlineStr">
+        <is>
+          <t>2026-04-29 14:11:07</t>
+        </is>
+      </c>
+      <c r="H2354" t="inlineStr">
+        <is>
+          <t>현대건설[000720]이 올해 1분기 주가와는 어울리지 않는 실적을 신고했다. 매출과 영업이익, 수주액 모두 이전보다 줄어들면서 이익 창출력은 이전보다 오히려 약해졌다.다락같이 오른 주가를 실적으로 뒷받침한 다른 건설사와는 대조적인 모습이다. 실질적인 수주 성과 가시화...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2355">
+      <c r="A2355" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2355" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2355" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2355" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2355" t="inlineStr">
+        <is>
+          <t>DL이앤씨 보유 SMR 개발사 엑스에너지 지분 가치 6배↑</t>
+        </is>
+      </c>
+      <c r="F2355" t="inlineStr">
+        <is>
+          <t>https://news.einfomax.co.kr/news/articleView.html?idxno=4412372</t>
+        </is>
+      </c>
+      <c r="G2355" t="inlineStr">
+        <is>
+          <t>2026-04-29 14:09:02</t>
+        </is>
+      </c>
+      <c r="H2355" t="inlineStr">
+        <is>
+          <t>DL이앤씨[375500]의 미국 소형모듈원자로(SMR) 선도 기업 엑스에너지(X-Energy) 투자가 커다란 결실로 돌아오고 있다.DL이앤씨는 엑스에너지가 지난 24일 미국 나스닥에 성공적으로 상장하며 보유 지분 가치가 증가했다고 29일 밝혔다.지난 28일(현지 시각)...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2356">
+      <c r="A2356" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2356" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2356" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2356" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2356" t="inlineStr">
+        <is>
+          <t>[금융가 사람들] &amp;quot;코스피 7천500P 갈 겁니다&amp;quot; 비웃음 샀던 그때 그 보고서</t>
+        </is>
+      </c>
+      <c r="F2356" t="inlineStr">
+        <is>
+          <t>https://news.einfomax.co.kr/news/articleView.html?idxno=4412371</t>
+        </is>
+      </c>
+      <c r="G2356" t="inlineStr">
+        <is>
+          <t>2026-04-29 14:04:03</t>
+        </is>
+      </c>
+      <c r="H2356" t="inlineStr">
+        <is>
+          <t>"이러다 진짜 7천피 가겠는데…"꿈의 지수라는 '코스피 7천피'. 이제는 힘차게 손 뻗으면 닿을 거리다.하지만 불과 6개월 전만 해도 요원한 숫자였다. 코스피 앞자리가 3과 4 사이를 오갈 때였다. 이때 '7'자를 처음 입에 올렸다가 주위의 따가운 시선을 한 몸에 받았...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2357">
+      <c r="A2357" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2357" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2357" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2357" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2357" t="inlineStr">
+        <is>
+          <t>1분기 외환거래 일평균 1천26억弗…'환헤지' 수요에 통계 개편 이후 최대</t>
+        </is>
+      </c>
+      <c r="F2357" t="inlineStr">
+        <is>
+          <t>https://news.einfomax.co.kr/news/articleView.html?idxno=4412370</t>
+        </is>
+      </c>
+      <c r="G2357" t="inlineStr">
+        <is>
+          <t>2026-04-29 14:00:26</t>
+        </is>
+      </c>
+      <c r="H2357" t="inlineStr">
+        <is>
+          <t>지난 1분기 외국환은행의 일평균 외환거래 규모가 5개 분기 연속 증가 흐름을 이어가며 통계 개편 이후 최대치를 기록했다.29일 한국은행에 따르면 2026년 1분기 현물환과 외환파생상품을 포함한 일평균 외환거래 규모는 1천26억5천만달러로 집계됐다.거래량은 일평균 매입 ...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2358">
+      <c r="A2358" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2358" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2358" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2358" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2358" t="inlineStr">
+        <is>
+          <t>NFL 구영회 실축이 사람 살렸다?…헛발질에 웃다가 발작 '뇌종양' 발견한 남성</t>
+        </is>
+      </c>
+      <c r="F2358" t="inlineStr">
+        <is>
+          <t>https://www.etnews.com/20260429000239</t>
+        </is>
+      </c>
+      <c r="G2358" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 13:55:00 +0900</t>
+        </is>
+      </c>
+      <c r="H2358" t="inlineStr">
+        <is>
+          <t>미국프로풋볼(NFL) 한국계 키커 구영회(31)의 실축이 우연히 한 남성의 목숨을 구한 사연이 전해졌다. 28일(현지시간) AP 통신 등에 따르면 미국 켄터키주 렉싱턴에 거주하는 남성 마크 투세이커(59)는 지난해 침대에 누워 아내와 함께 뉴욕 자이언츠와 뉴잉글랜드 패</t>
+        </is>
+      </c>
+    </row>
+    <row r="2359">
+      <c r="A2359" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2359" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2359" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2359" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2359" t="inlineStr">
+        <is>
+          <t>Qi2 무선충전 자석 내장?… 갤럭시 S27, 후면 카메라 디자인 확 바뀐다</t>
+        </is>
+      </c>
+      <c r="F2359" t="inlineStr">
+        <is>
+          <t>https://www.etnews.com/20260429000265</t>
+        </is>
+      </c>
+      <c r="G2359" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 13:45:00 +0900</t>
+        </is>
+      </c>
+      <c r="H2359" t="inlineStr">
+        <is>
+          <t>삼성전자의 차기 프리미엄 스마트폰 '갤럭시 S27'의 후면 카메라 외형이 달라질 수 있다는 관측이 나왔다. 27일(현지시간) IT매체 폰아레나는 IT팁스터 란즈크를 인용해 다음 세대 갤럭시 제품에서 후면 카메라 디자인이 조정될 가능성이 있다고 전했다. 그는 삼성전자가</t>
+        </is>
+      </c>
+    </row>
+    <row r="2360">
+      <c r="A2360" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2360" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2360" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2360" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2360" t="inlineStr">
+        <is>
+          <t>하정우·전은수, 파란 점퍼 입었다…부산 북갑·충남 아산을 출마 유력</t>
+        </is>
+      </c>
+      <c r="F2360" t="inlineStr">
+        <is>
+          <t>https://www.etnews.com/20260429000262</t>
+        </is>
+      </c>
+      <c r="G2360" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 13:39:44 +0900</t>
+        </is>
+      </c>
+      <c r="H2360" t="inlineStr">
+        <is>
+          <t>더불어민주당이 6·3 지방선거와 함께 치러질 국회의원 재·보궐선거를 앞두고 하정우 전 청와대 AI미래기획수석과 전은수 전 청와대 대변인을 영입·발탁했다. 정청래 민주당 대표는 29일 국회에서 열린 2차 인재영입식에서 하 전 수석을 '영입 인재', 전 전 대변인을 '발탁</t>
+        </is>
+      </c>
+    </row>
+    <row r="2361">
+      <c r="A2361" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2361" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2361" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2361" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2361" t="inlineStr">
+        <is>
+          <t>'김범석 쿠팡 동일인 지정'…공정위, 친족경영 실질적 영향 판단</t>
+        </is>
+      </c>
+      <c r="F2361" t="inlineStr">
+        <is>
+          <t>https://www.etnews.com/20260429000212</t>
+        </is>
+      </c>
+      <c r="G2361" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 12:52:27 +0900</t>
+        </is>
+      </c>
+      <c r="H2361" t="inlineStr">
+        <is>
+          <t>공정거래위원회가 쿠팡 기업집단 동일인을 김범석 의장으로 지정했다. 2024년 시행령 개정으로 도입된 법인 동일인 인정 예외 제도가 적용된 첫 사례다. 29일 공정위는 2026년도 공시대상기업집단 102개 지정하면서 쿠팡 동일인을 김범석으로 변경했다고 밝혔다. 그간 쿠팡</t>
+        </is>
+      </c>
+    </row>
+    <row r="2362">
+      <c r="A2362" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2362" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2362" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2362" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2362" t="inlineStr">
+        <is>
+          <t>전기차 충전요금 “완속은 낮추고 초급속은 올리고”…구간별 가격 차별화</t>
+        </is>
+      </c>
+      <c r="F2362" t="inlineStr">
+        <is>
+          <t>https://www.etnews.com/20260429000208</t>
+        </is>
+      </c>
+      <c r="G2362" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 12:18:45 +0900</t>
+        </is>
+      </c>
+      <c r="H2362" t="inlineStr">
+        <is>
+          <t>전기차 공공 충전요금이 완속 구간은 낮아지고 초급속 구간은 높아지는 방향으로 재편된다. 일상적으로 사용하는 저출력 충전은 부담을 줄이고, 빠른 충전은 비용을 반영하는 구조로 바뀌면서 충전 방식에 따른 가격 차이가 분명해졌다. 기후에너지환경부는 전기자동차 공공 충전시설의</t>
+        </is>
+      </c>
+    </row>
+    <row r="2363">
+      <c r="A2363" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2363" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2363" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2363" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2363" t="inlineStr">
+        <is>
+          <t>[르포]신조로지텍, '초중량 특수물류'로 글로벌 시장 정조준…ITER 수행 경험 바탕 '제2도약'</t>
+        </is>
+      </c>
+      <c r="F2363" t="inlineStr">
+        <is>
+          <t>https://www.etnews.com/20260429000100</t>
+        </is>
+      </c>
+      <c r="G2363" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 12:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="H2363" t="inlineStr">
+        <is>
+          <t>특수물류 기업 '신조로지텍'이 초중량·플랜트 화물 운송 역량을 앞세워 글로벌 시장 공략에 속도를 내고 있다. 국제 핵융합 프로젝트 수행 경험과 디지털 물류 기술을 기반으로 '정밀 엔지니어링 물류' 기업으로의 도약을 본격화한다는 구상이다. 권순욱 신조로지텍 대표는 최근</t>
+        </is>
+      </c>
+    </row>
+    <row r="2364">
+      <c r="A2364" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2364" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2364" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2364" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2364" t="inlineStr">
+        <is>
+          <t>모태펀드 1.8조 벤처펀드 선정…AI·딥테크 유니콘 육성 본격화</t>
+        </is>
+      </c>
+      <c r="F2364" t="inlineStr">
+        <is>
+          <t>https://www.etnews.com/20260429000083</t>
+        </is>
+      </c>
+      <c r="G2364" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 12:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="H2364" t="inlineStr">
+        <is>
+          <t>중소벤처기업부가 1.8조원 규모의 모태펀드 벤처펀드 선정을 완료하고, AI·딥테크 중심 투자 확대와 지역·초기 투자 활성화를 통해 벤처투자 회복세를 이어간다. 중소벤처기업부는 29일 '2026년 모태펀드 1차 정시 출자' 사업을 통해 총 60개, 1조7548억원 규모의</t>
+        </is>
+      </c>
+    </row>
+    <row r="2365">
+      <c r="A2365" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2365" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2365" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2365" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2365" t="inlineStr">
+        <is>
+          <t>지선 앞 '한국판 IRA' 꺼낸 국힘…“성과 기업에 10년 직접 보상”</t>
+        </is>
+      </c>
+      <c r="F2365" t="inlineStr">
+        <is>
+          <t>https://www.etnews.com/20260429000185</t>
+        </is>
+      </c>
+      <c r="G2365" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 11:47:05 +0900</t>
+        </is>
+      </c>
+      <c r="H2365" t="inlineStr">
+        <is>
+          <t>국민의힘이 6·3 지방선거를 앞두고 지역경제·민생 공약으로 한국판 '국내생산 촉진 세제(IRA)' 도입과 가칭 '중소기업 승계 지원 법제화'를 핵심으로 내세웠다. 단기 세제 지원을 넘어 성과 기반 장기 인센티브 체계를 구축해 제조업 공동화를 막고 일자리를 창출하겠다는</t>
+        </is>
+      </c>
+    </row>
+    <row r="2366">
+      <c r="A2366" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2366" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2366" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2366" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2366" t="inlineStr">
+        <is>
+          <t>에임인텔리전스 "미소스는 현실...'패치' 넘어 보안 체질 바꿔야"</t>
+        </is>
+      </c>
+      <c r="F2366" t="inlineStr">
+        <is>
+          <t>https://www.aitimes.com/news/articleView.html?idxno=209752</t>
+        </is>
+      </c>
+      <c r="G2366" t="inlineStr">
+        <is>
+          <t>2026-04-29 13:21:34</t>
+        </is>
+      </c>
+      <c r="H2366" t="inlineStr">
+        <is>
+          <t>지난 27년간 인간이 발견하지 못했던 보안 취약점까지 찾아냈다는 앤트로픽의 ‘미소스’가 보안 생태계를 뒤흔들고 있다. 이를 두고 ‘AI 시대 오펜하이머’라는 수식어까지 붙였다.기존 해킹에도 AI가 활용됐으나, 미소스가 촉발한 이번 사태는 차원이 다르다는 평가다.AI 보...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2367">
+      <c r="A2367" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2367" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2367" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2367" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2367" t="inlineStr">
+        <is>
+          <t>“스쳐가는 방문에서 머무는 섬으로”... 여수, 체류형 관광 콘텐츠 확대</t>
+        </is>
+      </c>
+      <c r="F2367" t="inlineStr">
+        <is>
+          <t>https://www.aitimes.com/news/articleView.html?idxno=209898</t>
+        </is>
+      </c>
+      <c r="G2367" t="inlineStr">
+        <is>
+          <t>2026-04-29 13:12:58</t>
+        </is>
+      </c>
+      <c r="H2367" t="inlineStr">
+        <is>
+          <t>여수시가 2026여수세계섬박람회를 계기로 섬과 바다, 도시를 잇는 복합해양관광도시 전환에 속도를 내고 있다고 29일 밝혔다.여수는 365개 섬이 가진 자연환경과 문화자원을 기반으로 체험형·체류형 콘텐츠를 확대하고, 관광객이 도시에서 섬으로 이동해 머무는 동선을 강화할 ...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2368">
+      <c r="A2368" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2368" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2368" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2368" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2368" t="inlineStr">
+        <is>
+          <t>엘리스그룹, 마키나락스와 국방 AI 인프라 확산 MOU</t>
+        </is>
+      </c>
+      <c r="F2368" t="inlineStr">
+        <is>
+          <t>https://www.aitimes.com/news/articleView.html?idxno=209900</t>
+        </is>
+      </c>
+      <c r="G2368" t="inlineStr">
+        <is>
+          <t>2026-04-29 13:12:34</t>
+        </is>
+      </c>
+      <c r="H2368" t="inlineStr">
+        <is>
+          <t>엘리스그룹(대표 김재원)은 마키나락스와 국방 및 산업 분야 AX를 위한 업무협약(MOU)을 체결했다고 29일 밝혔다.엘리스그룹의 클라우드 소프트웨어 'ECI'와 AI 모듈형 데이터센터 'AI PMDC', 마키나락스의 AI 운영체제(OS) '런웨이'를 결합해 국방 현장에...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2369">
+      <c r="A2369" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2369" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2369" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2369" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2369" t="inlineStr">
+        <is>
+          <t>삼성전자, 안경 없는 3D 디스플레이 ‘스페이셜 사이니지’ 출시</t>
+        </is>
+      </c>
+      <c r="F2369" t="inlineStr">
+        <is>
+          <t>https://www.aitimes.com/news/articleView.html?idxno=209892</t>
+        </is>
+      </c>
+      <c r="G2369" t="inlineStr">
+        <is>
+          <t>2026-04-29 12:57:54</t>
+        </is>
+      </c>
+      <c r="H2369" t="inlineStr">
+        <is>
+          <t>삼성전자는 무안경 3D 디스플레이 '스페이셜 사이니지(SMHX)' 32형 신제품을 출시했다고 28일 밝혔다.삼성 스페이셜 사이니지는 독자 기술인 '3D 플레이트'를 적용해 별도의 안경 없이도 화면 속에 또 하나의 공간이 펼쳐지는 듯한 입체감을 구현하는 것이 특징이다. ...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2370">
+      <c r="A2370" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2370" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2370" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2370" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2370" t="inlineStr">
+        <is>
+          <t>"AI 1인 창업가를 잡아라"...국내 액셀러레이터 선점 경쟁 치열</t>
+        </is>
+      </c>
+      <c r="F2370" t="inlineStr">
+        <is>
+          <t>https://www.aitimes.com/news/articleView.html?idxno=209864</t>
+        </is>
+      </c>
+      <c r="G2370" t="inlineStr">
+        <is>
+          <t>2026-04-29 12:56:56</t>
+        </is>
+      </c>
+      <c r="H2370" t="inlineStr">
+        <is>
+          <t>'바이브 코딩'의 확산으로 AI 에이전트가 기획부터 개발, 마케팅, CS까지 담당하면서 AI를 팀원처럼 활용하는 'AI 네이티브' 1인 창업자를 선점하려는 경쟁이 본격화되고 있다.미국 스타트업 지분관리 플랫폼 '카르타(Carta)'에 따르면 신규 벤처사 중 1인 창업자...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2371">
+      <c r="A2371" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2371" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2371" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2371" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2371" t="inlineStr">
+        <is>
+          <t>순천부읍성 서문안내소, ‘즐거웠던 나의 원도심’ 특별기획전 개최</t>
+        </is>
+      </c>
+      <c r="F2371" t="inlineStr">
+        <is>
+          <t>https://www.aitimes.com/news/articleView.html?idxno=209861</t>
+        </is>
+      </c>
+      <c r="G2371" t="inlineStr">
+        <is>
+          <t>2026-04-29 12:55:52</t>
+        </is>
+      </c>
+      <c r="H2371" t="inlineStr">
+        <is>
+          <t>순천은 순천부읍성 서문안내소 디지털역사관에서 특별기획전 즐거웠던 나의 원도심을 30일부터 6월26일까지 개최한다고 28일 밝혔다.이번 전시는 서문안내소가 디지털역사관으로 재단장한 이후 처음 선보이는 기획전이다.주영효 기자 society@aitimes.comPowered...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2372">
+      <c r="A2372" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2372" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2372" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2372" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2372" t="inlineStr">
+        <is>
+          <t>미국 상업용 부동산 ‘온사이트 태양광 1GW’ 시대 개막</t>
+        </is>
+      </c>
+      <c r="F2372" t="inlineStr">
+        <is>
+          <t>https://www.aitimes.com/news/articleView.html?idxno=209896</t>
+        </is>
+      </c>
+      <c r="G2372" t="inlineStr">
+        <is>
+          <t>2026-04-29 12:40:00</t>
+        </is>
+      </c>
+      <c r="H2372" t="inlineStr">
+        <is>
+          <t>미국 상업용 부동산 업계가 온사이트 태양광 1기가와트(GW) 시대에 들어섰다.솔라파워월드는 28일(현지시간) 블랙베어에너지의 ‘2025 부동산 태양광 리더보드’를 인용, 미국 부동산 업계의 온사이트 태양광 누적 설치량은 1.086기가와트직류(GWdc)에 도달했다고 보도...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2373">
+      <c r="A2373" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2373" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2373" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2373" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2373" t="inlineStr">
+        <is>
+          <t>중국, 탄소중립 성적표로 지방정부 심사… “목표 못 채우면 인사 불이익”</t>
+        </is>
+      </c>
+      <c r="F2373" t="inlineStr">
+        <is>
+          <t>https://www.aitimes.com/news/articleView.html?idxno=209897</t>
+        </is>
+      </c>
+      <c r="G2373" t="inlineStr">
+        <is>
+          <t>2026-04-29 12:20:00</t>
+        </is>
+      </c>
+      <c r="H2373" t="inlineStr">
+        <is>
+          <t>중국이 탄소중립 목표 이행을 지방정부 평가와 직접 연결하는 새 책임 체계를 도입했다.PV 매거진은 28일(현지시간) 중국이 탄소정점과 탄소중립 목표의 진척도를 평가하는 국가 차원의 새 기준을 마련했다고 보도했다.재생에너지 확대와 화석연료 감축을 정책 구호에 머물게 하지...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2374">
+      <c r="A2374" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2374" t="inlineStr">
+        <is>
+          <t>korean_stock</t>
+        </is>
+      </c>
+      <c r="C2374" t="inlineStr">
+        <is>
+          <t>국내 증권·투자</t>
+        </is>
+      </c>
+      <c r="D2374" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2374" t="inlineStr">
+        <is>
+          <t>코스피, 오픈AI 우려 딛고 장중 상승 전환…코스닥은 강보합</t>
+        </is>
+      </c>
+      <c r="F2374" t="inlineStr">
+        <is>
+          <t>https://www.hankyung.com/article/2026042952526</t>
+        </is>
+      </c>
+      <c r="G2374" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 13:10:11 +0900</t>
+        </is>
+      </c>
+      <c r="H2374" t="inlineStr"/>
+    </row>
+    <row r="2375">
+      <c r="A2375" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2375" t="inlineStr">
+        <is>
+          <t>korean_stock</t>
+        </is>
+      </c>
+      <c r="C2375" t="inlineStr">
+        <is>
+          <t>국내 증권·투자</t>
+        </is>
+      </c>
+      <c r="D2375" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2375" t="inlineStr">
+        <is>
+          <t>제이알글로벌리츠 '회생신청' 소식에 국내 리츠주 동반 약세</t>
+        </is>
+      </c>
+      <c r="F2375" t="inlineStr">
+        <is>
+          <t>https://www.hankyung.com/article/2026042950276</t>
+        </is>
+      </c>
+      <c r="G2375" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 11:40:24 +0900</t>
+        </is>
+      </c>
+      <c r="H2375" t="inlineStr"/>
+    </row>
+    <row r="2376">
+      <c r="A2376" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2376" t="inlineStr">
+        <is>
+          <t>korean_stock</t>
+        </is>
+      </c>
+      <c r="C2376" t="inlineStr">
+        <is>
+          <t>국내 증권·투자</t>
+        </is>
+      </c>
+      <c r="D2376" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2376" t="inlineStr">
+        <is>
+          <t>방산·증권주 매수하는 상위 1% 고수들…바이오주는 처분</t>
+        </is>
+      </c>
+      <c r="F2376" t="inlineStr">
+        <is>
+          <t>https://www.hankyung.com/article/202604294960i</t>
+        </is>
+      </c>
+      <c r="G2376" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 11:37:25 +0900</t>
+        </is>
+      </c>
+      <c r="H2376" t="inlineStr"/>
+    </row>
+    <row r="2377">
+      <c r="A2377" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2377" t="inlineStr">
+        <is>
+          <t>korean_stock</t>
+        </is>
+      </c>
+      <c r="C2377" t="inlineStr">
+        <is>
+          <t>국내 증권·투자</t>
+        </is>
+      </c>
+      <c r="D2377" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2377" t="inlineStr">
+        <is>
+          <t>[HD건설기계 분석] 또 '어닝 서프'…지정학적 불확실성은 존재</t>
+        </is>
+      </c>
+      <c r="F2377" t="inlineStr">
+        <is>
+          <t>https://www.hankyung.com/article/202604295009i</t>
+        </is>
+      </c>
+      <c r="G2377" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 11:32:04 +0900</t>
+        </is>
+      </c>
+      <c r="H2377" t="inlineStr"/>
+    </row>
+    <row r="2378">
+      <c r="A2378" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2378" t="inlineStr">
+        <is>
+          <t>korean_stock</t>
+        </is>
+      </c>
+      <c r="C2378" t="inlineStr">
+        <is>
+          <t>국내 증권·투자</t>
+        </is>
+      </c>
+      <c r="D2378" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2378" t="inlineStr">
+        <is>
+          <t>[한화시스템 분석] 넘치는 방산 수주 잔액…성장 모멘텀 확대 가능성</t>
+        </is>
+      </c>
+      <c r="F2378" t="inlineStr">
+        <is>
+          <t>https://www.hankyung.com/article/202604294934i</t>
+        </is>
+      </c>
+      <c r="G2378" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 11:16:33 +0900</t>
+        </is>
+      </c>
+      <c r="H2378" t="inlineStr"/>
+    </row>
+    <row r="2379">
+      <c r="A2379" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2379" t="inlineStr">
+        <is>
+          <t>korean_stock</t>
+        </is>
+      </c>
+      <c r="C2379" t="inlineStr">
+        <is>
+          <t>국내 증권·투자</t>
+        </is>
+      </c>
+      <c r="D2379" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2379" t="inlineStr">
+        <is>
+          <t>35억불 굴리는 VC 판테라…"韓 웹3 투자 확대"</t>
+        </is>
+      </c>
+      <c r="F2379" t="inlineStr">
+        <is>
+          <t>https://www.hankyung.com/article/2026042945076</t>
+        </is>
+      </c>
+      <c r="G2379" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 11:04:04 +0900</t>
+        </is>
+      </c>
+      <c r="H2379" t="inlineStr"/>
+    </row>
+    <row r="2380">
+      <c r="A2380" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2380" t="inlineStr">
+        <is>
+          <t>korean_stock</t>
+        </is>
+      </c>
+      <c r="C2380" t="inlineStr">
+        <is>
+          <t>국내 증권·투자</t>
+        </is>
+      </c>
+      <c r="D2380" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2380" t="inlineStr">
+        <is>
+          <t>[에코프로비엠 분석] 수익 개선엔 성공…헝가리 공장 가동 체크해야</t>
+        </is>
+      </c>
+      <c r="F2380" t="inlineStr">
+        <is>
+          <t>https://www.hankyung.com/article/202604294835i</t>
+        </is>
+      </c>
+      <c r="G2380" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 11:00:35 +0900</t>
+        </is>
+      </c>
+      <c r="H2380" t="inlineStr"/>
+    </row>
+    <row r="2381">
+      <c r="A2381" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2381" t="inlineStr">
+        <is>
+          <t>korean_stock</t>
+        </is>
+      </c>
+      <c r="C2381" t="inlineStr">
+        <is>
+          <t>국내 증권·투자</t>
+        </is>
+      </c>
+      <c r="D2381" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2381" t="inlineStr">
+        <is>
+          <t>"900조원치 사놨는데 대금 지불 못한다"…또 흔들리는 '오픈AI 공동체'</t>
+        </is>
+      </c>
+      <c r="F2381" t="inlineStr">
+        <is>
+          <t>https://www.hankyung.com/article/202604293962i</t>
+        </is>
+      </c>
+      <c r="G2381" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 10:54:23 +0900</t>
+        </is>
+      </c>
+      <c r="H2381" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/storage/news_db.xlsx
+++ b/storage/news_db.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2381"/>
+  <dimension ref="A1:H2498"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -74855,8 +74855,6 @@
           <t>https://www.hani.co.kr/arti/politics/politics_general/1256430.html</t>
         </is>
       </c>
-      <c r="G2326" t="inlineStr"/>
-      <c r="H2326" t="inlineStr"/>
     </row>
     <row r="2327">
       <c r="A2327" t="inlineStr">
@@ -74889,8 +74887,6 @@
           <t>https://www.hani.co.kr/arti/society/society_general/1256429.html</t>
         </is>
       </c>
-      <c r="G2327" t="inlineStr"/>
-      <c r="H2327" t="inlineStr"/>
     </row>
     <row r="2328">
       <c r="A2328" t="inlineStr">
@@ -74923,8 +74919,6 @@
           <t>https://www.hani.co.kr/arti/economy/economy_general/1256428.html</t>
         </is>
       </c>
-      <c r="G2328" t="inlineStr"/>
-      <c r="H2328" t="inlineStr"/>
     </row>
     <row r="2329">
       <c r="A2329" t="inlineStr">
@@ -74957,8 +74951,6 @@
           <t>https://www.hani.co.kr/arti/society/environment/1256427.html</t>
         </is>
       </c>
-      <c r="G2329" t="inlineStr"/>
-      <c r="H2329" t="inlineStr"/>
     </row>
     <row r="2330">
       <c r="A2330" t="inlineStr">
@@ -74991,8 +74983,6 @@
           <t>https://www.hani.co.kr/arti/economy/finance/1256426.html</t>
         </is>
       </c>
-      <c r="G2330" t="inlineStr"/>
-      <c r="H2330" t="inlineStr"/>
     </row>
     <row r="2331">
       <c r="A2331" t="inlineStr">
@@ -75025,8 +75015,6 @@
           <t>https://www.hani.co.kr/arti/area/capital/1256425.html</t>
         </is>
       </c>
-      <c r="G2331" t="inlineStr"/>
-      <c r="H2331" t="inlineStr"/>
     </row>
     <row r="2332">
       <c r="A2332" t="inlineStr">
@@ -75059,8 +75047,6 @@
           <t>https://www.hani.co.kr/arti/society/society_general/1256424.html</t>
         </is>
       </c>
-      <c r="G2332" t="inlineStr"/>
-      <c r="H2332" t="inlineStr"/>
     </row>
     <row r="2333">
       <c r="A2333" t="inlineStr">
@@ -75093,8 +75079,6 @@
           <t>https://www.hani.co.kr/arti/society/society_general/1256423.html</t>
         </is>
       </c>
-      <c r="G2333" t="inlineStr"/>
-      <c r="H2333" t="inlineStr"/>
     </row>
     <row r="2334">
       <c r="A2334" t="inlineStr">
@@ -75132,7 +75116,6 @@
           <t>Wed, 29 Apr 2026 14:08:53 +0900</t>
         </is>
       </c>
-      <c r="H2334" t="inlineStr"/>
     </row>
     <row r="2335">
       <c r="A2335" t="inlineStr">
@@ -75170,7 +75153,6 @@
           <t>Wed, 29 Apr 2026 14:04:00 +0900</t>
         </is>
       </c>
-      <c r="H2335" t="inlineStr"/>
     </row>
     <row r="2336">
       <c r="A2336" t="inlineStr">
@@ -75208,7 +75190,6 @@
           <t>Wed, 29 Apr 2026 13:55:58 +0900</t>
         </is>
       </c>
-      <c r="H2336" t="inlineStr"/>
     </row>
     <row r="2337">
       <c r="A2337" t="inlineStr">
@@ -75246,7 +75227,6 @@
           <t>Wed, 29 Apr 2026 13:44:22 +0900</t>
         </is>
       </c>
-      <c r="H2337" t="inlineStr"/>
     </row>
     <row r="2338">
       <c r="A2338" t="inlineStr">
@@ -75284,7 +75264,6 @@
           <t>Wed, 29 Apr 2026 13:34:40 +0900</t>
         </is>
       </c>
-      <c r="H2338" t="inlineStr"/>
     </row>
     <row r="2339">
       <c r="A2339" t="inlineStr">
@@ -75322,7 +75301,6 @@
           <t>Wed, 29 Apr 2026 12:26:55 +0900</t>
         </is>
       </c>
-      <c r="H2339" t="inlineStr"/>
     </row>
     <row r="2340">
       <c r="A2340" t="inlineStr">
@@ -75360,7 +75338,6 @@
           <t>Wed, 29 Apr 2026 12:23:25 +0900</t>
         </is>
       </c>
-      <c r="H2340" t="inlineStr"/>
     </row>
     <row r="2341">
       <c r="A2341" t="inlineStr">
@@ -75398,7 +75375,6 @@
           <t>Wed, 29 Apr 2026 12:21:15 +0900</t>
         </is>
       </c>
-      <c r="H2341" t="inlineStr"/>
     </row>
     <row r="2342">
       <c r="A2342" t="inlineStr">
@@ -75604,7 +75580,6 @@
           <t>Wed, 29 Apr 2026 14:12:59 +09:00</t>
         </is>
       </c>
-      <c r="H2346" t="inlineStr"/>
     </row>
     <row r="2347">
       <c r="A2347" t="inlineStr">
@@ -76776,7 +76751,6 @@
           <t>Wed, 29 Apr 2026 13:10:11 +0900</t>
         </is>
       </c>
-      <c r="H2374" t="inlineStr"/>
     </row>
     <row r="2375">
       <c r="A2375" t="inlineStr">
@@ -76814,7 +76788,6 @@
           <t>Wed, 29 Apr 2026 11:40:24 +0900</t>
         </is>
       </c>
-      <c r="H2375" t="inlineStr"/>
     </row>
     <row r="2376">
       <c r="A2376" t="inlineStr">
@@ -76852,7 +76825,6 @@
           <t>Wed, 29 Apr 2026 11:37:25 +0900</t>
         </is>
       </c>
-      <c r="H2376" t="inlineStr"/>
     </row>
     <row r="2377">
       <c r="A2377" t="inlineStr">
@@ -76890,7 +76862,6 @@
           <t>Wed, 29 Apr 2026 11:32:04 +0900</t>
         </is>
       </c>
-      <c r="H2377" t="inlineStr"/>
     </row>
     <row r="2378">
       <c r="A2378" t="inlineStr">
@@ -76928,7 +76899,6 @@
           <t>Wed, 29 Apr 2026 11:16:33 +0900</t>
         </is>
       </c>
-      <c r="H2378" t="inlineStr"/>
     </row>
     <row r="2379">
       <c r="A2379" t="inlineStr">
@@ -76966,7 +76936,6 @@
           <t>Wed, 29 Apr 2026 11:04:04 +0900</t>
         </is>
       </c>
-      <c r="H2379" t="inlineStr"/>
     </row>
     <row r="2380">
       <c r="A2380" t="inlineStr">
@@ -77004,7 +76973,6 @@
           <t>Wed, 29 Apr 2026 11:00:35 +0900</t>
         </is>
       </c>
-      <c r="H2380" t="inlineStr"/>
     </row>
     <row r="2381">
       <c r="A2381" t="inlineStr">
@@ -77042,7 +77010,4883 @@
           <t>Wed, 29 Apr 2026 10:54:23 +0900</t>
         </is>
       </c>
-      <c r="H2381" t="inlineStr"/>
+    </row>
+    <row r="2382">
+      <c r="A2382" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2382" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2382" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2382" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2382" t="inlineStr">
+        <is>
+          <t>美·이란 교착 장기화 조짐…브렌트유 114달러 넘어서</t>
+        </is>
+      </c>
+      <c r="F2382" t="inlineStr">
+        <is>
+          <t>https://www.hankyung.com/article/202604296598i</t>
+        </is>
+      </c>
+      <c r="G2382" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 20:20:28 +0900</t>
+        </is>
+      </c>
+      <c r="H2382" t="inlineStr"/>
+    </row>
+    <row r="2383">
+      <c r="A2383" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2383" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2383" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2383" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2383" t="inlineStr">
+        <is>
+          <t>신세계, 경영전략실 개편…정용진 회장이 직접 지휘</t>
+        </is>
+      </c>
+      <c r="F2383" t="inlineStr">
+        <is>
+          <t>https://www.hankyung.com/article/2026042966001</t>
+        </is>
+      </c>
+      <c r="G2383" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 20:18:41 +0900</t>
+        </is>
+      </c>
+      <c r="H2383" t="inlineStr"/>
+    </row>
+    <row r="2384">
+      <c r="A2384" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2384" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2384" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2384" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2384" t="inlineStr">
+        <is>
+          <t>[포토] 트럼프 주니어, 정용진 회장 부인 콘서트 참석</t>
+        </is>
+      </c>
+      <c r="F2384" t="inlineStr">
+        <is>
+          <t>https://www.hankyung.com/article/2026042965991</t>
+        </is>
+      </c>
+      <c r="G2384" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 20:18:14 +0900</t>
+        </is>
+      </c>
+      <c r="H2384" t="inlineStr"/>
+    </row>
+    <row r="2385">
+      <c r="A2385" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2385" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2385" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2385" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2385" t="inlineStr">
+        <is>
+          <t>스벅까지 뛰어들었다…"아아는 거들 뿐" 사장님들 꽂힌 '이 메뉴' [트렌드+]</t>
+        </is>
+      </c>
+      <c r="F2385" t="inlineStr">
+        <is>
+          <t>https://www.hankyung.com/article/202604295825g</t>
+        </is>
+      </c>
+      <c r="G2385" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 20:00:04 +0900</t>
+        </is>
+      </c>
+      <c r="H2385" t="inlineStr"/>
+    </row>
+    <row r="2386">
+      <c r="A2386" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2386" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2386" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2386" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2386" t="inlineStr">
+        <is>
+          <t>美, 램리서치 등 반도체 장비 회사에 중국 선적 중단 명령</t>
+        </is>
+      </c>
+      <c r="F2386" t="inlineStr">
+        <is>
+          <t>https://www.hankyung.com/article/202604296559i</t>
+        </is>
+      </c>
+      <c r="G2386" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 19:12:40 +0900</t>
+        </is>
+      </c>
+      <c r="H2386" t="inlineStr"/>
+    </row>
+    <row r="2387">
+      <c r="A2387" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2387" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2387" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2387" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2387" t="inlineStr">
+        <is>
+          <t>딥엑스, 신한금융서 1000억 이상 투자 받는다</t>
+        </is>
+      </c>
+      <c r="F2387" t="inlineStr">
+        <is>
+          <t>https://www.hankyung.com/article/2026042962631</t>
+        </is>
+      </c>
+      <c r="G2387" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 18:23:26 +0900</t>
+        </is>
+      </c>
+      <c r="H2387" t="inlineStr"/>
+    </row>
+    <row r="2388">
+      <c r="A2388" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2388" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2388" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2388" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2388" t="inlineStr">
+        <is>
+          <t>[포토] 현대글로비스, 세계 최대 車운반선 도입</t>
+        </is>
+      </c>
+      <c r="F2388" t="inlineStr">
+        <is>
+          <t>https://www.hankyung.com/article/2026042963391</t>
+        </is>
+      </c>
+      <c r="G2388" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 18:22:00 +0900</t>
+        </is>
+      </c>
+      <c r="H2388" t="inlineStr"/>
+    </row>
+    <row r="2389">
+      <c r="A2389" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2389" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2389" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2389" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2389" t="inlineStr">
+        <is>
+          <t>[포토] 메디슨 황, 두산과 로봇 사업 논의</t>
+        </is>
+      </c>
+      <c r="F2389" t="inlineStr">
+        <is>
+          <t>https://www.hankyung.com/article/2026042963001</t>
+        </is>
+      </c>
+      <c r="G2389" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 18:18:16 +0900</t>
+        </is>
+      </c>
+      <c r="H2389" t="inlineStr"/>
+    </row>
+    <row r="2390">
+      <c r="A2390" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2390" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2390" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2390" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2390" t="inlineStr">
+        <is>
+          <t>“매시간 수영장 100개 분량 소실되는 셈”…무섭게 녹아내리는 그린란드 얼음</t>
+        </is>
+      </c>
+      <c r="F2390" t="inlineStr">
+        <is>
+          <t>https://www.mk.co.kr/news/world/12031382</t>
+        </is>
+      </c>
+      <c r="G2390" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 20:31:49 +09:00</t>
+        </is>
+      </c>
+      <c r="H2390" t="inlineStr">
+        <is>
+          <t>지난해 알프스 얼음 1.5배 사라져 유럽 대륙 온난화, 전세계보다 2배 빨라 10년마다 0.56도 상승유럽의 온난화 속도가 전세계 평균보다 2배 빠르게 진행되고 있는 가운데, 그린..</t>
+        </is>
+      </c>
+    </row>
+    <row r="2391">
+      <c r="A2391" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2391" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2391" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2391" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2391" t="inlineStr">
+        <is>
+          <t>하이브, ‘BTS 컴백’에 1분기 매출 6983억원…조정 영업익 585억</t>
+        </is>
+      </c>
+      <c r="F2391" t="inlineStr">
+        <is>
+          <t>https://www.mk.co.kr/news/business/12031375</t>
+        </is>
+      </c>
+      <c r="G2391" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 20:21:18 +09:00</t>
+        </is>
+      </c>
+      <c r="H2391" t="inlineStr">
+        <is>
+          <t>엔터테인먼트 기업 하이브가 소속 가수 방탄소년단(BTS)의 컴백 등에 힘입어 1분기에 연결 기준 7천억원에 가까운 매출을 기록했다. 하이브는 올해 1분기 매출이 6천983억원으로,..</t>
+        </is>
+      </c>
+    </row>
+    <row r="2392">
+      <c r="A2392" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2392" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2392" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2392" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2392" t="inlineStr">
+        <is>
+          <t>“음쓰 버리다가 사장님 만났네요”…삼성·네이버·SK 모두 여기 산다</t>
+        </is>
+      </c>
+      <c r="F2392" t="inlineStr">
+        <is>
+          <t>https://www.mk.co.kr/news/realestate/12031366</t>
+        </is>
+      </c>
+      <c r="G2392" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 20:16:06 +09:00</t>
+        </is>
+      </c>
+      <c r="H2392" t="inlineStr">
+        <is>
+          <t>CEO스코어, 주소지 분석  디에이치퍼스티어아이파크 삼성전자 노태문·네이버 최수연  셀트리온 서진석 등 11명 거주  나인원한남·래미안퍼스티지 순 서울 밖 경기권 상위 단지는  판..</t>
+        </is>
+      </c>
+    </row>
+    <row r="2393">
+      <c r="A2393" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2393" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2393" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2393" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2393" t="inlineStr">
+        <is>
+          <t>[대한민국 100대 CEO] 장인화 포스코그룹 회장 | 전례 없는 철강 불황…그래도 웃었다</t>
+        </is>
+      </c>
+      <c r="F2393" t="inlineStr">
+        <is>
+          <t>https://www.mk.co.kr/news/business/12031365</t>
+        </is>
+      </c>
+      <c r="G2393" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 20:15:15 +09:00</t>
+        </is>
+      </c>
+      <c r="H2393" t="inlineStr">
+        <is>
+          <t>최근 철강 업계는 글로벌 공급 과잉, 보호무역주의 강화, 탄소중립 이행이라는 전례 없는 ‘삼중고’에 직면했다. 포스코그룹은 이러한 복합 위기 속에서도 구조적 원가 혁신으로 수익성 ..</t>
+        </is>
+      </c>
+    </row>
+    <row r="2394">
+      <c r="A2394" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2394" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2394" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2394" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2394" t="inlineStr">
+        <is>
+          <t>[대한민국 100대 CEO] 장원재 메리츠증권 사장 | 리테일·IB 결합해 한국판 골드만삭스 속도</t>
+        </is>
+      </c>
+      <c r="F2394" t="inlineStr">
+        <is>
+          <t>https://www.mk.co.kr/news/business/12031363</t>
+        </is>
+      </c>
+      <c r="G2394" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 20:14:03 +09:00</t>
+        </is>
+      </c>
+      <c r="H2394" t="inlineStr">
+        <is>
+          <t>지난해 메리츠증권은 기업금융(IB)과 리테일 부문 동반 성장을 이뤄냈다. 당기순이익은 7663억원으로 전년 대비 10% 증가했고, 자기자본 8조원을 돌파했다. 전 사업 부문에서 고..</t>
+        </is>
+      </c>
+    </row>
+    <row r="2395">
+      <c r="A2395" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2395" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2395" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2395" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2395" t="inlineStr">
+        <is>
+          <t>트럼프 ‘일방적 승리’ 선언할까?”…중간선거 참패 우려도</t>
+        </is>
+      </c>
+      <c r="F2395" t="inlineStr">
+        <is>
+          <t>https://www.mk.co.kr/news/world/12031353</t>
+        </is>
+      </c>
+      <c r="G2395" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 20:10:40 +09:00</t>
+        </is>
+      </c>
+      <c r="H2395" t="inlineStr">
+        <is>
+          <t>정보당국, 일방적 승전선언 시 영향 분석 오는 11월 중간선거 앞두고 전략 모색미국 정보기관들이 도널드 트럼프 미국 대통령의 ‘일방적 승리 선언’이 미칠 영향에 대해 분석하기 시작..</t>
+        </is>
+      </c>
+    </row>
+    <row r="2396">
+      <c r="A2396" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2396" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2396" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2396" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2396" t="inlineStr">
+        <is>
+          <t>공무원 행세하며 5억원 뜯었다…소상공인 울린 사기꾼의 최후</t>
+        </is>
+      </c>
+      <c r="F2396" t="inlineStr">
+        <is>
+          <t>https://www.mk.co.kr/news/society/12031335</t>
+        </is>
+      </c>
+      <c r="G2396" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 20:04:56 +09:00</t>
+        </is>
+      </c>
+      <c r="H2396" t="inlineStr">
+        <is>
+          <t>지방자지단체와 공공기관을 사칭하며 물품 대리 구매를 유도하는 보이스피싱에 가담한 사기꾼이 감옥 신세를 지게 됐다. 29일 연합뉴스에 따르면 부산지법 형사5부(김현순 부장판사)는 전..</t>
+        </is>
+      </c>
+    </row>
+    <row r="2397">
+      <c r="A2397" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2397" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2397" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2397" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2397" t="inlineStr">
+        <is>
+          <t>“뜻밖의 일, 매우 기뻐”…47세 탕웨이 10년만에 둘째 임신</t>
+        </is>
+      </c>
+      <c r="F2397" t="inlineStr">
+        <is>
+          <t>https://www.mk.co.kr/news/society/12031317</t>
+        </is>
+      </c>
+      <c r="G2397" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 19:59:53 +09:00</t>
+        </is>
+      </c>
+      <c r="H2397" t="inlineStr">
+        <is>
+          <t>김태용 감독의 아내이자 중국 출신 배우인 탕웨이가 사회관계망서비스(SNS)를 통해 둘째 임신 사실을 공개했다. 탕웨이는 29일 SNS에 중국어로 “우리 집에 새끼 말이 하나 더 생..</t>
+        </is>
+      </c>
+    </row>
+    <row r="2398">
+      <c r="A2398" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2398" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2398" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2398" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2398" t="inlineStr">
+        <is>
+          <t>달러-원, 런던장서 DXY·WTI 반등에 1,480원선 웃돌아…한때 1,480.20원</t>
+        </is>
+      </c>
+      <c r="F2398" t="inlineStr">
+        <is>
+          <t>https://news.einfomax.co.kr/news/articleView.html?idxno=4412461</t>
+        </is>
+      </c>
+      <c r="G2398" t="inlineStr">
+        <is>
+          <t>2026-04-29 19:59:04</t>
+        </is>
+      </c>
+      <c r="H2398" t="inlineStr"/>
+    </row>
+    <row r="2399">
+      <c r="A2399" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2399" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2399" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2399" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2399" t="inlineStr">
+        <is>
+          <t>LG전자, 1Q 영업익 1.7조 확정…&amp;quot;VS사업 영업익 역대 최대&amp;quot;(종합)</t>
+        </is>
+      </c>
+      <c r="F2399" t="inlineStr">
+        <is>
+          <t>https://news.einfomax.co.kr/news/articleView.html?idxno=4412460</t>
+        </is>
+      </c>
+      <c r="G2399" t="inlineStr">
+        <is>
+          <t>2026-04-29 19:16:00</t>
+        </is>
+      </c>
+      <c r="H2399" t="inlineStr">
+        <is>
+          <t>LG전자가 올해 1분기 역대급 실적을 확정지었다. HS·VS사업본부가 사상 최대 분기 매출액을 달성했고, VS사업본부는 영업이익도 역대 최대를 기록했다.29일 금융감독원 전자공시시스템에 따르면 LG전자는 올해 1분기 연결 기준 매출액으로 23조7천272억원, 영업이익으...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2400">
+      <c r="A2400" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2400" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2400" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2400" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2400" t="inlineStr">
+        <is>
+          <t>[亞증시-종합] 중국·홍콩, 강세…대만은↓</t>
+        </is>
+      </c>
+      <c r="F2400" t="inlineStr">
+        <is>
+          <t>https://news.einfomax.co.kr/news/articleView.html?idxno=4412459</t>
+        </is>
+      </c>
+      <c r="G2400" t="inlineStr">
+        <is>
+          <t>2026-04-29 19:10:51</t>
+        </is>
+      </c>
+      <c r="H2400" t="inlineStr">
+        <is>
+          <t>29일 아시아 증시는 일본이 휴장한 가운데 대체로 강세를 나타냈다. 중국과 홍콩의 주요 지수가 일제히 올랐고, 대만 증시는 반도체 부진 속에 하락했다.◇중국 = 중국 증시는 중동 불안 속에서도 희토류 관련주를 중심으로 매수세가 들어오며 상승했다.연합인포맥스 세계주가지수...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2401">
+      <c r="A2401" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2401" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2401" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2401" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2401" t="inlineStr">
+        <is>
+          <t>DL이앤씨, 상대원2구역 시공사 지위 회복…GS건설 선정 '브레이크'</t>
+        </is>
+      </c>
+      <c r="F2401" t="inlineStr">
+        <is>
+          <t>https://news.einfomax.co.kr/news/articleView.html?idxno=4412458</t>
+        </is>
+      </c>
+      <c r="G2401" t="inlineStr">
+        <is>
+          <t>2026-04-29 19:04:13</t>
+        </is>
+      </c>
+      <c r="H2401" t="inlineStr">
+        <is>
+          <t>상대원2구역 재개발 사업이 새 국면을 맞았다. DL이앤씨[375500]가 시공사 지위를 회복함과 동시에, 조합 측이 강행하려던 새로운 시공사 선정 총회에는 제동이 걸렸다.29일 정비업계에 따르면 수원지방법원 성남지원(제5민사부)은 DL이앤씨가 제기한 시공사 해제총회 결...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2402">
+      <c r="A2402" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2402" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2402" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2402" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2402" t="inlineStr">
+        <is>
+          <t>[채권-마감] WGBI 유입 기대·연금 매수에 국고 10년 1.8bp↓</t>
+        </is>
+      </c>
+      <c r="F2402" t="inlineStr">
+        <is>
+          <t>https://news.einfomax.co.kr/news/articleView.html?idxno=4412457</t>
+        </is>
+      </c>
+      <c r="G2402" t="inlineStr">
+        <is>
+          <t>2026-04-29 19:03:21</t>
+        </is>
+      </c>
+      <c r="H2402" t="inlineStr">
+        <is>
+          <t>국고채 금리가 29일 장기물 중심으로 하락했다.장중 대부분 약세를 보였으나, 세계국채지수(WGBI) 자금 유입과 국민연금의 국고채 매수 소식이 강세 재료로 작용했다.서울 채권시장에 따르면 국고채 3년물 최종호가 수익률은 전장 대비 0.4bp 하락한 3.525%였다. 1...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2403">
+      <c r="A2403" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2403" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2403" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2403" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2403" t="inlineStr">
+        <is>
+          <t>정의선 현대차그룹 회장, 8년 만에 中 베이징 모터쇼 방문</t>
+        </is>
+      </c>
+      <c r="F2403" t="inlineStr">
+        <is>
+          <t>https://news.einfomax.co.kr/news/articleView.html?idxno=4412456</t>
+        </is>
+      </c>
+      <c r="G2403" t="inlineStr">
+        <is>
+          <t>2026-04-29 19:00:00</t>
+        </is>
+      </c>
+      <c r="H2403" t="inlineStr">
+        <is>
+          <t>정의선 현대차그룹 회장이 8년 만에 세계 최대 자동차 전시회인 베이징 모터쇼를 방문했다.29일 관련 업계에 따르면 정 회장은 이날 베이징 모터쇼(오토차이나 2026)를 찾았다.그가 베이징 모터쇼를 참관한 것은 2018년 이후 8년 만이다. 지난해에는 상하이 모터쇼를 방...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2404">
+      <c r="A2404" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2404" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2404" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2404" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2404" t="inlineStr">
+        <is>
+          <t>우리금융F&amp;amp;I, 공모채 수요예측에 1.4조 유입…두 자릿수 '언더'</t>
+        </is>
+      </c>
+      <c r="F2404" t="inlineStr">
+        <is>
+          <t>https://news.einfomax.co.kr/news/articleView.html?idxno=4412455</t>
+        </is>
+      </c>
+      <c r="G2404" t="inlineStr">
+        <is>
+          <t>2026-04-29 18:59:42</t>
+        </is>
+      </c>
+      <c r="H2404" t="inlineStr">
+        <is>
+          <t>우리금융에프앤아이(A)가 공모채 수요예측에서 조 단위 수요를 확보해 가산금리(스프레드)를 두 자릿수 아래로 끌어 내렸다.29일 투자은행(IB) 업계에 따르면 우리금융에프앤아이는 이날 1천억원 규모의 회사채 수요예측에서 1조4천380억원 규모의 주문을 모았다.모집액은 1...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2405">
+      <c r="A2405" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2405" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2405" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2405" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2405" t="inlineStr">
+        <is>
+          <t>IRS 금리, 중장기 구간 위주로 하락…美금리 따라 플래트닝</t>
+        </is>
+      </c>
+      <c r="F2405" t="inlineStr">
+        <is>
+          <t>https://news.einfomax.co.kr/news/articleView.html?idxno=4412454</t>
+        </is>
+      </c>
+      <c r="G2405" t="inlineStr">
+        <is>
+          <t>2026-04-29 18:58:39</t>
+        </is>
+      </c>
+      <c r="H2405" t="inlineStr">
+        <is>
+          <t>IRS(금리스와프) 금리가 중장기 구간을 중심으로 소폭 하락하며 강보합세를 나타냈다.29일 서울 채권시장에 따르면 1년 IRS 금리는 오후 4시 54분 기준 전 거래일 대비 0.50bp 하락한 3.2425%를 기록했다.2년은 전일과 동일한 3.5575%였으며, 3년은 ...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2406">
+      <c r="A2406" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2406" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2406" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2406" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2406" t="inlineStr">
+        <is>
+          <t>부자아빠 “폭락장 다가온다…더 부자가 될 계획”…“금·은·비트코인 사라”</t>
+        </is>
+      </c>
+      <c r="F2406" t="inlineStr">
+        <is>
+          <t>https://www.etnews.com/20260429000477</t>
+        </is>
+      </c>
+      <c r="G2406" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 17:48:10 +0900</t>
+        </is>
+      </c>
+      <c r="H2406" t="inlineStr">
+        <is>
+          <t>'부자 아빠 가난한 아빠'의 저자 로버트 기요사키가 글로벌 금융시장에 대공황급 위기가 올 수 있다고 경고했다. 기요사키는 28일 자신의 엑스(X·옛 트위터)를 통해 “2026~2027년에 대형 시장 붕괴가 올 수 있다”며 “다가오는 이번 폭락은 또 다른 대공황이 될 수</t>
+        </is>
+      </c>
+    </row>
+    <row r="2407">
+      <c r="A2407" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2407" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2407" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2407" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2407" t="inlineStr">
+        <is>
+          <t>“김치 남기면 재사용하겠습니다”…“테토 사장이네” 식당 셀프바 경고문 갑론을박</t>
+        </is>
+      </c>
+      <c r="F2407" t="inlineStr">
+        <is>
+          <t>https://www.etnews.com/20260429000467</t>
+        </is>
+      </c>
+      <c r="G2407" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 17:08:05 +0900</t>
+        </is>
+      </c>
+      <c r="H2407" t="inlineStr">
+        <is>
+          <t>반찬 셀프바에 “김치를 남기시면 재사용하겠습니다”라는 경고문을 붙인 한 식당이 온라인에서 논란이 되고 있다. 최근 온라인 커뮤니티 '보배드림'에는 한 식당 반찬 코너 사진이 올라왔다. 안내문에는 “김치를 남기시면 재사용하겠습니다. 땅파면 돈 나오나?”라는 문구가 적혀</t>
+        </is>
+      </c>
+    </row>
+    <row r="2408">
+      <c r="A2408" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2408" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2408" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2408" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2408" t="inlineStr">
+        <is>
+          <t>두산로보틱스-엔비디아, 피지컬 AI 로봇 협력…2028년 산업용 휴머노이드 선보인다</t>
+        </is>
+      </c>
+      <c r="F2408" t="inlineStr">
+        <is>
+          <t>https://www.etnews.com/20260429000466</t>
+        </is>
+      </c>
+      <c r="G2408" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 17:02:25 +0900</t>
+        </is>
+      </c>
+      <c r="H2408" t="inlineStr">
+        <is>
+          <t>두산로보틱스가 엔비디아와 피지컬 인공지능(AI) 기반 로봇 솔루션 개발 협력에 나선다. 로봇 전용 실행 소프트웨어와 엔비디아 AI·로보틱스 생태계를 결합해 지능형 로봇 솔루션과 산업용 휴머노이드 상용화를 추진한다. 두산로보틱스는 엔비디아 옴니버스 및 로보틱스 제품 마케</t>
+        </is>
+      </c>
+    </row>
+    <row r="2409">
+      <c r="A2409" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2409" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2409" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2409" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2409" t="inlineStr">
+        <is>
+          <t>“라면 먹을떄 '이것' 같이 먹지 마세요”…혈관·뼈 동시에 망가뜨려</t>
+        </is>
+      </c>
+      <c r="F2409" t="inlineStr">
+        <is>
+          <t>https://www.etnews.com/20260429000461</t>
+        </is>
+      </c>
+      <c r="G2409" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 17:01:49 +0900</t>
+        </is>
+      </c>
+      <c r="H2409" t="inlineStr">
+        <is>
+          <t>라면과 콜라, 사이다를 함께 먹는 식습관이 혈관과 뼈 건강을 동시에 위협할 수 있다는 지적이 나왔다. 라면의 높은 나트륨과 탄산음료 속 인산 성분이 체내 칼슘을 이중으로 소모시키기 때문이다. 질병관리청이 최근 공개한 국민건강영양조사 결과에 따르면 한국인의 칼슘 섭취량은</t>
+        </is>
+      </c>
+    </row>
+    <row r="2410">
+      <c r="A2410" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2410" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2410" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2410" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2410" t="inlineStr">
+        <is>
+          <t>레인보우로보틱스, 판교서 SW 인재 확보전…피지컬 AI 내재화 가속</t>
+        </is>
+      </c>
+      <c r="F2410" t="inlineStr">
+        <is>
+          <t>https://www.etnews.com/20260429000283</t>
+        </is>
+      </c>
+      <c r="G2410" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 17:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="H2410" t="inlineStr">
+        <is>
+          <t>레인보우로보틱스가 인공지능(AI)·소프트웨어(SW) 인력 확보와 연구개발(R&amp;amp;D) 투자를 확대하며 휴머노이드 로봇 개발에 속도를 낸다. 양팔 로봇 제어와 로봇 학습, 시뮬레이션 기반 개발 인력을 집중 채용하며 피지컬 AI 기술 내재화에 나선 모습이다. 29일 업...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2411">
+      <c r="A2411" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2411" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2411" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2411" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2411" t="inlineStr">
+        <is>
+          <t>1분기 버텼지만…석화업계, 원가 부담에 하반기 비상</t>
+        </is>
+      </c>
+      <c r="F2411" t="inlineStr">
+        <is>
+          <t>https://www.etnews.com/20260429000270</t>
+        </is>
+      </c>
+      <c r="G2411" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 17:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="H2411" t="inlineStr">
+        <is>
+          <t>석유화학업계가 1분기 래깅효과의 영향으로 실적 방어에 성공했지만 하반기 수익성 악화를 우려하고 있다. 중동 지정학 리스크로 급등한 원가가 시차를 두고 반영되면서 실적 변동성이 확대될 가능성이 크기 때문이다. 29일 관련 업계에 따르면 주요 석유화학사들은 올 1분기 전</t>
+        </is>
+      </c>
+    </row>
+    <row r="2412">
+      <c r="A2412" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2412" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2412" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2412" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2412" t="inlineStr">
+        <is>
+          <t>전자 소자·부품도 공급망 경고등…고사양 콘덴서 공급 20주 넘게 밀린다</t>
+        </is>
+      </c>
+      <c r="F2412" t="inlineStr">
+        <is>
+          <t>https://www.etnews.com/20260429000331</t>
+        </is>
+      </c>
+      <c r="G2412" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 16:30:00 +0900</t>
+        </is>
+      </c>
+      <c r="H2412" t="inlineStr">
+        <is>
+          <t>전자산업 핵심 수동소자인 적층세라믹콘덴서(MLCC)를 비롯해 글로벌 전자 소자·부품 공급망에 비상이 걸렸다. 인공지능(AI) 서버와 전장(Automotive) 수요가 폭증하면서 주요 제조사들의 납기(리드타임) 지연이 잇따르고 있다. 이로 인한 가격 인상 압박도 가시화됐</t>
+        </is>
+      </c>
+    </row>
+    <row r="2413">
+      <c r="A2413" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2413" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2413" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2413" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2413" t="inlineStr">
+        <is>
+          <t>尹, '체포방해' 등 2심서 징역 7년…1심보다 2년 늘어</t>
+        </is>
+      </c>
+      <c r="F2413" t="inlineStr">
+        <is>
+          <t>https://www.etnews.com/20260429000443</t>
+        </is>
+      </c>
+      <c r="G2413" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 16:21:32 +0900</t>
+        </is>
+      </c>
+      <c r="H2413" t="inlineStr">
+        <is>
+          <t>자신에 대한 고위공직자범죄수사처(공수처)의 체포를 방해한 혐의 등으로 기소된 윤석열 전 대통령이 항소심에서 1심보다 무거운 징역 7년을 선고받았다. 서울고법 내란전담재판부인 형사1부(부장판사 윤성식)는 29일 특수공무집행방해와 직권남용 권리행사방해 등 혐의로 재판에 넘</t>
+        </is>
+      </c>
+    </row>
+    <row r="2414">
+      <c r="A2414" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2414" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2414" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2414" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2414" t="inlineStr">
+        <is>
+          <t>[포토] 엔비디아 매디슨 황 수석 이사, 두산로보틱스 방문</t>
+        </is>
+      </c>
+      <c r="F2414" t="inlineStr">
+        <is>
+          <t>https://www.etnews.com/20260429000486</t>
+        </is>
+      </c>
+      <c r="G2414" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 19:05:44 +0900</t>
+        </is>
+      </c>
+      <c r="H2414" t="inlineStr">
+        <is>
+          <t>두산로보틱스 김민표 대표(왼쪽 여섯 번째)와 엔비디아 매디슨 황 수석 이사(왼쪽 다섯 번째)가 29일 경기 성남시 분당구 두산로보틱스 이노베이션센터에서 관계자들과 기념사진을 촬영하고 있다. 〈두산로보틱스 제공〉</t>
+        </is>
+      </c>
+    </row>
+    <row r="2415">
+      <c r="A2415" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2415" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2415" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2415" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2415" t="inlineStr">
+        <is>
+          <t>[포토] 대화하는 김민표 두산로보틱스 대표와 매디슨 황 엔비디아 수석 이사</t>
+        </is>
+      </c>
+      <c r="F2415" t="inlineStr">
+        <is>
+          <t>https://www.etnews.com/20260429000485</t>
+        </is>
+      </c>
+      <c r="G2415" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 19:05:43 +0900</t>
+        </is>
+      </c>
+      <c r="H2415" t="inlineStr">
+        <is>
+          <t>김민표 두산로보틱스 대표와 매디슨 황 엔비디아 수석 이사가 29일 경기 성남시 분당구 두산로보틱스 이노베이션센터에서 함께 대화하며 시설을 둘러보고 있다. 〈두산로보틱스 제공〉</t>
+        </is>
+      </c>
+    </row>
+    <row r="2416">
+      <c r="A2416" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2416" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2416" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2416" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2416" t="inlineStr">
+        <is>
+          <t>지란지교소프트, 넥스트인텔리전스닷에이아이 흡수합병</t>
+        </is>
+      </c>
+      <c r="F2416" t="inlineStr">
+        <is>
+          <t>https://www.etnews.com/20260429000472</t>
+        </is>
+      </c>
+      <c r="G2416" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 17:18:40 +0900</t>
+        </is>
+      </c>
+      <c r="H2416" t="inlineStr">
+        <is>
+          <t>지란지교소프트는 자회사 넥스트인텔리전스닷에이아이(NI)를 흡수합병해 인공지능(AI) 기반 사업 체제를 강화한다고 29일 밝혔다. 이번 합병은 NI 지분 100%를 보유한 상태에서 진행되는 무증자·무대가 방식으로, 신주 발행은 없다. 합병 기일은 5월 29일이다. 소멸법</t>
+        </is>
+      </c>
+    </row>
+    <row r="2417">
+      <c r="A2417" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2417" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2417" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2417" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2417" t="inlineStr">
+        <is>
+          <t>엑스엘에이트, KT위즈파크에 AI 실시간 통번역 솔루션 '이벤트캣' 공급</t>
+        </is>
+      </c>
+      <c r="F2417" t="inlineStr">
+        <is>
+          <t>https://www.etnews.com/20260429000447</t>
+        </is>
+      </c>
+      <c r="G2417" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 16:25:22 +0900</t>
+        </is>
+      </c>
+      <c r="H2417" t="inlineStr">
+        <is>
+          <t>엑스엘에이트는 KT 프로 야구단 KT위즈의 홈구장인 수원 KT 위즈파크에 인공지능(AI) 실시간 통번역 자막 솔루션 '이벤트캣'을 공급했다고 29일 밝혔다. 지난 2일 개막전을 시작으로 올 시즌 KT 위즈파크에서 열리는 전체 홈경기 72경기의 현장 해설을 영어 자막으로</t>
+        </is>
+      </c>
+    </row>
+    <row r="2418">
+      <c r="A2418" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2418" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2418" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2418" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2418" t="inlineStr">
+        <is>
+          <t>예산 깎인 시대, 맥라렌 F1이 2년 연속 챔피언이 된 비결은 더 똑똑한 AI가 아니었다</t>
+        </is>
+      </c>
+      <c r="F2418" t="inlineStr">
+        <is>
+          <t>https://www.etnews.com/20260429000431</t>
+        </is>
+      </c>
+      <c r="G2418" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 16:09:03 +0900</t>
+        </is>
+      </c>
+      <c r="H2418" t="inlineStr">
+        <is>
+          <t>더 정확한 AI를 가진 팀이 이긴다는 통념을 맥라렌 F1(McLaren F1)이 뒤집었다. 글로벌 컨설팅 기업 딜로이트(Deloitte)가 발표한 사례 보고서 '데이터로 가속하고 전략으로 승리하다(McLaren F1's Data-Driven Strategy)'에 따르면...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2419">
+      <c r="A2419" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2419" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2419" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2419" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2419" t="inlineStr">
+        <is>
+          <t>[ET톡] 5천만 국민 모두의 AI가 나오려면</t>
+        </is>
+      </c>
+      <c r="F2419" t="inlineStr">
+        <is>
+          <t>https://www.etnews.com/20260429000175</t>
+        </is>
+      </c>
+      <c r="G2419" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 16:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="H2419" t="inlineStr">
+        <is>
+          <t>“수천만 국민이 사용하는 우리나라 인공지능(AI) 서비스는 왜 아직입니까.” AI 업계 주요 관계자들 사이에서 이재명 대통령이 비공식 석상에서 배경훈 부총리 겸 과학기술정보통신부 장관과 하정우 당시 청와대 AI미래기획수석에게 물었다고 회자되는 발언 요지다. 하 전 수석</t>
+        </is>
+      </c>
+    </row>
+    <row r="2420">
+      <c r="A2420" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2420" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2420" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2420" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2420" t="inlineStr">
+        <is>
+          <t>KISIA, 'AI보안 기술개발 교육과정' 교육생 75명 모집</t>
+        </is>
+      </c>
+      <c r="F2420" t="inlineStr">
+        <is>
+          <t>https://www.etnews.com/20260429000403</t>
+        </is>
+      </c>
+      <c r="G2420" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 15:36:04 +0900</t>
+        </is>
+      </c>
+      <c r="H2420" t="inlineStr">
+        <is>
+          <t>한국정보보호산업협회(KISIA)는 과학기술정보통신부가 주최하는 '2026년 인공지능(AI) 보안 기술개발 교육과정' 교육생을 6월 중순까지 모집한다고 29일 밝혔다. 최근 생성형 AI와 대규모 언어모델(LLM) 확산으로 피싱 메일 생성, 악성코드 제작 자동화, 개인정보</t>
+        </is>
+      </c>
+    </row>
+    <row r="2421">
+      <c r="A2421" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2421" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2421" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2421" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2421" t="inlineStr">
+        <is>
+          <t>개인정보위 “듀오 유출 정보, 다크웹 모니터링 강화”</t>
+        </is>
+      </c>
+      <c r="F2421" t="inlineStr">
+        <is>
+          <t>https://www.etnews.com/20260429000374</t>
+        </is>
+      </c>
+      <c r="G2421" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 14:57:35 +0900</t>
+        </is>
+      </c>
+      <c r="H2421" t="inlineStr">
+        <is>
+          <t>정부가 듀오 개인정보 유출 사건과 관련해 다크웹 등 2차 유통 모니터링을 강화하고 있다. 양청삼 개인정보보호위원회 사무처장은 29일 서울 중구 프레스센터에서 열린 동북아공동체ICT포럼 제96회 조찬간담회에서 “듀오에서 유출된 민감한 정보들이 다크웹과 같은 2차 유통 마</t>
+        </is>
+      </c>
+    </row>
+    <row r="2422">
+      <c r="A2422" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2422" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2422" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2422" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2422" t="inlineStr">
+        <is>
+          <t>텐센트, 최신 'Hy3' 강화학습 과정에 '클로드' 활용 논란</t>
+        </is>
+      </c>
+      <c r="F2422" t="inlineStr">
+        <is>
+          <t>https://www.aitimes.com/news/articleView.html?idxno=209889</t>
+        </is>
+      </c>
+      <c r="G2422" t="inlineStr">
+        <is>
+          <t>2026-04-29 19:07:08</t>
+        </is>
+      </c>
+      <c r="H2422" t="inlineStr">
+        <is>
+          <t>중국 텐센트의 최신 AI 모델 ‘Hy3’가 개발자들로부터 긍정적인 평가를 받는 가운데, 개발 과정에서 미국 앤트로픽의 기술이 활용된 정황이 드러나 논란이 일고 있다.디 인포메이션은 28일(현지시간) 복수의 관계자와 내부 문서를 인용, 텐센트 연구진이 Hy3 성능 개선을...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2423">
+      <c r="A2423" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2423" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2423" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2423" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2423" t="inlineStr">
+        <is>
+          <t>앤트로픽, '클로드 코드' 비용 추청치 두배로 올려…사용량 기반 요금제 예고</t>
+        </is>
+      </c>
+      <c r="F2423" t="inlineStr">
+        <is>
+          <t>https://www.aitimes.com/news/articleView.html?idxno=209929</t>
+        </is>
+      </c>
+      <c r="G2423" t="inlineStr">
+        <is>
+          <t>2026-04-29 18:58:13</t>
+        </is>
+      </c>
+      <c r="H2423" t="inlineStr">
+        <is>
+          <t>앤트로픽이 '클로드 코드'의 예상 사용 비용을 최근 대폭 상향 조정, 현재의 월 정액제 모델을 종료하고 사용량 기반 과금(정량제)으로의 전환을 사실상 예고했다.앤트로픽은 27일(현지시간) 기업 개발자 기준 클로드 코드의 평균 비용이 하루 활성 사용자당 약 13달러로 집...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2424">
+      <c r="A2424" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2424" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2424" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2424" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2424" t="inlineStr">
+        <is>
+          <t>중국, GPU 없이 국산 CPU만으로 엑사스케일 슈퍼컴퓨터 개발…"역대 최고 성능 목표"</t>
+        </is>
+      </c>
+      <c r="F2424" t="inlineStr">
+        <is>
+          <t>https://www.aitimes.com/news/articleView.html?idxno=209927</t>
+        </is>
+      </c>
+      <c r="G2424" t="inlineStr">
+        <is>
+          <t>2026-04-29 18:38:27</t>
+        </is>
+      </c>
+      <c r="H2424" t="inlineStr">
+        <is>
+          <t>중국이 외산 기술과 엔비디아 GPU 가속기에 의존하지 않는 차세대 엑사스케일 슈퍼컴퓨터 개발에 나섰다. 중국 선전 국가슈퍼컴퓨팅센터는 24일(현지시간) ‘링성(Lingshen)’ 프로젝트를 공식 발표하고, CPU만으로 2엑사플롭스(ExaFLOPS) 이상의 지속 성능 달...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2425">
+      <c r="A2425" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2425" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2425" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2425" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2425" t="inlineStr">
+        <is>
+          <t>엔트로픽, 창작 소프트웨어 제어하는 '클로드 커넥터' 출시..."어도비·블렌더와 연동"</t>
+        </is>
+      </c>
+      <c r="F2425" t="inlineStr">
+        <is>
+          <t>https://www.aitimes.com/news/articleView.html?idxno=209904</t>
+        </is>
+      </c>
+      <c r="G2425" t="inlineStr">
+        <is>
+          <t>2026-04-29 18:26:49</t>
+        </is>
+      </c>
+      <c r="H2425" t="inlineStr">
+        <is>
+          <t>앤트로픽이 디자이너·아티스트·음악 프로듀서 등 크리에이티브 전문가를 위한 새로운 협업 방식을 제시했다. 앤트로픽은 28일(현지시간) 다양한 창작 소프트웨어와 '클로드'를 직접 연결하는 ‘커넥터(Connector)’를 공개했다.이번에 발표된 커넥터는 블렌더, 오토데스크,...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2426">
+      <c r="A2426" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2426" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2426" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2426" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2426" t="inlineStr">
+        <is>
+          <t>메타, 인간 형체·움직임 정밀하게 읽어내는 비전 모델 개발</t>
+        </is>
+      </c>
+      <c r="F2426" t="inlineStr">
+        <is>
+          <t>https://www.aitimes.com/news/articleView.html?idxno=209874</t>
+        </is>
+      </c>
+      <c r="G2426" t="inlineStr">
+        <is>
+          <t>2026-04-29 17:59:52</t>
+        </is>
+      </c>
+      <c r="H2426" t="inlineStr">
+        <is>
+          <t>메타 연구진은 27일(현지시간) 인간 중심 시각 인식을 위한 차세대 파운데이션 모델 ‘사피엔스2(Sapiens2)’를 온라인 아카이브를 통해 공개했다.모션 캡처 시스템이 사람의 손가락 움직임을 처리하는 데 어려움을 겪거나 분할 모델이 치아와 잇몸을 구분하지 못하는 것처...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2427">
+      <c r="A2427" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2427" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2427" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2427" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2427" t="inlineStr">
+        <is>
+          <t>버즈빌, 인터랙션 AI 에이전트 공개..."단순 광고·고객 타겟팅 한계 해결할 것"</t>
+        </is>
+      </c>
+      <c r="F2427" t="inlineStr">
+        <is>
+          <t>https://www.aitimes.com/news/articleView.html?idxno=209939</t>
+        </is>
+      </c>
+      <c r="G2427" t="inlineStr">
+        <is>
+          <t>2026-04-29 17:55:00</t>
+        </is>
+      </c>
+      <c r="H2427" t="inlineStr">
+        <is>
+          <t>버즈빌(대표 이관우)은 29일 '버즈빌 미디어 데이 2026'을 개최하고 자체 인터렉션 엔진 '다이내믹 트리오'를 결합한 AI 에이전트를 공개했다.다이내믹 트리오는 광고 노출 이후 사용자에게 최적화된 참여 경험을 실시간으로 설계하는 기술이다. 버즈빌은 '제로 클릭' 시...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2428">
+      <c r="A2428" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2428" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2428" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2428" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2428" t="inlineStr">
+        <is>
+          <t>[게시판] 스냅태그, 비가시성 워터마크 플랫폼 'K-세이프 AI' 론칭 등 단신</t>
+        </is>
+      </c>
+      <c r="F2428" t="inlineStr">
+        <is>
+          <t>https://www.aitimes.com/news/articleView.html?idxno=209940</t>
+        </is>
+      </c>
+      <c r="G2428" t="inlineStr">
+        <is>
+          <t>2026-04-29 17:50:00</t>
+        </is>
+      </c>
+      <c r="H2428" t="inlineStr">
+        <is>
+          <t>■ 비가시성 워터마크 기술 전문 스냅태그(대표 민경웅)는 AI 기본법 대응 부담이 증가한 기업들을 지원하기 위해, 무상으로 비가시성 워터마크를 적용할 수 있는 플랫폼 ‘K-세이프 AI’를 공식 론칭했다고 밝혔다. K-세이프 AI’ 플랫폼은 스냅태그의 비가시성 워터마크 ...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2429">
+      <c r="A2429" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2429" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2429" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2429" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2429" t="inlineStr">
+        <is>
+          <t>[게시판] 빅밸류, AI 부동산 비서 '복덕방 가재' 선공개 등 단신</t>
+        </is>
+      </c>
+      <c r="F2429" t="inlineStr">
+        <is>
+          <t>https://www.aitimes.com/news/articleView.html?idxno=209924</t>
+        </is>
+      </c>
+      <c r="G2429" t="inlineStr">
+        <is>
+          <t>2026-04-29 17:50:00</t>
+        </is>
+      </c>
+      <c r="H2429" t="inlineStr">
+        <is>
+          <t>■ 데이터 전문 빅밸류(공동 대표 구름, 이병욱)는 홈페이지 '실험실' 카테고리에 AI 부동산 상담 에이전트 '복덕방 가재'를 선보였다고 밝혔다. 실험실은 서비스 정식 출시 전 사용자들에게 미리 공개하는 공간이다. 복덕방 가재는 빅밸류의 부동산 데이터와 AI 에이전트 ...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2430">
+      <c r="A2430" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2430" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2430" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2430" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2430" t="inlineStr">
+        <is>
+          <t>Anti-Trump Instagram pic of seashells now enough to indict ex-FBI directors</t>
+        </is>
+      </c>
+      <c r="F2430" t="inlineStr">
+        <is>
+          <t>https://arstechnica.com/tech-policy/2026/04/anti-trump-instagram-pic-of-seashells-now-enough-to-indict-ex-fbi-directors/</t>
+        </is>
+      </c>
+      <c r="G2430" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 23:08:02 +0000</t>
+        </is>
+      </c>
+      <c r="H2430" t="inlineStr">
+        <is>
+          <t>The clown car is all gassed up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2431">
+      <c r="A2431" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2431" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2431" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2431" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2431" t="inlineStr">
+        <is>
+          <t>Flesh-eating bacteria devour man's arm and leg in just three days</t>
+        </is>
+      </c>
+      <c r="F2431" t="inlineStr">
+        <is>
+          <t>https://arstechnica.com/health/2026/04/flesh-eating-bacteria-devour-mans-arm-and-leg-in-just-three-days/</t>
+        </is>
+      </c>
+      <c r="G2431" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 20:15:04 +0000</t>
+        </is>
+      </c>
+      <c r="H2431" t="inlineStr">
+        <is>
+          <t>When doctors saw him, his limbs were discolored and crackling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2432">
+      <c r="A2432" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2432" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2432" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2432" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2432" t="inlineStr">
+        <is>
+          <t>FCC orders review of ABC licenses after Kimmel joke offends Trump and first lady</t>
+        </is>
+      </c>
+      <c r="F2432" t="inlineStr">
+        <is>
+          <t>https://arstechnica.com/tech-policy/2026/04/fcc-orders-review-of-abc-licenses-after-kimmel-joke-offends-trump-and-first-lady/</t>
+        </is>
+      </c>
+      <c r="G2432" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 19:57:13 +0000</t>
+        </is>
+      </c>
+      <c r="H2432" t="inlineStr">
+        <is>
+          <t>Kimmel joke calling Melania an "expectant widow" followed quickly by FCC order.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2433">
+      <c r="A2433" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2433" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2433" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2433" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2433" t="inlineStr">
+        <is>
+          <t>Drone pilot makes US rescind no-fly zones around unmarked, moving ICE vehicles</t>
+        </is>
+      </c>
+      <c r="F2433" t="inlineStr">
+        <is>
+          <t>https://arstechnica.com/gadgets/2026/04/no-fly-zones-around-moving-ice-vehicles-this-drone-pilot-fought-back-and-won/</t>
+        </is>
+      </c>
+      <c r="G2433" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 19:37:09 +0000</t>
+        </is>
+      </c>
+      <c r="H2433" t="inlineStr">
+        <is>
+          <t>Civil liberty concerns spur FAA to revise drone no-fly zones near ICE vehicles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2434">
+      <c r="A2434" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2434" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2434" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2434" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2434" t="inlineStr">
+        <is>
+          <t>Humanoid robots start sorting luggage in Tokyo airport test amid labor shortage</t>
+        </is>
+      </c>
+      <c r="F2434" t="inlineStr">
+        <is>
+          <t>https://arstechnica.com/ai/2026/04/japan-airlines-tests-having-robots-instead-of-humans-handle-travelers-luggage/</t>
+        </is>
+      </c>
+      <c r="G2434" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 18:01:36 +0000</t>
+        </is>
+      </c>
+      <c r="H2434" t="inlineStr">
+        <is>
+          <t>Humanoid robots could load cargo and clean aircraft cabins at Haneda Airport.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2435">
+      <c r="A2435" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2435" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2435" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2435" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2435" t="inlineStr">
+        <is>
+          <t>GitHub will start charging Copilot users based on their actual AI usage</t>
+        </is>
+      </c>
+      <c r="F2435" t="inlineStr">
+        <is>
+          <t>https://arstechnica.com/ai/2026/04/github-will-start-charging-copilot-users-based-on-their-actual-ai-usage/</t>
+        </is>
+      </c>
+      <c r="G2435" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 15:41:32 +0000</t>
+        </is>
+      </c>
+      <c r="H2435" t="inlineStr">
+        <is>
+          <t>GitHub says it can no longer absorb "escalating inference cost" from it heaviest AI users.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2436">
+      <c r="A2436" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2436" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2436" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2436" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2436" t="inlineStr">
+        <is>
+          <t>Electrical current might be the key to a better cup of coffee</t>
+        </is>
+      </c>
+      <c r="F2436" t="inlineStr">
+        <is>
+          <t>https://arstechnica.com/science/2026/04/electrical-current-might-be-the-key-to-a-better-cup-of-coffee/</t>
+        </is>
+      </c>
+      <c r="G2436" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 15:00:11 +0000</t>
+        </is>
+      </c>
+      <c r="H2436" t="inlineStr">
+        <is>
+          <t>University of Oregon scientists repurposed battery-testing tool to better measure coffee's flavor profile</t>
+        </is>
+      </c>
+    </row>
+    <row r="2437">
+      <c r="A2437" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2437" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2437" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2437" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2437" t="inlineStr">
+        <is>
+          <t>The great American data center divide</t>
+        </is>
+      </c>
+      <c r="F2437" t="inlineStr">
+        <is>
+          <t>https://arstechnica.com/ai/2026/04/rural-america-is-resisting-the-surge-in-data-center-construction/</t>
+        </is>
+      </c>
+      <c r="G2437" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 14:15:11 +0000</t>
+        </is>
+      </c>
+      <c r="H2437" t="inlineStr">
+        <is>
+          <t>Many rural communities are viscerally opposed to AI infrastructure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2438">
+      <c r="A2438" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2438" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2438" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2438" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2438" t="inlineStr">
+        <is>
+          <t>Meta isn’t doing enough to keep kids off Facebook and Instagram, rules EU</t>
+        </is>
+      </c>
+      <c r="F2438" t="inlineStr">
+        <is>
+          <t>https://www.theverge.com/tech/920313/meta-facebook-instagram-eu-dsa-age-verification</t>
+        </is>
+      </c>
+      <c r="G2438" t="inlineStr">
+        <is>
+          <t>2026-04-29T06:46:24-04:00</t>
+        </is>
+      </c>
+      <c r="H2438" t="inlineStr">
+        <is>
+          <t>Meta is breaching Europe's Digital Services Act (DSA) rules by failing to prevent children under 13 from using Facebook and Instagram, according to a ...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2439">
+      <c r="A2439" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2439" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2439" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2439" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2439" t="inlineStr">
+        <is>
+          <t>China freezes new robotaxi licenses after Baidu chaos</t>
+        </is>
+      </c>
+      <c r="F2439" t="inlineStr">
+        <is>
+          <t>https://www.theverge.com/ai-artificial-intelligence/920312/china-suspends-autonomous-vehicle-permits-baidu-chaos</t>
+        </is>
+      </c>
+      <c r="G2439" t="inlineStr">
+        <is>
+          <t>2026-04-29T06:39:21-04:00</t>
+        </is>
+      </c>
+      <c r="H2439" t="inlineStr">
+        <is>
+          <t>China has suspended new licenses for autonomous vehicles, Bloomberg reports, citing unnamed people familiar with the matter. The move comes after doze...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2440">
+      <c r="A2440" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2440" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2440" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2440" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2440" t="inlineStr">
+        <is>
+          <t>GitHub rushed to fix a critical vulnerability in less than six hours</t>
+        </is>
+      </c>
+      <c r="F2440" t="inlineStr">
+        <is>
+          <t>https://www.theverge.com/news/920295/github-remote-code-execution-vulnerability-fix</t>
+        </is>
+      </c>
+      <c r="G2440" t="inlineStr">
+        <is>
+          <t>2026-04-29T06:04:25-04:00</t>
+        </is>
+      </c>
+      <c r="H2440" t="inlineStr">
+        <is>
+          <t>GitHub employees fixed a critical remote code execution vulnerability in less than six hours last month. Wiz Research used AI models to uncover a vuln...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2441">
+      <c r="A2441" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2441" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2441" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2441" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2441" t="inlineStr">
+        <is>
+          <t>General Motors is adding Gemini to four million cars</t>
+        </is>
+      </c>
+      <c r="F2441" t="inlineStr">
+        <is>
+          <t>https://www.theverge.com/transportation/920285/general-motors-gm-gemini-ai-update</t>
+        </is>
+      </c>
+      <c r="G2441" t="inlineStr">
+        <is>
+          <t>2026-04-29T05:14:38-04:00</t>
+        </is>
+      </c>
+      <c r="H2441" t="inlineStr">
+        <is>
+          <t>General Motors is planning to bring Google's Gemini AI assistant to around four million vehicles across the US. Model year 2022 and newer Cadillac, Ch...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2442">
+      <c r="A2442" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2442" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2442" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2442" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2442" t="inlineStr">
+        <is>
+          <t>It’s primetime for conspiracy theorist video creators</t>
+        </is>
+      </c>
+      <c r="F2442" t="inlineStr">
+        <is>
+          <t>https://www.theverge.com/streaming/919291/white-house-correspondents-dinner-conspiracy-videos-false-flag</t>
+        </is>
+      </c>
+      <c r="G2442" t="inlineStr">
+        <is>
+          <t>2026-04-28T19:31:53-04:00</t>
+        </is>
+      </c>
+      <c r="H2442" t="inlineStr">
+        <is>
+          <t>In the days since this year's White House Correspondents' Dinner was cut short when shots were fired at the event, there has been a boom of conspiracy...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2443">
+      <c r="A2443" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2443" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2443" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2443" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2443" t="inlineStr">
+        <is>
+          <t>Elon Musk appeared more petty than prepared</t>
+        </is>
+      </c>
+      <c r="F2443" t="inlineStr">
+        <is>
+          <t>https://www.theverge.com/ai-artificial-intelligence/920191/elon-musk-sam-altman-trial-day-one</t>
+        </is>
+      </c>
+      <c r="G2443" t="inlineStr">
+        <is>
+          <t>2026-04-28T19:17:12-04:00</t>
+        </is>
+      </c>
+      <c r="H2443" t="inlineStr">
+        <is>
+          <t>Today the first witness was sworn in in Musk v. Altman: Elon Musk. I was surprised by how flat he seemed. This is not the first time I've seen Musk in...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2444">
+      <c r="A2444" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2444" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2444" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2444" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2444" t="inlineStr">
+        <is>
+          <t>James Comey indicted over Instagram seashell photo that allegedly threatened Trump</t>
+        </is>
+      </c>
+      <c r="F2444" t="inlineStr">
+        <is>
+          <t>https://www.theverge.com/policy/920131/james-comey-indicted-over-instagram-seashell-photo-that-allegedly-threatened-trump</t>
+        </is>
+      </c>
+      <c r="G2444" t="inlineStr">
+        <is>
+          <t>2026-04-28T17:40:08-04:00</t>
+        </is>
+      </c>
+      <c r="H2444" t="inlineStr">
+        <is>
+          <t>The US Department of Justice has once again indicted James Comey - this time, for an alleged threat the former FBI director made toward President Dona...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2445">
+      <c r="A2445" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2445" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2445" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2445" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2445" t="inlineStr">
+        <is>
+          <t>Elon Musk tells the jury that all he wants to do is save humanity</t>
+        </is>
+      </c>
+      <c r="F2445" t="inlineStr">
+        <is>
+          <t>https://www.theverge.com/ai-artificial-intelligence/920048/elon-musk-testimony-save-humanity</t>
+        </is>
+      </c>
+      <c r="G2445" t="inlineStr">
+        <is>
+          <t>2026-04-28T16:46:54-04:00</t>
+        </is>
+      </c>
+      <c r="H2445" t="inlineStr">
+        <is>
+          <t>On the stand, Elon Musk is positioning himself as a savior. In the high-profile trial between him and his fellow OpenAI cofounder, now CEO, Sam Altman...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2446">
+      <c r="A2446" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2446" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2446" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2446" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2446" t="inlineStr">
+        <is>
+          <t>Coby Adcock’s Scout AI raises $100 million to train its models for war. We visited its bootcamp</t>
+        </is>
+      </c>
+      <c r="F2446" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/04/29/coby-adcocks-scout-ai-raises-100-million-to-train-models-for-war-we-visited-its-bootcamp/</t>
+        </is>
+      </c>
+      <c r="G2446" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 09:45:00 +0000</t>
+        </is>
+      </c>
+      <c r="H2446" t="inlineStr">
+        <is>
+          <t>We visited Scout AI's training ground where it's working on AI agents that give individual soldiers control of  fleets of autonomous vehicles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2447">
+      <c r="A2447" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2447" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2447" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2447" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2447" t="inlineStr">
+        <is>
+          <t>How one venture firm is investing in an increasingly fragmented world</t>
+        </is>
+      </c>
+      <c r="F2447" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/04/28/how-one-venture-firm-is-navigating-an-increasingly-fragmented-world/</t>
+        </is>
+      </c>
+      <c r="G2447" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 03:00:00 +0000</t>
+        </is>
+      </c>
+      <c r="H2447" t="inlineStr">
+        <is>
+          <t>Geopolitical turmoil has made venture investing challenging, leading Kompas VC to carve out a niche in startups focused on the physical world.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2448">
+      <c r="A2448" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2448" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2448" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2448" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2448" t="inlineStr">
+        <is>
+          <t>At his OpenAI trial, Musk relitigates an old friendship</t>
+        </is>
+      </c>
+      <c r="F2448" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/04/28/at-his-openai-trial-musk-relitigates-an-old-friendship/</t>
+        </is>
+      </c>
+      <c r="G2448" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 00:40:16 +0000</t>
+        </is>
+      </c>
+      <c r="H2448" t="inlineStr">
+        <is>
+          <t>It's a story Musk has told before -- in interviews and to author Walter Isaacson for his bestselling biography of Musk -- but Tuesday was the first ti...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2449">
+      <c r="A2449" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2449" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2449" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2449" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2449" t="inlineStr">
+        <is>
+          <t>Amazon is already offering new OpenAI products on AWS</t>
+        </is>
+      </c>
+      <c r="F2449" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/04/28/amazon-is-already-offering-new-openai-products-on-aws/</t>
+        </is>
+      </c>
+      <c r="G2449" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 19:48:02 +0000</t>
+        </is>
+      </c>
+      <c r="H2449" t="inlineStr">
+        <is>
+          <t>A day after OpenAI got Microsoft to agree to end exclusive rights, AWS announced a slate of OpenAI model offerings, including a new agent service.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2450">
+      <c r="A2450" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2450" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2450" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2450" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2450" t="inlineStr">
+        <is>
+          <t>Amazon launches an AI-powered audio Q&amp;A experience on product pages</t>
+        </is>
+      </c>
+      <c r="F2450" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/04/28/amazon-launches-an-ai-powered-audio-qa-experience-on-product-pages/</t>
+        </is>
+      </c>
+      <c r="G2450" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 18:49:54 +0000</t>
+        </is>
+      </c>
+      <c r="H2450" t="inlineStr">
+        <is>
+          <t>Amazon's new "Join the chat" feature lets you ask questions about products and receive AI-powered audio responses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2451">
+      <c r="A2451" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2451" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2451" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2451" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2451" t="inlineStr">
+        <is>
+          <t>Match Group invests $100M in Sniffies, a cruising app for gay men</t>
+        </is>
+      </c>
+      <c r="F2451" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/04/28/match-group-invests-100-million-in-sniffies-a-cruising-app-for-gay-men/</t>
+        </is>
+      </c>
+      <c r="G2451" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 18:16:54 +0000</t>
+        </is>
+      </c>
+      <c r="H2451" t="inlineStr">
+        <is>
+          <t>The app is Match Group's newest attempt to get mobile users excited about online romance again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2452">
+      <c r="A2452" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2452" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2452" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2452" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2452" t="inlineStr">
+        <is>
+          <t>Google expands Pentagon’s access to its AI after Anthropic’s refusal</t>
+        </is>
+      </c>
+      <c r="F2452" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/04/28/google-expands-pentagons-access-to-its-ai-after-anthropics-refusal/</t>
+        </is>
+      </c>
+      <c r="G2452" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 18:15:00 +0000</t>
+        </is>
+      </c>
+      <c r="H2452" t="inlineStr">
+        <is>
+          <t>After Anthropic refused to allow the DoD to use its AI for domestic mass surveillance and autonomous weapons, Google has signed a new contract with th...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2453">
+      <c r="A2453" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2453" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2453" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2453" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2453" t="inlineStr">
+        <is>
+          <t>Paragon is not collaborating with Italian authorities probing spyware attacks, report says</t>
+        </is>
+      </c>
+      <c r="F2453" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/04/28/paragon-is-not-collaborating-with-italian-authorities-probing-spyware-attacks-report-says/</t>
+        </is>
+      </c>
+      <c r="G2453" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 17:46:47 +0000</t>
+        </is>
+      </c>
+      <c r="H2453" t="inlineStr">
+        <is>
+          <t>Despite promising to help determine what happened with the hacks targeting journalists and activists in Italy, Israeli American spyware maker Paragon ...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2454">
+      <c r="A2454" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2454" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2454" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2454" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2454" t="inlineStr">
+        <is>
+          <t>It’s time to make a plan for nuclear waste</t>
+        </is>
+      </c>
+      <c r="F2454" t="inlineStr">
+        <is>
+          <t>https://www.technologyreview.com/2026/04/29/1136659/plan-nuclear-waste/</t>
+        </is>
+      </c>
+      <c r="G2454" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 08:00:00 +0000</t>
+        </is>
+      </c>
+      <c r="H2454" t="inlineStr">
+        <is>
+          <t>Today, nuclear energy enjoys a rare moment of support across the political spectrum in the US. Interest from tech companies that are scrambling to mee...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2455">
+      <c r="A2455" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2455" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2455" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2455" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2455" t="inlineStr">
+        <is>
+          <t>The Download: Musk and Altman’s legal showdown, and AI’s profit problem</t>
+        </is>
+      </c>
+      <c r="F2455" t="inlineStr">
+        <is>
+          <t>https://www.technologyreview.com/2026/04/28/1136479/the-download-musk-altman-openai-trial-ai-profit-problem/</t>
+        </is>
+      </c>
+      <c r="G2455" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 12:10:00 +0000</t>
+        </is>
+      </c>
+      <c r="H2455" t="inlineStr">
+        <is>
+          <t>This is today&amp;#8217;s edition of The Download, our weekday newsletter that provides a daily dose of what&amp;#8217;s going on in the world of technology. ...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2456">
+      <c r="A2456" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2456" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2456" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2456" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2456" t="inlineStr">
+        <is>
+          <t>Elon Musk and Sam Altman are going to court over OpenAI’s future</t>
+        </is>
+      </c>
+      <c r="F2456" t="inlineStr">
+        <is>
+          <t>https://www.technologyreview.com/2026/04/27/1136466/elon-musk-and-sam-altman-are-going-to-court-over-openais-future/</t>
+        </is>
+      </c>
+      <c r="G2456" t="inlineStr">
+        <is>
+          <t>Mon, 27 Apr 2026 22:52:57 +0000</t>
+        </is>
+      </c>
+      <c r="H2456" t="inlineStr">
+        <is>
+          <t>After a yearslong legal feud, Elon Musk and OpenAI CEO Sam Altman are heading to trial this week in Northern California in a case that could have swee...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2457">
+      <c r="A2457" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2457" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2457" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2457" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2457" t="inlineStr">
+        <is>
+          <t>The missing step between hype and profit</t>
+        </is>
+      </c>
+      <c r="F2457" t="inlineStr">
+        <is>
+          <t>https://www.technologyreview.com/2026/04/27/1136456/the-missing-step-between-hype-and-profit/</t>
+        </is>
+      </c>
+      <c r="G2457" t="inlineStr">
+        <is>
+          <t>Mon, 27 Apr 2026 16:13:41 +0000</t>
+        </is>
+      </c>
+      <c r="H2457" t="inlineStr">
+        <is>
+          <t>This story originally appeared in The Algorithm, our weekly newsletter on AI. To get stories like this in your inbox first, sign up here. In February,...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2458">
+      <c r="A2458" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2458" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2458" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2458" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2458" t="inlineStr">
+        <is>
+          <t>Rebuilding the data stack for AI</t>
+        </is>
+      </c>
+      <c r="F2458" t="inlineStr">
+        <is>
+          <t>https://www.technologyreview.com/2026/04/27/1136322/rebuilding-the-data-stack-for-ai/</t>
+        </is>
+      </c>
+      <c r="G2458" t="inlineStr">
+        <is>
+          <t>Mon, 27 Apr 2026 13:00:00 +0000</t>
+        </is>
+      </c>
+      <c r="H2458" t="inlineStr">
+        <is>
+          <t>Artificial intelligence may be dominating boardroom agendas, but many enterprises are discovering that the biggest obstacle to meaningful adoption is ...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2459">
+      <c r="A2459" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2459" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2459" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2459" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2459" t="inlineStr">
+        <is>
+          <t>The Download: DeepSeek’s latest AI breakthrough, and the race to build world models</t>
+        </is>
+      </c>
+      <c r="F2459" t="inlineStr">
+        <is>
+          <t>https://www.technologyreview.com/2026/04/27/1136438/the-download-deepseek-v4-ai-world-models/</t>
+        </is>
+      </c>
+      <c r="G2459" t="inlineStr">
+        <is>
+          <t>Mon, 27 Apr 2026 12:10:00 +0000</t>
+        </is>
+      </c>
+      <c r="H2459" t="inlineStr">
+        <is>
+          <t>This is today&amp;#8217;s edition of The Download, our weekday newsletter that provides a daily dose of what&amp;#8217;s going on in the world of technology. ...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2460">
+      <c r="A2460" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2460" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2460" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2460" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2460" t="inlineStr">
+        <is>
+          <t>Three reasons why DeepSeek’s new model matters</t>
+        </is>
+      </c>
+      <c r="F2460" t="inlineStr">
+        <is>
+          <t>https://www.technologyreview.com/2026/04/24/1136422/why-deepseeks-v4-matters/</t>
+        </is>
+      </c>
+      <c r="G2460" t="inlineStr">
+        <is>
+          <t>Fri, 24 Apr 2026 21:40:58 +0000</t>
+        </is>
+      </c>
+      <c r="H2460" t="inlineStr">
+        <is>
+          <t>On April 24, Chinese AI firm DeepSeek released a preview of V4, its long-awaited new flagship model. The model can process much longer prompts than it...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2461">
+      <c r="A2461" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2461" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2461" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2461" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2461" t="inlineStr">
+        <is>
+          <t>The Download: supercharged scams and studying AI healthcare</t>
+        </is>
+      </c>
+      <c r="F2461" t="inlineStr">
+        <is>
+          <t>https://www.technologyreview.com/2026/04/24/1136400/the-download-supercharged-scams-questionable-ai-healthcare/</t>
+        </is>
+      </c>
+      <c r="G2461" t="inlineStr">
+        <is>
+          <t>Fri, 24 Apr 2026 12:10:00 +0000</t>
+        </is>
+      </c>
+      <c r="H2461" t="inlineStr">
+        <is>
+          <t>This is today&amp;#8217;s edition of The Download, our weekday newsletter that provides a daily dose of what&amp;#8217;s going on in the world of technology. ...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2462">
+      <c r="A2462" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2462" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2462" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2462" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2462" t="inlineStr">
+        <is>
+          <t>The best VPN services for iPhone in 2026: Expert tested and reviewed</t>
+        </is>
+      </c>
+      <c r="F2462" t="inlineStr">
+        <is>
+          <t>https://www.zdnet.com/article/best-iphone-vpn/</t>
+        </is>
+      </c>
+      <c r="G2462" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 10:01:28 GMT</t>
+        </is>
+      </c>
+      <c r="H2462" t="inlineStr">
+        <is>
+          <t>Your iPhone content and web activities say a lot about you. Use one of our top tried-and-tested VPNs to keep your information private and to boost you...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2463">
+      <c r="A2463" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2463" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2463" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2463" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2463" t="inlineStr">
+        <is>
+          <t>Amazon Prime Day 2026 is likely coming earlier. Here's everything to know so far</t>
+        </is>
+      </c>
+      <c r="F2463" t="inlineStr">
+        <is>
+          <t>https://www.zdnet.com/article/amazon-prime-day-2026-faq/</t>
+        </is>
+      </c>
+      <c r="G2463" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 10:01:01 GMT</t>
+        </is>
+      </c>
+      <c r="H2463" t="inlineStr">
+        <is>
+          <t>Amazon's summer Prime Day event is on its way, but it may not be in July. Here's what you need to know right now.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2464">
+      <c r="A2464" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2464" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2464" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2464" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2464" t="inlineStr">
+        <is>
+          <t>The best Apple TV VPNs of 2026: Expert tested and reviewed</t>
+        </is>
+      </c>
+      <c r="F2464" t="inlineStr">
+        <is>
+          <t>https://www.zdnet.com/article/best-apple-tv-vpns/</t>
+        </is>
+      </c>
+      <c r="G2464" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 09:00:48 GMT</t>
+        </is>
+      </c>
+      <c r="H2464" t="inlineStr">
+        <is>
+          <t>Setting up a VPN on your Apple TV can be a nuisance, but with one of our top Apple TV VPNs, setup and streaming will take mere moments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2465">
+      <c r="A2465" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2465" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2465" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2465" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2465" t="inlineStr">
+        <is>
+          <t>Over 80% of US government agencies already use AI agents - and it's only the beginning</t>
+        </is>
+      </c>
+      <c r="F2465" t="inlineStr">
+        <is>
+          <t>https://www.zdnet.com/article/government-adoption-of-ai-agents-may-outpace-the-private-sector/</t>
+        </is>
+      </c>
+      <c r="G2465" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 19:12:00 GMT</t>
+        </is>
+      </c>
+      <c r="H2465" t="inlineStr">
+        <is>
+          <t>A new survey finds most government leaders believe that by 2030, the public sector will consist of humans and AI agents working together.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2466">
+      <c r="A2466" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2466" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2466" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2466" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2466" t="inlineStr">
+        <is>
+          <t>Microsoft finally open sources DOS 1.0 - and it's so much more than the code</t>
+        </is>
+      </c>
+      <c r="F2466" t="inlineStr">
+        <is>
+          <t>https://www.zdnet.com/article/microsoft-open-sources-dos-1-0-much-more-than-the-code/</t>
+        </is>
+      </c>
+      <c r="G2466" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 18:45:10 GMT</t>
+        </is>
+      </c>
+      <c r="H2466" t="inlineStr">
+        <is>
+          <t>Want a blast from the past? Microsoft just open-sourced its very first operating system, offering a rare insight into the PC's earliest days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2467">
+      <c r="A2467" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2467" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2467" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2467" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2467" t="inlineStr">
+        <is>
+          <t>I was not expecting a Razer keyboard to enhance my office productivity - here's how it did</t>
+        </is>
+      </c>
+      <c r="F2467" t="inlineStr">
+        <is>
+          <t>https://www.zdnet.com/article/razer-pro-type-ergo-keyboard-review/</t>
+        </is>
+      </c>
+      <c r="G2467" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 18:14:00 GMT</t>
+        </is>
+      </c>
+      <c r="H2467" t="inlineStr">
+        <is>
+          <t>Razer's Pro Type Ergo keyboard features a split ergonomic design and a plush wrist rest, while still being great for gaming.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2468">
+      <c r="A2468" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2468" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2468" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2468" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2468" t="inlineStr">
+        <is>
+          <t>User interfaces as we know them are dead - 4 ways to prep for 'disposable' UIs</t>
+        </is>
+      </c>
+      <c r="F2468" t="inlineStr">
+        <is>
+          <t>https://www.zdnet.com/article/user-interfaces-as-we-know-them-are-dead-4-ways-to-prep-for-disposable-uis/</t>
+        </is>
+      </c>
+      <c r="G2468" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 17:43:38 GMT</t>
+        </is>
+      </c>
+      <c r="H2468" t="inlineStr">
+        <is>
+          <t>UIs are evolving from the fixed, static screens we've viewed for decades to generated 'just-in-time' projection layers that appear as simple text boxe...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2469">
+      <c r="A2469" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2469" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2469" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2469" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2469" t="inlineStr">
+        <is>
+          <t>Want a free Apple Watch? T-Mobile will give you the SE 3 - how to get yours today</t>
+        </is>
+      </c>
+      <c r="F2469" t="inlineStr">
+        <is>
+          <t>https://www.zdnet.com/article/apple-watch-se-3-tmobile-deal/</t>
+        </is>
+      </c>
+      <c r="G2469" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 16:59:33 GMT</t>
+        </is>
+      </c>
+      <c r="H2469" t="inlineStr">
+        <is>
+          <t>The Apple Watch SE 3 is the latest refresh of Apple's entry-level smartwatch, and you can get one for free with a new smartwatch line on your T-Mobile...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2470">
+      <c r="A2470" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2470" t="inlineStr">
+        <is>
+          <t>ai_ml</t>
+        </is>
+      </c>
+      <c r="C2470" t="inlineStr">
+        <is>
+          <t>AI·ML</t>
+        </is>
+      </c>
+      <c r="D2470" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2470" t="inlineStr">
+        <is>
+          <t>Railway secures $100 million to challenge AWS with AI-native cloud infrastructure</t>
+        </is>
+      </c>
+      <c r="F2470" t="inlineStr">
+        <is>
+          <t>https://venturebeat.com/infrastructure/railway-secures-usd100-million-to-challenge-aws-with-ai-native-cloud</t>
+        </is>
+      </c>
+      <c r="G2470" t="inlineStr">
+        <is>
+          <t>Thu, 22 Jan 2026 14:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H2470" t="inlineStr">
+        <is>
+          <t>Railway, a San Francisco-based cloud platform that has quietly amassed two million developers without spending a dollar on marketing, announced Thursd...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2471">
+      <c r="A2471" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2471" t="inlineStr">
+        <is>
+          <t>ai_ml</t>
+        </is>
+      </c>
+      <c r="C2471" t="inlineStr">
+        <is>
+          <t>AI·ML</t>
+        </is>
+      </c>
+      <c r="D2471" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2471" t="inlineStr">
+        <is>
+          <t>Claude Code costs up to $200 a month. Goose does the same thing for free.</t>
+        </is>
+      </c>
+      <c r="F2471" t="inlineStr">
+        <is>
+          <t>https://venturebeat.com/infrastructure/claude-code-costs-up-to-usd200-a-month-goose-does-the-same-thing-for-free</t>
+        </is>
+      </c>
+      <c r="G2471" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 14:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H2471" t="inlineStr">
+        <is>
+          <t>The artificial intelligence coding revolution comes with a catch: it&amp;#x27;s expensive.Claude Code, Anthropic&amp;#x27;s terminal-based AI agent that can w...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2472">
+      <c r="A2472" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2472" t="inlineStr">
+        <is>
+          <t>ai_ml</t>
+        </is>
+      </c>
+      <c r="C2472" t="inlineStr">
+        <is>
+          <t>AI·ML</t>
+        </is>
+      </c>
+      <c r="D2472" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2472" t="inlineStr">
+        <is>
+          <t>Listen Labs raises $69M after viral billboard hiring stunt to scale AI customer interviews</t>
+        </is>
+      </c>
+      <c r="F2472" t="inlineStr">
+        <is>
+          <t>https://venturebeat.com/technology/listen-labs-raises-usd69m-after-viral-billboard-hiring-stunt-to-scale-ai</t>
+        </is>
+      </c>
+      <c r="G2472" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 14:01:00 GMT</t>
+        </is>
+      </c>
+      <c r="H2472" t="inlineStr">
+        <is>
+          <t>Alfred Wahlforss was running out of options. His startup, Listen Labs, needed to hire over 100 engineers, but competing against Mark Zuckerberg&amp;#x27;s...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2473">
+      <c r="A2473" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2473" t="inlineStr">
+        <is>
+          <t>ai_ml</t>
+        </is>
+      </c>
+      <c r="C2473" t="inlineStr">
+        <is>
+          <t>AI·ML</t>
+        </is>
+      </c>
+      <c r="D2473" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2473" t="inlineStr">
+        <is>
+          <t>Salesforce rolls out new Slackbot AI agent as it battles Microsoft and Google in workplace AI</t>
+        </is>
+      </c>
+      <c r="F2473" t="inlineStr">
+        <is>
+          <t>https://venturebeat.com/technology/salesforce-rolls-out-new-slackbot-ai-agent-as-it-battles-microsoft-and</t>
+        </is>
+      </c>
+      <c r="G2473" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 13:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H2473" t="inlineStr">
+        <is>
+          <t>Salesforce on Tuesday launched an entirely rebuilt version of Slackbot, the company&amp;#x27;s workplace assistant, transforming it from a simple notifica...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2474">
+      <c r="A2474" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2474" t="inlineStr">
+        <is>
+          <t>ai_ml</t>
+        </is>
+      </c>
+      <c r="C2474" t="inlineStr">
+        <is>
+          <t>AI·ML</t>
+        </is>
+      </c>
+      <c r="D2474" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2474" t="inlineStr">
+        <is>
+          <t>Anthropic launches Cowork, a Claude Desktop agent that works in your files — no coding required</t>
+        </is>
+      </c>
+      <c r="F2474" t="inlineStr">
+        <is>
+          <t>https://venturebeat.com/technology/anthropic-launches-cowork-a-claude-desktop-agent-that-works-in-your-files-no</t>
+        </is>
+      </c>
+      <c r="G2474" t="inlineStr">
+        <is>
+          <t>Mon, 12 Jan 2026 11:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="H2474" t="inlineStr">
+        <is>
+          <t>Anthropic released Cowork on Monday, a new AI agent capability that extends the power of its wildly successful Claude Code tool to non-technical users...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2475">
+      <c r="A2475" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2475" t="inlineStr">
+        <is>
+          <t>ai_ml</t>
+        </is>
+      </c>
+      <c r="C2475" t="inlineStr">
+        <is>
+          <t>AI·ML</t>
+        </is>
+      </c>
+      <c r="D2475" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2475" t="inlineStr">
+        <is>
+          <t>Nous Research's NousCoder-14B is an open-source coding model landing right in the Claude Code moment</t>
+        </is>
+      </c>
+      <c r="F2475" t="inlineStr">
+        <is>
+          <t>https://venturebeat.com/technology/nous-researchs-nouscoder-14b-is-an-open-source-coding-model-landing-right-in</t>
+        </is>
+      </c>
+      <c r="G2475" t="inlineStr">
+        <is>
+          <t>Wed, 07 Jan 2026 20:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H2475" t="inlineStr">
+        <is>
+          <t>Nous Research, the open-source artificial intelligence startup backed by crypto venture firm Paradigm, released a new competitive programming model on...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2476">
+      <c r="A2476" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2476" t="inlineStr">
+        <is>
+          <t>ai_ml</t>
+        </is>
+      </c>
+      <c r="C2476" t="inlineStr">
+        <is>
+          <t>AI·ML</t>
+        </is>
+      </c>
+      <c r="D2476" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2476" t="inlineStr">
+        <is>
+          <t>The creator of Claude Code just revealed his workflow, and developers are losing their minds</t>
+        </is>
+      </c>
+      <c r="F2476" t="inlineStr">
+        <is>
+          <t>https://venturebeat.com/technology/the-creator-of-claude-code-just-revealed-his-workflow-and-developers-are</t>
+        </is>
+      </c>
+      <c r="G2476" t="inlineStr">
+        <is>
+          <t>Mon, 05 Jan 2026 07:45:00 GMT</t>
+        </is>
+      </c>
+      <c r="H2476" t="inlineStr">
+        <is>
+          <t>When the creator of the world&amp;#x27;s most advanced coding agent speaks, Silicon Valley doesn&amp;#x27;t just listen — it takes notes.For the past week, th...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2477">
+      <c r="A2477" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2477" t="inlineStr">
+        <is>
+          <t>ai_ml</t>
+        </is>
+      </c>
+      <c r="C2477" t="inlineStr">
+        <is>
+          <t>AI·ML</t>
+        </is>
+      </c>
+      <c r="D2477" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2477" t="inlineStr">
+        <is>
+          <t>AI Weekly Issue #487: 100 years from now : The Allowance</t>
+        </is>
+      </c>
+      <c r="F2477" t="inlineStr">
+        <is>
+          <t>https://aiweekly.co/issues/100-years-from-now-the-allowance</t>
+        </is>
+      </c>
+      <c r="G2477" t="inlineStr">
+        <is>
+          <t>Sun, 26 Apr 2026 00:00:00 +0000</t>
+        </is>
+      </c>
+      <c r="H2477" t="inlineStr">
+        <is>
+          <t>This is 100 Years From Now, a weekly series. Once a week we skip a century and try to picture what life actually looks like when the stuff we're build...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2478">
+      <c r="A2478" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2478" t="inlineStr">
+        <is>
+          <t>ai_ml</t>
+        </is>
+      </c>
+      <c r="C2478" t="inlineStr">
+        <is>
+          <t>AI·ML</t>
+        </is>
+      </c>
+      <c r="D2478" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2478" t="inlineStr">
+        <is>
+          <t>AI Weekly Issue #486: Apple is replacing Tim Cook because of AI</t>
+        </is>
+      </c>
+      <c r="F2478" t="inlineStr">
+        <is>
+          <t>https://aiweekly.co/issues/apple-is-replacing-tim-cook-because-of-ai</t>
+        </is>
+      </c>
+      <c r="G2478" t="inlineStr">
+        <is>
+          <t>Wed, 22 Apr 2026 00:00:00 +0000</t>
+        </is>
+      </c>
+      <c r="H2478" t="inlineStr">
+        <is>
+          <t>Apple handed the next decade to a silicon engineer. Bezos hit $38B in five months. Brin came out of retirement to code. When the founders stop delegat...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2479">
+      <c r="A2479" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2479" t="inlineStr">
+        <is>
+          <t>ai_ml</t>
+        </is>
+      </c>
+      <c r="C2479" t="inlineStr">
+        <is>
+          <t>AI·ML</t>
+        </is>
+      </c>
+      <c r="D2479" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2479" t="inlineStr">
+        <is>
+          <t>AI Weekly Issue #485: When AI teaches AI, it teaches in secret</t>
+        </is>
+      </c>
+      <c r="F2479" t="inlineStr">
+        <is>
+          <t>https://aiweekly.co/issues/when-ai-teaches-ai-it-teaches-in-secret</t>
+        </is>
+      </c>
+      <c r="G2479" t="inlineStr">
+        <is>
+          <t>Sun, 19 Apr 2026 00:00:00 +0000</t>
+        </is>
+      </c>
+      <c r="H2479" t="inlineStr">
+        <is>
+          <t>Watch &amp;amp; Listen First
+Jensen Huang on Dwarkesh: The $4 Trillion Company · Listen on Spotify
+-&amp;gt; Huang on TPU competition, why Anthropic drove "10...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2480">
+      <c r="A2480" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2480" t="inlineStr">
+        <is>
+          <t>ai_ml</t>
+        </is>
+      </c>
+      <c r="C2480" t="inlineStr">
+        <is>
+          <t>AI·ML</t>
+        </is>
+      </c>
+      <c r="D2480" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2480" t="inlineStr">
+        <is>
+          <t>AI Weekly Issue #484: Your AI chats can be used against you in court</t>
+        </is>
+      </c>
+      <c r="F2480" t="inlineStr">
+        <is>
+          <t>https://aiweekly.co/issues/your-ai-chats-can-be-used-against-you-in-court</t>
+        </is>
+      </c>
+      <c r="G2480" t="inlineStr">
+        <is>
+          <t>Thu, 16 Apr 2026 00:00:00 +0000</t>
+        </is>
+      </c>
+      <c r="H2480" t="inlineStr">
+        <is>
+          <t>Quick Hits
+Chery sells humanoid robot to consumers for $42,000: The Chinese automaker ships the first mass-market humanoid. A car company is now a ro...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2481">
+      <c r="A2481" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2481" t="inlineStr">
+        <is>
+          <t>ai_ml</t>
+        </is>
+      </c>
+      <c r="C2481" t="inlineStr">
+        <is>
+          <t>AI·ML</t>
+        </is>
+      </c>
+      <c r="D2481" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2481" t="inlineStr">
+        <is>
+          <t>AI Weekly Issue #483: 100 years from now : The Ghost in the Contract</t>
+        </is>
+      </c>
+      <c r="F2481" t="inlineStr">
+        <is>
+          <t>https://aiweekly.co/issues/100-years-from-now-the-ghost-in-the-contract</t>
+        </is>
+      </c>
+      <c r="G2481" t="inlineStr">
+        <is>
+          <t>Mon, 13 Apr 2026 00:00:00 +0000</t>
+        </is>
+      </c>
+      <c r="H2481" t="inlineStr">
+        <is>
+          <t>This is 100 Years From Now, a weekly series. Once a week, we skip ahead a century and imagine ordinary life in a world that's had a hundred years to a...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2482">
+      <c r="A2482" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2482" t="inlineStr">
+        <is>
+          <t>ai_ml</t>
+        </is>
+      </c>
+      <c r="C2482" t="inlineStr">
+        <is>
+          <t>AI·ML</t>
+        </is>
+      </c>
+      <c r="D2482" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2482" t="inlineStr">
+        <is>
+          <t>AI Weekly Issue #482: AI is now the weapon and the target : things are getting really serious</t>
+        </is>
+      </c>
+      <c r="F2482" t="inlineStr">
+        <is>
+          <t>https://aiweekly.co/issues/ai-is-now-the-weapon-and-the-target-things-are-getting</t>
+        </is>
+      </c>
+      <c r="G2482" t="inlineStr">
+        <is>
+          <t>Fri, 10 Apr 2026 00:00:00 +0000</t>
+        </is>
+      </c>
+      <c r="H2482" t="inlineStr">
+        <is>
+          <t>Four attack vectors, one week. The npm packages your app depends on were compromised by a nation-state. A data center got its GPS coordinates publishe...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2483">
+      <c r="A2483" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2483" t="inlineStr">
+        <is>
+          <t>ai_ml</t>
+        </is>
+      </c>
+      <c r="C2483" t="inlineStr">
+        <is>
+          <t>AI·ML</t>
+        </is>
+      </c>
+      <c r="D2483" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2483" t="inlineStr">
+        <is>
+          <t>AI Weekly Issue #481: Musk wants Altman fired, Anthropic passes OpenAI, Meta goes closed</t>
+        </is>
+      </c>
+      <c r="F2483" t="inlineStr">
+        <is>
+          <t>https://aiweekly.co/issues/musk-wants-altman-fired-anthropic-passes-openai-meta-goes</t>
+        </is>
+      </c>
+      <c r="G2483" t="inlineStr">
+        <is>
+          <t>Thu, 09 Apr 2026 00:00:00 +0000</t>
+        </is>
+      </c>
+      <c r="H2483" t="inlineStr">
+        <is>
+          <t>Three seismic shifts in one week. Anthropic's revenue run rate passed OpenAI's — $30 billion to $24 billion — powered by enterprise demand that double...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2484">
+      <c r="A2484" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2484" t="inlineStr">
+        <is>
+          <t>ai_ml</t>
+        </is>
+      </c>
+      <c r="C2484" t="inlineStr">
+        <is>
+          <t>AI·ML</t>
+        </is>
+      </c>
+      <c r="D2484" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2484" t="inlineStr">
+        <is>
+          <t>AI Weekly Issue #480: Monday Edition : npm compromised by North Korea, Iran targets AI data centers, and nobody wants OpenAI stock</t>
+        </is>
+      </c>
+      <c r="F2484" t="inlineStr">
+        <is>
+          <t>https://aiweekly.co/issues/monday-edition-npm-compromised-by-north-korea-iran-targets</t>
+        </is>
+      </c>
+      <c r="G2484" t="inlineStr">
+        <is>
+          <t>Mon, 06 Apr 2026 00:00:00 +0000</t>
+        </is>
+      </c>
+      <c r="H2484" t="inlineStr">
+        <is>
+          <t>Three days, three threat vectors nobody had on their bingo card. North Korea compromised the npm package your app probably depends on. Iran published ...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2485">
+      <c r="A2485" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2485" t="inlineStr">
+        <is>
+          <t>ai_ml</t>
+        </is>
+      </c>
+      <c r="C2485" t="inlineStr">
+        <is>
+          <t>AI·ML</t>
+        </is>
+      </c>
+      <c r="D2485" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2485" t="inlineStr">
+        <is>
+          <t>AI needs a strong data fabric to deliver business value</t>
+        </is>
+      </c>
+      <c r="F2485" t="inlineStr">
+        <is>
+          <t>https://www.technologyreview.com/2026/04/22/1135295/ai-needs-a-strong-data-fabric-to-deliver-business-value/</t>
+        </is>
+      </c>
+      <c r="G2485" t="inlineStr">
+        <is>
+          <t>Wed, 22 Apr 2026 10:05:06 +0000</t>
+        </is>
+      </c>
+      <c r="H2485" t="inlineStr">
+        <is>
+          <t>Artificial intelligence is moving quickly in the enterprise, from experimentation to everyday use. Organizations are deploying copilots, agents, and p...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2486">
+      <c r="A2486" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2486" t="inlineStr">
+        <is>
+          <t>ai_ml</t>
+        </is>
+      </c>
+      <c r="C2486" t="inlineStr">
+        <is>
+          <t>AI·ML</t>
+        </is>
+      </c>
+      <c r="D2486" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2486" t="inlineStr">
+        <is>
+          <t>10 Things That Matter in AI Right Now</t>
+        </is>
+      </c>
+      <c r="F2486" t="inlineStr">
+        <is>
+          <t>https://www.technologyreview.com/2026/04/21/1135643/10-ai-artificial-intelligence-trends-technologies-research-2026/</t>
+        </is>
+      </c>
+      <c r="G2486" t="inlineStr">
+        <is>
+          <t>Tue, 21 Apr 2026 20:45:00 +0000</t>
+        </is>
+      </c>
+      <c r="H2486" t="inlineStr"/>
+    </row>
+    <row r="2487">
+      <c r="A2487" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2487" t="inlineStr">
+        <is>
+          <t>ai_ml</t>
+        </is>
+      </c>
+      <c r="C2487" t="inlineStr">
+        <is>
+          <t>AI·ML</t>
+        </is>
+      </c>
+      <c r="D2487" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2487" t="inlineStr">
+        <is>
+          <t>LLMs+</t>
+        </is>
+      </c>
+      <c r="F2487" t="inlineStr">
+        <is>
+          <t>https://www.technologyreview.com/2026/04/21/1135645/llm-large-language-models-ai/</t>
+        </is>
+      </c>
+      <c r="G2487" t="inlineStr">
+        <is>
+          <t>Tue, 21 Apr 2026 20:45:00 +0000</t>
+        </is>
+      </c>
+      <c r="H2487" t="inlineStr">
+        <is>
+          <t>When ChatGPT launched as an experimental prototype in late 2022, OpenAI’s chatbot became an everyday everything app for hundreds of millions of people...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2488">
+      <c r="A2488" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2488" t="inlineStr">
+        <is>
+          <t>ai_ml</t>
+        </is>
+      </c>
+      <c r="C2488" t="inlineStr">
+        <is>
+          <t>AI·ML</t>
+        </is>
+      </c>
+      <c r="D2488" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2488" t="inlineStr">
+        <is>
+          <t>Supercharged scams</t>
+        </is>
+      </c>
+      <c r="F2488" t="inlineStr">
+        <is>
+          <t>https://www.technologyreview.com/2026/04/21/1135647/supercharged-scams-ai-artificial-intelligence/</t>
+        </is>
+      </c>
+      <c r="G2488" t="inlineStr">
+        <is>
+          <t>Tue, 21 Apr 2026 20:45:00 +0000</t>
+        </is>
+      </c>
+      <c r="H2488" t="inlineStr">
+        <is>
+          <t>When ChatGPT was released to the public in late 2022, it opened people’s eyes to how easily generative AI could churn out vast amounts of human-seemin...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2489" t="inlineStr">
+        <is>
+          <t>ai_ml</t>
+        </is>
+      </c>
+      <c r="C2489" t="inlineStr">
+        <is>
+          <t>AI·ML</t>
+        </is>
+      </c>
+      <c r="D2489" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2489" t="inlineStr">
+        <is>
+          <t>World models</t>
+        </is>
+      </c>
+      <c r="F2489" t="inlineStr">
+        <is>
+          <t>https://www.technologyreview.com/2026/04/21/1135650/world-models-ai-artificial-intelligence/</t>
+        </is>
+      </c>
+      <c r="G2489" t="inlineStr">
+        <is>
+          <t>Tue, 21 Apr 2026 20:45:00 +0000</t>
+        </is>
+      </c>
+      <c r="H2489" t="inlineStr">
+        <is>
+          <t>AI systems have already gained impressive mastery over the digital world, but the physical world is still humanity’s domain. As it turns out, building...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2490">
+      <c r="A2490" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2490" t="inlineStr">
+        <is>
+          <t>ai_ml</t>
+        </is>
+      </c>
+      <c r="C2490" t="inlineStr">
+        <is>
+          <t>AI·ML</t>
+        </is>
+      </c>
+      <c r="D2490" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2490" t="inlineStr">
+        <is>
+          <t>Weaponized deepfakes</t>
+        </is>
+      </c>
+      <c r="F2490" t="inlineStr">
+        <is>
+          <t>https://www.technologyreview.com/2026/04/21/1135652/weaponized-deepfakes-ai-artificial-intelligence/</t>
+        </is>
+      </c>
+      <c r="G2490" t="inlineStr">
+        <is>
+          <t>Tue, 21 Apr 2026 20:45:00 +0000</t>
+        </is>
+      </c>
+      <c r="H2490" t="inlineStr">
+        <is>
+          <t>For years, experts have warned that deepfakes—AI-generated videos, images, or audio recordings of people doing or saying things they haven’t actually ...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2491">
+      <c r="A2491" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2491" t="inlineStr">
+        <is>
+          <t>ai_ml</t>
+        </is>
+      </c>
+      <c r="C2491" t="inlineStr">
+        <is>
+          <t>AI·ML</t>
+        </is>
+      </c>
+      <c r="D2491" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2491" t="inlineStr">
+        <is>
+          <t>When Robots Have Their ChatGPT Moment, Remember These Pincers</t>
+        </is>
+      </c>
+      <c r="F2491" t="inlineStr">
+        <is>
+          <t>https://www.wired.com/story/when-robots-have-their-chatgpt-moment-remember-these-pincers/</t>
+        </is>
+      </c>
+      <c r="G2491" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 10:00:00 +0000</t>
+        </is>
+      </c>
+      <c r="H2491" t="inlineStr">
+        <is>
+          <t>From sorting chicken nuggets to screwing in light bulbs, Eka’s robots are eerily lifelike. But do they have real physical smarts?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2492">
+      <c r="A2492" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2492" t="inlineStr">
+        <is>
+          <t>ai_ml</t>
+        </is>
+      </c>
+      <c r="C2492" t="inlineStr">
+        <is>
+          <t>AI·ML</t>
+        </is>
+      </c>
+      <c r="D2492" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2492" t="inlineStr">
+        <is>
+          <t>How AI Could Help Combat Antibiotic Resistance</t>
+        </is>
+      </c>
+      <c r="F2492" t="inlineStr">
+        <is>
+          <t>https://www.wired.com/story/wired-health-2026-tackling-antimicrobial-resistance-ara-darzi/</t>
+        </is>
+      </c>
+      <c r="G2492" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 09:00:00 +0000</t>
+        </is>
+      </c>
+      <c r="H2492" t="inlineStr">
+        <is>
+          <t>At WIRED Health, British surgeon Ara Darzi said AI is set to transform the diagnosis and treatment of drug-resistant infections. But a lack of incenti...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2493">
+      <c r="A2493" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2493" t="inlineStr">
+        <is>
+          <t>ai_ml</t>
+        </is>
+      </c>
+      <c r="C2493" t="inlineStr">
+        <is>
+          <t>AI·ML</t>
+        </is>
+      </c>
+      <c r="D2493" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2493" t="inlineStr">
+        <is>
+          <t>OpenAI Really Wants Codex to Shut Up About Goblins</t>
+        </is>
+      </c>
+      <c r="F2493" t="inlineStr">
+        <is>
+          <t>https://www.wired.com/story/openai-really-wants-codex-to-shut-up-about-goblins/</t>
+        </is>
+      </c>
+      <c r="G2493" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 23:45:05 +0000</t>
+        </is>
+      </c>
+      <c r="H2493" t="inlineStr">
+        <is>
+          <t>“Never talk about goblins, gremlins, raccoons, trolls, ogres, pigeons, or other animals or creatures unless it is absolutely and unambiguously relevan...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2494">
+      <c r="A2494" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2494" t="inlineStr">
+        <is>
+          <t>ai_ml</t>
+        </is>
+      </c>
+      <c r="C2494" t="inlineStr">
+        <is>
+          <t>AI·ML</t>
+        </is>
+      </c>
+      <c r="D2494" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2494" t="inlineStr">
+        <is>
+          <t>Elon Musk Testifies That He Started OpenAI to Prevent a ‘Terminator Outcome’</t>
+        </is>
+      </c>
+      <c r="F2494" t="inlineStr">
+        <is>
+          <t>https://www.wired.com/story/model-behavior-elon-musk-testifies-at-musk-v-altman-trial/</t>
+        </is>
+      </c>
+      <c r="G2494" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 21:35:17 +0000</t>
+        </is>
+      </c>
+      <c r="H2494" t="inlineStr">
+        <is>
+          <t>The judge also warned Musk and Sam Altman to curb their “propensity to use social media to make things worse outside the courtroom” after both sides t...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2495">
+      <c r="A2495" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2495" t="inlineStr">
+        <is>
+          <t>ai_ml</t>
+        </is>
+      </c>
+      <c r="C2495" t="inlineStr">
+        <is>
+          <t>AI·ML</t>
+        </is>
+      </c>
+      <c r="D2495" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2495" t="inlineStr">
+        <is>
+          <t>‘It’s Undignified’: Hundreds of Workers Training Meta’s AI Could Be Laid Off</t>
+        </is>
+      </c>
+      <c r="F2495" t="inlineStr">
+        <is>
+          <t>https://www.wired.com/story/meta-covalen-ai-workers-layoffs/</t>
+        </is>
+      </c>
+      <c r="G2495" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 18:36:47 +0000</t>
+        </is>
+      </c>
+      <c r="H2495" t="inlineStr">
+        <is>
+          <t>More than 700 people working for a Meta contractor in Ireland are at risk of losing their jobs, documents show.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2496">
+      <c r="A2496" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2496" t="inlineStr">
+        <is>
+          <t>ai_ml</t>
+        </is>
+      </c>
+      <c r="C2496" t="inlineStr">
+        <is>
+          <t>AI·ML</t>
+        </is>
+      </c>
+      <c r="D2496" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2496" t="inlineStr">
+        <is>
+          <t>The Race Is on to Keep AI Agents From Running Wild With Your Credit Cards</t>
+        </is>
+      </c>
+      <c r="F2496" t="inlineStr">
+        <is>
+          <t>https://www.wired.com/story/the-race-is-on-to-keep-ai-agents-from-running-wild-with-your-credit-cards/</t>
+        </is>
+      </c>
+      <c r="G2496" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 13:00:00 +0000</t>
+        </is>
+      </c>
+      <c r="H2496" t="inlineStr">
+        <is>
+          <t>AI agents may soon be buying your stuff for you. The FIDO Alliance has teamed up with Google and Mastercard to try to ensure that shopping in the near...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2497">
+      <c r="A2497" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2497" t="inlineStr">
+        <is>
+          <t>ai_ml</t>
+        </is>
+      </c>
+      <c r="C2497" t="inlineStr">
+        <is>
+          <t>AI·ML</t>
+        </is>
+      </c>
+      <c r="D2497" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2497" t="inlineStr">
+        <is>
+          <t>The Bloomberg Terminal Is Getting an AI Makeover, Like It or Not</t>
+        </is>
+      </c>
+      <c r="F2497" t="inlineStr">
+        <is>
+          <t>https://www.wired.com/story/the-bloomberg-terminal-is-getting-an-ai-makeover-like-it-or-not/</t>
+        </is>
+      </c>
+      <c r="G2497" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 08:30:00 +0000</t>
+        </is>
+      </c>
+      <c r="H2497" t="inlineStr">
+        <is>
+          <t>WIRED spoke with Bloomberg’s chief technology officer about the big, chatbot-style changes coming to the iconic platform for traders.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2498">
+      <c r="A2498" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2498" t="inlineStr">
+        <is>
+          <t>ai_ml</t>
+        </is>
+      </c>
+      <c r="C2498" t="inlineStr">
+        <is>
+          <t>AI·ML</t>
+        </is>
+      </c>
+      <c r="D2498" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2498" t="inlineStr">
+        <is>
+          <t>Some Musk v. Altman Jurors Don't Like Elon Musk</t>
+        </is>
+      </c>
+      <c r="F2498" t="inlineStr">
+        <is>
+          <t>https://www.wired.com/story/some-musk-v-altman-jurors-dont-like-elon-musk/</t>
+        </is>
+      </c>
+      <c r="G2498" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 00:39:30 +0000</t>
+        </is>
+      </c>
+      <c r="H2498" t="inlineStr">
+        <is>
+          <t>Musk’s lawsuit challenges OpenAI’s evolution under Sam Altman. But during jury selection, several potential jurors voiced negative views of Musk himse...</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/storage/news_db.xlsx
+++ b/storage/news_db.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2498"/>
+  <dimension ref="A1:H2639"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -77047,7 +77047,6 @@
           <t>Wed, 29 Apr 2026 20:20:28 +0900</t>
         </is>
       </c>
-      <c r="H2382" t="inlineStr"/>
     </row>
     <row r="2383">
       <c r="A2383" t="inlineStr">
@@ -77085,7 +77084,6 @@
           <t>Wed, 29 Apr 2026 20:18:41 +0900</t>
         </is>
       </c>
-      <c r="H2383" t="inlineStr"/>
     </row>
     <row r="2384">
       <c r="A2384" t="inlineStr">
@@ -77123,7 +77121,6 @@
           <t>Wed, 29 Apr 2026 20:18:14 +0900</t>
         </is>
       </c>
-      <c r="H2384" t="inlineStr"/>
     </row>
     <row r="2385">
       <c r="A2385" t="inlineStr">
@@ -77161,7 +77158,6 @@
           <t>Wed, 29 Apr 2026 20:00:04 +0900</t>
         </is>
       </c>
-      <c r="H2385" t="inlineStr"/>
     </row>
     <row r="2386">
       <c r="A2386" t="inlineStr">
@@ -77199,7 +77195,6 @@
           <t>Wed, 29 Apr 2026 19:12:40 +0900</t>
         </is>
       </c>
-      <c r="H2386" t="inlineStr"/>
     </row>
     <row r="2387">
       <c r="A2387" t="inlineStr">
@@ -77237,7 +77232,6 @@
           <t>Wed, 29 Apr 2026 18:23:26 +0900</t>
         </is>
       </c>
-      <c r="H2387" t="inlineStr"/>
     </row>
     <row r="2388">
       <c r="A2388" t="inlineStr">
@@ -77275,7 +77269,6 @@
           <t>Wed, 29 Apr 2026 18:22:00 +0900</t>
         </is>
       </c>
-      <c r="H2388" t="inlineStr"/>
     </row>
     <row r="2389">
       <c r="A2389" t="inlineStr">
@@ -77313,7 +77306,6 @@
           <t>Wed, 29 Apr 2026 18:18:16 +0900</t>
         </is>
       </c>
-      <c r="H2389" t="inlineStr"/>
     </row>
     <row r="2390">
       <c r="A2390" t="inlineStr">
@@ -77687,7 +77679,6 @@
           <t>2026-04-29 19:59:04</t>
         </is>
       </c>
-      <c r="H2398" t="inlineStr"/>
     </row>
     <row r="2399">
       <c r="A2399" t="inlineStr">
@@ -81382,7 +81373,6 @@
           <t>Tue, 21 Apr 2026 20:45:00 +0000</t>
         </is>
       </c>
-      <c r="H2486" t="inlineStr"/>
     </row>
     <row r="2487">
       <c r="A2487" t="inlineStr">
@@ -81885,6 +81875,5884 @@
       <c r="H2498" t="inlineStr">
         <is>
           <t>Musk’s lawsuit challenges OpenAI’s evolution under Sam Altman. But during jury selection, several potential jurors voiced negative views of Musk himse...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2499">
+      <c r="A2499" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2499" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2499" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2499" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2499" t="inlineStr">
+        <is>
+          <t>배우 임윤아, 새 얼굴 선정…'르무통' 국민 신발 도약 나선다</t>
+        </is>
+      </c>
+      <c r="F2499" t="inlineStr">
+        <is>
+          <t>https://www.hankyung.com/article/2026043084227</t>
+        </is>
+      </c>
+      <c r="G2499" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 13:28:22 +0900</t>
+        </is>
+      </c>
+      <c r="H2499" t="inlineStr"/>
+    </row>
+    <row r="2500">
+      <c r="A2500" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2500" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2500" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2500" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2500" t="inlineStr">
+        <is>
+          <t>로봇 훈련시켜 하루에 6만건씩 데이터 싹쓸이…'데이터 제국' 구축하는 中 [차이나 워치]</t>
+        </is>
+      </c>
+      <c r="F2500" t="inlineStr">
+        <is>
+          <t>https://www.hankyung.com/article/202604308395i</t>
+        </is>
+      </c>
+      <c r="G2500" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 13:14:53 +0900</t>
+        </is>
+      </c>
+      <c r="H2500" t="inlineStr"/>
+    </row>
+    <row r="2501">
+      <c r="A2501" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2501" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2501" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2501" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2501" t="inlineStr">
+        <is>
+          <t>'넥스트 라부부' 실종…해외 성장에 제동 걸린 팝마트</t>
+        </is>
+      </c>
+      <c r="F2501" t="inlineStr">
+        <is>
+          <t>https://www.hankyung.com/article/202604308201i</t>
+        </is>
+      </c>
+      <c r="G2501" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 11:45:56 +0900</t>
+        </is>
+      </c>
+      <c r="H2501" t="inlineStr"/>
+    </row>
+    <row r="2502">
+      <c r="A2502" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2502" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2502" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2502" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2502" t="inlineStr">
+        <is>
+          <t>매파로 돌변한 美 FOMC…美 금리인하 사이클 종료 시사 [심성미의 중앙은행 워치]</t>
+        </is>
+      </c>
+      <c r="F2502" t="inlineStr">
+        <is>
+          <t>https://www.hankyung.com/article/202604306993i</t>
+        </is>
+      </c>
+      <c r="G2502" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 11:12:53 +0900</t>
+        </is>
+      </c>
+      <c r="H2502" t="inlineStr"/>
+    </row>
+    <row r="2503">
+      <c r="A2503" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2503" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2503" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2503" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2503" t="inlineStr">
+        <is>
+          <t>한국맥도날드, 지난해 매출 1조4310억원…전년비 14.5% 증가</t>
+        </is>
+      </c>
+      <c r="F2503" t="inlineStr">
+        <is>
+          <t>https://www.hankyung.com/article/202604308082g</t>
+        </is>
+      </c>
+      <c r="G2503" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 11:10:20 +0900</t>
+        </is>
+      </c>
+      <c r="H2503" t="inlineStr"/>
+    </row>
+    <row r="2504">
+      <c r="A2504" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2504" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2504" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2504" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2504" t="inlineStr">
+        <is>
+          <t>변우석이 새긴 '킵워킹'…조니워커 블루 각인 서비스 내놔</t>
+        </is>
+      </c>
+      <c r="F2504" t="inlineStr">
+        <is>
+          <t>https://www.hankyung.com/article/202604307206i</t>
+        </is>
+      </c>
+      <c r="G2504" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 11:00:01 +0900</t>
+        </is>
+      </c>
+      <c r="H2504" t="inlineStr"/>
+    </row>
+    <row r="2505">
+      <c r="A2505" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2505" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2505" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2505" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2505" t="inlineStr">
+        <is>
+          <t>중견련 "중견기업 향한 적시 금융지원 필요"</t>
+        </is>
+      </c>
+      <c r="F2505" t="inlineStr">
+        <is>
+          <t>https://www.hankyung.com/article/202604307993i</t>
+        </is>
+      </c>
+      <c r="G2505" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 10:51:06 +0900</t>
+        </is>
+      </c>
+      <c r="H2505" t="inlineStr"/>
+    </row>
+    <row r="2506">
+      <c r="A2506" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2506" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2506" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2506" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2506" t="inlineStr">
+        <is>
+          <t>SSG닷컴 손잡은 국민은행, 고금리 콜라보 예·적금 출시</t>
+        </is>
+      </c>
+      <c r="F2506" t="inlineStr">
+        <is>
+          <t>https://www.hankyung.com/article/202604307861i</t>
+        </is>
+      </c>
+      <c r="G2506" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 10:29:24 +0900</t>
+        </is>
+      </c>
+      <c r="H2506" t="inlineStr"/>
+    </row>
+    <row r="2507">
+      <c r="A2507" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2507" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2507" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2507" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2507" t="inlineStr">
+        <is>
+          <t>서울 아파트 폭등 잡겠다고 난리치는 사이…무너지는 빌라·상가 [기자24시]</t>
+        </is>
+      </c>
+      <c r="F2507" t="inlineStr">
+        <is>
+          <t>https://www.mk.co.kr/news/realestate/12032238</t>
+        </is>
+      </c>
+      <c r="G2507" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 14:24:18 +09:00</t>
+        </is>
+      </c>
+      <c r="H2507" t="inlineStr">
+        <is>
+          <t>정부가 연일 집값을 잡기 위한 대책을 쏟아내고 있다. 언뜻 보면 부동산 시장이 과열됐다는 착각이 든다. 실상은 그렇지 않다. 가격 급등을 겪은 건 서울과 수도권 일부 지역의 아파트..</t>
+        </is>
+      </c>
+    </row>
+    <row r="2508">
+      <c r="A2508" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2508" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2508" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2508" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2508" t="inlineStr">
+        <is>
+          <t>“복지 사각지대 해소”…한국남부발전, 부산사회복지공동모금회에 1500만원 기부</t>
+        </is>
+      </c>
+      <c r="F2508" t="inlineStr">
+        <is>
+          <t>https://www.mk.co.kr/news/business/12032236</t>
+        </is>
+      </c>
+      <c r="G2508" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 14:22:04 +09:00</t>
+        </is>
+      </c>
+      <c r="H2508" t="inlineStr">
+        <is>
+          <t>부산혁신도시 이전공공기관 합동  2026년 지역융화사업 본격 추진 뇌병변 장애 아동·청소년 문화체험  소외계층 1000가구 생필품 지원한국남부발전이 지역사회와의 상생을 위한 ‘20..</t>
+        </is>
+      </c>
+    </row>
+    <row r="2509">
+      <c r="A2509" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2509" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2509" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2509" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2509" t="inlineStr">
+        <is>
+          <t>[단독]거래소 이사장, ‘AI 유니콘’ 코스닥 영입 나선다…내달 4일 CEO들과 간담회</t>
+        </is>
+      </c>
+      <c r="F2509" t="inlineStr">
+        <is>
+          <t>https://www.mk.co.kr/news/stock/12032234</t>
+        </is>
+      </c>
+      <c r="G2509" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 14:17:05 +09:00</t>
+        </is>
+      </c>
+      <c r="H2509" t="inlineStr">
+        <is>
+          <t>유망 비상장 AI기업 코스닥 상장 설득 시장 재편과 저불어 혁신기업 유치 본격화정은보 한국거래소 이사장이 코스닥시장 부양을 위해 국내 대표 인공지능(AI) 기업 유치전에 직접 나섰..</t>
+        </is>
+      </c>
+    </row>
+    <row r="2510">
+      <c r="A2510" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2510" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2510" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2510" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2510" t="inlineStr">
+        <is>
+          <t>서울 공시지가, 전년 대비 평균 4.9% 상승</t>
+        </is>
+      </c>
+      <c r="F2510" t="inlineStr">
+        <is>
+          <t>https://www.mk.co.kr/news/realestate/12032233</t>
+        </is>
+      </c>
+      <c r="G2510" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 14:16:54 +09:00</t>
+        </is>
+      </c>
+      <c r="H2510" t="inlineStr">
+        <is>
+          <t>서울 평균 땅값, 지난해 대비 4.9% 상승 가장 많이 오른 자치구는 용산구…9.2%↑ 가장 비싼 땅 23년째 명동…평당 6억2000만원서울시의 올해 개별공시지가가 지난해에 비해 ..</t>
+        </is>
+      </c>
+    </row>
+    <row r="2511">
+      <c r="A2511" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2511" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2511" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2511" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2511" t="inlineStr">
+        <is>
+          <t>GH, 하남교산 A-3블록 1100세대 사업계획승인…주택 공급‘본궤도’</t>
+        </is>
+      </c>
+      <c r="F2511" t="inlineStr">
+        <is>
+          <t>https://www.mk.co.kr/news/society/12032230</t>
+        </is>
+      </c>
+      <c r="G2511" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 14:11:42 +09:00</t>
+        </is>
+      </c>
+      <c r="H2511" t="inlineStr">
+        <is>
+          <t>경기주택도시공사(GH)가 하남교산 공공주택지구 A-3블록 통합공공임대주택 건립 사업에 대한 사업계획승인이 고시됨에 따라 주택공급 사업이 본궤도에 올랐다. 30일 GH에 따르면 이번..</t>
+        </is>
+      </c>
+    </row>
+    <row r="2512">
+      <c r="A2512" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2512" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2512" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2512" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2512" t="inlineStr">
+        <is>
+          <t>경과원, 평택시 중소기업 역량강화 사업 추진…최대 2700만원 지원</t>
+        </is>
+      </c>
+      <c r="F2512" t="inlineStr">
+        <is>
+          <t>https://www.mk.co.kr/news/society/12032229</t>
+        </is>
+      </c>
+      <c r="G2512" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 14:10:06 +09:00</t>
+        </is>
+      </c>
+      <c r="H2512" t="inlineStr">
+        <is>
+          <t>경기도경제과학진흥원이 평택시와 함께 ‘2026년 평택시 중소기업 역량강화 지원사업’ 참여 기업을 다음달 18일까지 모집한다고 밝혔다. 이번 사업은 경기 위축과 대외 환경 불확실성 ..</t>
+        </is>
+      </c>
+    </row>
+    <row r="2513">
+      <c r="A2513" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2513" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2513" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2513" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2513" t="inlineStr">
+        <is>
+          <t>“알아서 집 찾아준다”… 빅밸류, AI 부동산 비서 ‘복덕방 가재’ 출시</t>
+        </is>
+      </c>
+      <c r="F2513" t="inlineStr">
+        <is>
+          <t>https://www.mk.co.kr/news/realestate/12032226</t>
+        </is>
+      </c>
+      <c r="G2513" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 14:09:53 +09:00</t>
+        </is>
+      </c>
+      <c r="H2513" t="inlineStr">
+        <is>
+          <t>데이터테크 기업 빅밸류는 AI(인공지능) 부동산 상담 에이전트 ‘복덕방 가재’를 선보인다고 30일 밝혔다. 우선 홈페이지 내 신규 메뉴인 ‘실험실’에 이번 상담 서비스를 넣었다. ..</t>
+        </is>
+      </c>
+    </row>
+    <row r="2514">
+      <c r="A2514" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2514" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2514" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2514" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2514" t="inlineStr">
+        <is>
+          <t>크루즈 켠 채 졸음운전…경찰관 숨진 참사에도 집행유예</t>
+        </is>
+      </c>
+      <c r="F2514" t="inlineStr">
+        <is>
+          <t>https://www.mk.co.kr/news/society/12032224</t>
+        </is>
+      </c>
+      <c r="G2514" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 14:08:32 +09:00</t>
+        </is>
+      </c>
+      <c r="H2514" t="inlineStr">
+        <is>
+          <t>졸음운전·과속으로 사고 수습 현장 덮쳐 순직 경찰관 포함 2명 숨져고속도로 사고 수습 현장을 덮쳐 경찰관과 견인기사 등 2명을 숨지게 한 30대 운전자에게 1심 법원이 집행유예를 ..</t>
+        </is>
+      </c>
+    </row>
+    <row r="2515">
+      <c r="A2515" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2515" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2515" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2515" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2515" t="inlineStr">
+        <is>
+          <t>李대통령 &amp;quot;인면수심의 가짜뉴스·모욕적 댓글, 엄벌해 마땅&amp;quot;</t>
+        </is>
+      </c>
+      <c r="F2515" t="inlineStr">
+        <is>
+          <t>https://news.einfomax.co.kr/news/articleView.html?idxno=4412679</t>
+        </is>
+      </c>
+      <c r="G2515" t="inlineStr">
+        <is>
+          <t>2026-04-30 14:25:03</t>
+        </is>
+      </c>
+      <c r="H2515" t="inlineStr">
+        <is>
+          <t>이재명 대통령은 30일 "인면수심의 가짜뉴스, 모욕적 댓글은 엄벌해 마땅하다"고 밝혔다.이 대통령은 이날 엑스(X·옛 트위터)에 '세월호·이태원 참사 피해자와 유가족을 대상으로 여러 차례 허위 사실을 유포하고 비방하는 글을 올린 남성이 경찰에 구속됐다'는 기사를 공유하...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2516">
+      <c r="A2516" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2516" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2516" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2516" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2516" t="inlineStr">
+        <is>
+          <t>李대통령 &amp;quot;일부 조직 노동자, 나만 살겠다고 과도한 요구 안돼&amp;quot;(종합)</t>
+        </is>
+      </c>
+      <c r="F2516" t="inlineStr">
+        <is>
+          <t>https://news.einfomax.co.kr/news/articleView.html?idxno=4412678</t>
+        </is>
+      </c>
+      <c r="G2516" t="inlineStr">
+        <is>
+          <t>2026-04-30 14:22:11</t>
+        </is>
+      </c>
+      <c r="H2516" t="inlineStr">
+        <is>
+          <t>이재명 대통령이 30일 "일부 조직 노동자들이 자신들만 살겠다고 과도한 요구, 부당한 요구를 해서 우리 국민들로부터 지탄을 받게 되면 해당 노조뿐만이 아니라 다른 노동자들에게도 피해를 입히게 된다"고 지적했다.이 대통령은 이날 오후 청와대 여민관에서 열린 수석보좌관회의...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2517">
+      <c r="A2517" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2517" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2517" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2517" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2517" t="inlineStr">
+        <is>
+          <t>포스코홀딩스, 1Q 영업익 7천100억…어닝 서프라이즈</t>
+        </is>
+      </c>
+      <c r="F2517" t="inlineStr">
+        <is>
+          <t>https://news.einfomax.co.kr/news/articleView.html?idxno=4412677</t>
+        </is>
+      </c>
+      <c r="G2517" t="inlineStr">
+        <is>
+          <t>2026-04-30 14:17:30</t>
+        </is>
+      </c>
+      <c r="H2517" t="inlineStr"/>
+    </row>
+    <row r="2518">
+      <c r="A2518" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2518" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2518" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2518" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2518" t="inlineStr">
+        <is>
+          <t>李대통령 &amp;quot;일부 조직 노동자, 나만 살겠다고 과도한 요구 안돼&amp;quot;</t>
+        </is>
+      </c>
+      <c r="F2518" t="inlineStr">
+        <is>
+          <t>https://news.einfomax.co.kr/news/articleView.html?idxno=4412676</t>
+        </is>
+      </c>
+      <c r="G2518" t="inlineStr">
+        <is>
+          <t>2026-04-30 14:14:06</t>
+        </is>
+      </c>
+      <c r="H2518" t="inlineStr"/>
+    </row>
+    <row r="2519">
+      <c r="A2519" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2519" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2519" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2519" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2519" t="inlineStr">
+        <is>
+          <t>李대통령 &amp;quot;물가안정대책 강화해야…물류비 부담 완화 방안 찾아야&amp;quot;</t>
+        </is>
+      </c>
+      <c r="F2519" t="inlineStr">
+        <is>
+          <t>https://news.einfomax.co.kr/news/articleView.html?idxno=4412675</t>
+        </is>
+      </c>
+      <c r="G2519" t="inlineStr">
+        <is>
+          <t>2026-04-30 14:10:07</t>
+        </is>
+      </c>
+      <c r="H2519" t="inlineStr"/>
+    </row>
+    <row r="2520">
+      <c r="A2520" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2520" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2520" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2520" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2520" t="inlineStr">
+        <is>
+          <t>삼성 노조, 김정관 산업부 장관에 &amp;quot;노조 악마화&amp;quot;</t>
+        </is>
+      </c>
+      <c r="F2520" t="inlineStr">
+        <is>
+          <t>https://news.einfomax.co.kr/news/articleView.html?idxno=4412674</t>
+        </is>
+      </c>
+      <c r="G2520" t="inlineStr">
+        <is>
+          <t>2026-04-30 14:06:10</t>
+        </is>
+      </c>
+      <c r="H2520" t="inlineStr">
+        <is>
+          <t>삼성그룹 초기업 노동조합이 김정관 산업통상부 장관에게 "노사관계 개입 및 이공계 노동자 가치 폄훼에 대해 강력한 유감을 표명한다"며 "반도체 산업 노동자 악마화"에 대해 경고한다고 30일 밝혔다.홍광흠 삼성그룹 초기업 노동조합 위원장은 이날 항의서한을 통해 "본 노동조...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2521">
+      <c r="A2521" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2521" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2521" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2521" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2521" t="inlineStr">
+        <is>
+          <t>셀트리온, 유럽서 유방암 치료제 '허쥬마SC' 제형 추가 신청</t>
+        </is>
+      </c>
+      <c r="F2521" t="inlineStr">
+        <is>
+          <t>https://news.einfomax.co.kr/news/articleView.html?idxno=4412673</t>
+        </is>
+      </c>
+      <c r="G2521" t="inlineStr">
+        <is>
+          <t>2026-04-30 14:04:29</t>
+        </is>
+      </c>
+      <c r="H2521" t="inlineStr">
+        <is>
+          <t>셀트리온은 유럽의약품청(EMA)에 유방암 치료제 허쥬마(성분명 트라스투주맙)의 피하주사(SC) 제형인 '허쥬마SC(개발명 CT-P6 SC)'의 제형 추가 신청을 완료했다고 30일 밝혔다.셀트리온[068270]은 이번 허가 신청을 시작으로 주요국 규제기관에 순차적으로 허...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2522">
+      <c r="A2522" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2522" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2522" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2522" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2522" t="inlineStr">
+        <is>
+          <t>서울 아파트 매매·전세 상승률 소폭 둔화…강남·용산 매매 하락세 여전</t>
+        </is>
+      </c>
+      <c r="F2522" t="inlineStr">
+        <is>
+          <t>https://news.einfomax.co.kr/news/articleView.html?idxno=4412672</t>
+        </is>
+      </c>
+      <c r="G2522" t="inlineStr">
+        <is>
+          <t>2026-04-30 14:03:25</t>
+        </is>
+      </c>
+      <c r="H2522" t="inlineStr">
+        <is>
+          <t>4월 넷째 주 서울 아파트 매매 및 전세 가격 상승 폭이 소폭 둔화했다.매매가격의 경우 지난주까지 조정을 받던 서초구는 상승 전환했고, 강남구와 용산구는 여전히 하락세를 유지 중이다.◇ 서울, 상승·관망 지역 혼재…수도권 둔화한국부동산원이 30일 발표한 지난 27일 기...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2523">
+      <c r="A2523" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2523" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2523" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2523" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2523" t="inlineStr">
+        <is>
+          <t>“우리 경제 위기 대응력 충분”… F4 수장들 첫 회동 - v.daum.net</t>
+        </is>
+      </c>
+      <c r="F2523" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTFBLbU1IN1FUbldUNEpZZjBlbnhyd0JjQy13ak5sbkUybEZBTjdvRzVUeFhieUNvU1N6ZGZwUlRlTDhSeFlxVnd6N0NBQ0VsQUE?oc=5</t>
+        </is>
+      </c>
+      <c r="G2523" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 02:06:58 GMT</t>
+        </is>
+      </c>
+      <c r="H2523" t="inlineStr">
+        <is>
+          <t>“우리 경제 위기 대응력 충분”… F4 수장들 첫 회동&amp;nbsp;&amp;nbsp;v.daum.net</t>
+        </is>
+      </c>
+    </row>
+    <row r="2524">
+      <c r="A2524" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2524" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2524" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2524" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2524" t="inlineStr">
+        <is>
+          <t>구윤철 “금융시장 변동성 지속…위기 대응력은 충분” - 인더스트리뉴스</t>
+        </is>
+      </c>
+      <c r="F2524" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE40LU9IcE1fUzJsWXdYOTdBbE01d3FTLXVac2lGcGlvYnIxanlXV1RSNmduUXlVdXFZaVRfUmtjVUJEYXRxSDJfSG11Z1BjbzllUHZMNUVvNWhuTDRUOFpVMDBhd2N4NVd4LUZhNHN0ZHFRZw?oc=5</t>
+        </is>
+      </c>
+      <c r="G2524" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 02:38:09 GMT</t>
+        </is>
+      </c>
+      <c r="H2524" t="inlineStr">
+        <is>
+          <t>구윤철 “금융시장 변동성 지속…위기 대응력은 충분”&amp;nbsp;&amp;nbsp;인더스트리뉴스</t>
+        </is>
+      </c>
+    </row>
+    <row r="2525">
+      <c r="A2525" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2525" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2525" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2525" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2525" t="inlineStr">
+        <is>
+          <t>[포토] 확대거시경제금융회의 개최 - 아시아경제</t>
+        </is>
+      </c>
+      <c r="F2525" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTE5tY2FPejhFaW1IODM3Z05IZmluZnRBYWJjQjBNdVgwYktTa0xVWjl6dklQV3QxWERaX2xqTkRuWTFyRHpxQ1ZFY1pscHk2M2hyRW9fRVRnd0I4U3kwY2hHZQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G2525" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 23:55:51 GMT</t>
+        </is>
+      </c>
+      <c r="H2525" t="inlineStr">
+        <is>
+          <t>[포토] 확대거시경제금융회의 개최&amp;nbsp;&amp;nbsp;아시아경제</t>
+        </is>
+      </c>
+    </row>
+    <row r="2526">
+      <c r="A2526" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2526" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2526" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2526" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2526" t="inlineStr">
+        <is>
+          <t>경제·금융·통화 수장 첫 회동…구윤철 "위기 대응력 충분" - 국제신문</t>
+        </is>
+      </c>
+      <c r="F2526" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQcExiRUh3cjVUR0RZRlpfcG5ROGF6REdGaGpUU2ltX0UzQTgxN29ycnFzTlIycDdhQWFUVy1aNG4wLVJYTDZjSmVRWkYweW5rQUtTQk83RE9PMmZqeGMxQXIzMlRKNlVsLUdZdnBtNVBRa1FUUlJCajRpRWt0VGxneDhpRFNjWF82aFBaV1Bn?oc=5</t>
+        </is>
+      </c>
+      <c r="G2526" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 01:48:00 GMT</t>
+        </is>
+      </c>
+      <c r="H2526" t="inlineStr">
+        <is>
+          <t>경제·금융·통화 수장 첫 회동…구윤철 "위기 대응력 충분"&amp;nbsp;&amp;nbsp;국제신문</t>
+        </is>
+      </c>
+    </row>
+    <row r="2527">
+      <c r="A2527" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2527" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2527" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2527" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2527" t="inlineStr">
+        <is>
+          <t>경제금융수장들 "중동 상황에 향후 금리 경로상 불확실성 지속...공조 강화" - 파이낸셜신문</t>
+        </is>
+      </c>
+      <c r="F2527" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE9HNHVKQnEwLUY3NFdyVklya3hiaFdQenNFU3lsUWdqd2o5MTlFbnh5eXhsTHUyMmFQNXFsU0NLa0pSc0hrdmJWTDVPNkdvNVdkN01XRnN4ZElVdEVxZEJianp4ak81UFR6c1BB?oc=5</t>
+        </is>
+      </c>
+      <c r="G2527" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 01:23:00 GMT</t>
+        </is>
+      </c>
+      <c r="H2527" t="inlineStr">
+        <is>
+          <t>경제금융수장들 "중동 상황에 향후 금리 경로상 불확실성 지속...공조 강화"&amp;nbsp;&amp;nbsp;파이낸셜신문</t>
+        </is>
+      </c>
+    </row>
+    <row r="2528">
+      <c r="A2528" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2528" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2528" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2528" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2528" t="inlineStr">
+        <is>
+          <t>정부 "유가·환율 등 위기상황에도 금융 대응 여력 충분...24시간 시장 모니터링" - 조선일보</t>
+        </is>
+      </c>
+      <c r="F2528" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNNDc5ZTZLZWhENU9xRzBSVm1aZDVxSmFjTjdSMmpRckF4RFlMc0JCWTh1cUR6S05LTTBTeGFJT0dWY0hoM0lBLTZtRV9XWEVEZnhKam9QLUxIeWV3NnUzcGJxQm5admo4TDczalB3WU4yTG8wTU5oY2hFS3JxNEVpSzM5UmN1V1JRTlJqQVln?oc=5</t>
+        </is>
+      </c>
+      <c r="G2528" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 01:10:00 GMT</t>
+        </is>
+      </c>
+      <c r="H2528" t="inlineStr">
+        <is>
+          <t>정부 "유가·환율 등 위기상황에도 금융 대응 여력 충분...24시간 시장 모니터링"&amp;nbsp;&amp;nbsp;조선일보</t>
+        </is>
+      </c>
+    </row>
+    <row r="2529">
+      <c r="A2529" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2529" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2529" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2529" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2529" t="inlineStr">
+        <is>
+          <t>확대 거시경제 금융회의 발언하는 구윤철 경제부총리 - 뉴시스</t>
+        </is>
+      </c>
+      <c r="F2529" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTFBGQ3FLazRFTGVicjB0QkNuN0N3SkFzRnBTSXJjWWNrbkZRMVRRUnk4R0tUYXE4S1pkZldYMDhUYVNpejNWU0s2SWlKb3M4MTR6VzM5bGVTbFFwdks3dFhlQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G2529" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 23:32:53 GMT</t>
+        </is>
+      </c>
+      <c r="H2529" t="inlineStr">
+        <is>
+          <t>확대 거시경제 금융회의 발언하는 구윤철 경제부총리&amp;nbsp;&amp;nbsp;뉴시스</t>
+        </is>
+      </c>
+    </row>
+    <row r="2530">
+      <c r="A2530" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2530" t="inlineStr">
+        <is>
+          <t>korean_economy</t>
+        </is>
+      </c>
+      <c r="C2530" t="inlineStr">
+        <is>
+          <t>국내 경제</t>
+        </is>
+      </c>
+      <c r="D2530" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2530" t="inlineStr">
+        <is>
+          <t>SAS "금융은 핵심 국가기반시설, 무너지면 경제 전체가 흔들린다" - 지디넷코리아</t>
+        </is>
+      </c>
+      <c r="F2530" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE91VUltUkhCWkxESm9FSWlrLTN4N0c0Slpkd1RyTWJ1VURfY3Q3YVdQWnVLWVN4aWU0VFpxVWtuQW9VR0Z5dTBERW1uMHVLLXQtOTdiek13?oc=5</t>
+        </is>
+      </c>
+      <c r="G2530" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 00:19:24 GMT</t>
+        </is>
+      </c>
+      <c r="H2530" t="inlineStr">
+        <is>
+          <t>SAS "금융은 핵심 국가기반시설, 무너지면 경제 전체가 흔들린다"&amp;nbsp;&amp;nbsp;지디넷코리아</t>
+        </is>
+      </c>
+    </row>
+    <row r="2531">
+      <c r="A2531" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2531" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2531" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2531" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2531" t="inlineStr">
+        <is>
+          <t>LG에너지솔루션, 1분기 매출 6조5550억·2078억 손실 기록</t>
+        </is>
+      </c>
+      <c r="F2531" t="inlineStr">
+        <is>
+          <t>https://www.etnews.com/20260430000262</t>
+        </is>
+      </c>
+      <c r="G2531" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 13:45:42 +0900</t>
+        </is>
+      </c>
+      <c r="H2531" t="inlineStr">
+        <is>
+          <t>LG에너지솔루션이 30일 오전 실적설명회를 열고 2026년 1분기 매출 6조5550억원, 영업손실 2078억원을 기록했다고 밝혔다. 매출은 전년 동기(6조7227억원) 대비 2.5% 감소, 전기(6조4743억원) 대비 1.2% 증가했다. 영업이익은 전년 동기(3747억</t>
+        </is>
+      </c>
+    </row>
+    <row r="2532">
+      <c r="A2532" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2532" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2532" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2532" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2532" t="inlineStr">
+        <is>
+          <t>세월호·이태원 피해자 조롱 50대 구속에…李대통령 “엄벌이 마땅”</t>
+        </is>
+      </c>
+      <c r="F2532" t="inlineStr">
+        <is>
+          <t>https://www.etnews.com/20260430000260</t>
+        </is>
+      </c>
+      <c r="G2532" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 13:45:15 +0900</t>
+        </is>
+      </c>
+      <c r="H2532" t="inlineStr">
+        <is>
+          <t>이재명 대통령이 사회회적 참사에 대한 조롱·모욕 등 2차 가해에 대해 엄정 대응을 강조했다. 이 대통령은 30일 X(구 트위터)에 “인면수심의 가짜뉴스 모욕적 댓글은 엄벌해 마땅하다”고 말했다. 이와 함께 댓글로 세월호·이태원 참사 피해자를 조롱한 50대 남성이 구속됐</t>
+        </is>
+      </c>
+    </row>
+    <row r="2533">
+      <c r="A2533" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2533" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2533" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2533" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2533" t="inlineStr">
+        <is>
+          <t>LG CNS, 1분기 영업익 942억…AI·클라우드 성장 견인</t>
+        </is>
+      </c>
+      <c r="F2533" t="inlineStr">
+        <is>
+          <t>https://www.etnews.com/20260430000243</t>
+        </is>
+      </c>
+      <c r="G2533" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 13:30:44 +0900</t>
+        </is>
+      </c>
+      <c r="H2533" t="inlineStr">
+        <is>
+          <t>LG CNS는 2026년 1분기 매출 1조3150억원, 영업이익 942억원으로 잠정집계됐다고 30일 공시했다. 이는 전년 동기 대비 각각 8.6%, 19.4% 증가한 수치다. 특히 핵심 성장 동력인 인공지능(AI)·클라우드 사업이 1분기 성장을 이끌었다. AI·클라우드</t>
+        </is>
+      </c>
+    </row>
+    <row r="2534">
+      <c r="A2534" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2534" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2534" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2534" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2534" t="inlineStr">
+        <is>
+          <t>삼성전기, 2026년 1분기 영업이익 2806억원…전년比 40%↑</t>
+        </is>
+      </c>
+      <c r="F2534" t="inlineStr">
+        <is>
+          <t>https://www.etnews.com/20260430000212</t>
+        </is>
+      </c>
+      <c r="G2534" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 13:02:09 +0900</t>
+        </is>
+      </c>
+      <c r="H2534" t="inlineStr">
+        <is>
+          <t>삼성전기가 1분기 연결기준 매출 3조2091억원, 영업이익 2806억원을 기록했다고 30일 밝혔다. 매출은 전년 동기 대비 17%, 영업이익은 일회성 비용 714억 원 반영에도 불구하고 전년 동기 대비 40% 증가한 수치다. 특히 창사 이래 처음으로 분기 매출 3조원을</t>
+        </is>
+      </c>
+    </row>
+    <row r="2535">
+      <c r="A2535" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2535" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2535" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2535" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2535" t="inlineStr">
+        <is>
+          <t>삼성전자 “HBM4, 3분기 메모리 매출 과반 예상”</t>
+        </is>
+      </c>
+      <c r="F2535" t="inlineStr">
+        <is>
+          <t>https://www.etnews.com/20260430000211</t>
+        </is>
+      </c>
+      <c r="G2535" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 13:01:37 +0900</t>
+        </is>
+      </c>
+      <c r="H2535" t="inlineStr">
+        <is>
+          <t>삼성전자 1분기 HBM4 매출이 전년 같은 기간 대비 3배 증가한 것으로 나타났다. 오는 3분기에는 HBM4가 전체 메모리 매출에서 과반을 넘어설 것으로 예상된다 . 삼성전자는 30일 2026년 1분기 실적 발표 이후 진행된 컨퍼런스콜에서 이와 같이 밝히며 AI 서버</t>
+        </is>
+      </c>
+    </row>
+    <row r="2536">
+      <c r="A2536" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2536" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2536" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2536" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2536" t="inlineStr">
+        <is>
+          <t>삼성전자, 플랙트 한국법인·공장 설립…가전 부진 속 AIDC·HVAC 신사업 승부</t>
+        </is>
+      </c>
+      <c r="F2536" t="inlineStr">
+        <is>
+          <t>https://www.etnews.com/20260430000208</t>
+        </is>
+      </c>
+      <c r="G2536" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 12:53:44 +0900</t>
+        </is>
+      </c>
+      <c r="H2536" t="inlineStr">
+        <is>
+          <t>삼성전자가 지난해 인수한 유럽 냉난방공조(HVAC) 전문기업 플랙트그룹의 한국 법인을 설립한다. 생산 공장도 설치해 인공지능(AI) 데이터센터 시장을 본격 공략한다. 이상직 삼성전자 DA사업부 부사장은 30일 열린 2026년 1분기 경영설명회에서 “플랙트 중심으로 유럽</t>
+        </is>
+      </c>
+    </row>
+    <row r="2537">
+      <c r="A2537" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2537" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2537" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2537" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2537" t="inlineStr">
+        <is>
+          <t>구윤철 “금융·외환 변동성 지속…위기 대응여력 충분”</t>
+        </is>
+      </c>
+      <c r="F2537" t="inlineStr">
+        <is>
+          <t>https://www.etnews.com/20260430000195</t>
+        </is>
+      </c>
+      <c r="G2537" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 11:48:17 +0900</t>
+        </is>
+      </c>
+      <c r="H2537" t="inlineStr">
+        <is>
+          <t>금융·외환시장 변동성이 이어지는 가운데 국내 금융시스템의 위기 대응 여력은 충분한 수준이라는 평가가 나왔다. 구윤철 부총리 겸 재정경제부 장관은 30일 서울 은행회관에서 확대거시경제금융회의를 주재하고 미국 연방공개시장위원회 금리 동결 이후 시장 상황을 점검했다. 참석자</t>
+        </is>
+      </c>
+    </row>
+    <row r="2538">
+      <c r="A2538" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2538" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2538" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2538" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2538" t="inlineStr">
+        <is>
+          <t>현대차그룹, AI 에이전트 탑재 '플레오스' 공개…글로벌 확장 가속</t>
+        </is>
+      </c>
+      <c r="F2538" t="inlineStr">
+        <is>
+          <t>https://www.etnews.com/20260430000186</t>
+        </is>
+      </c>
+      <c r="G2538" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 11:33:01 +0900</t>
+        </is>
+      </c>
+      <c r="H2538" t="inlineStr">
+        <is>
+          <t>현대차그룹이 차세대 인포테인먼트 시스템(IVI) '플레오스 커넥트'를 처음으로 공개했다. 플레오스 커넥트는 지난해 현대차그룹이 개발자 컨퍼런스 'Pleos 25'를 통해 공개한 연구개발 버전의 양산 모델로, 향후 소프트웨어정의차량(SDV) 시대를 견인하며 고객에게 새로</t>
+        </is>
+      </c>
+    </row>
+    <row r="2539">
+      <c r="A2539" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2539" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2539" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2539" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2539" t="inlineStr">
+        <is>
+          <t>변리사회 “헌재 결정 유감…변호사 자동자격 폐지 추진”</t>
+        </is>
+      </c>
+      <c r="F2539" t="inlineStr">
+        <is>
+          <t>https://www.etnews.com/20260430000247</t>
+        </is>
+      </c>
+      <c r="G2539" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 13:32:02 +0900</t>
+        </is>
+      </c>
+      <c r="H2539" t="inlineStr">
+        <is>
+          <t>헌법재판소가 변리사회 의무가입 제도의 정당성을 인정하면서도 변호사의 변리사 자격 자동 취득에 따른 의무가입에는 헌법불합치 결정을 내린 가운데, 대한변리사회가 유감을 표하며 변호사의 변리사 자동자격 취득 제도 폐지를 위한 법 개정을 촉구했다. 대한변리사회는 30일 성명을</t>
+        </is>
+      </c>
+    </row>
+    <row r="2540">
+      <c r="A2540" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2540" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2540" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2540" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2540" t="inlineStr">
+        <is>
+          <t>AISH·금천구·서울시립대·동양미래대·금천구상공회, 'G밸리 AI 스마트워크 생태계 구축' 업무협약 체결</t>
+        </is>
+      </c>
+      <c r="F2540" t="inlineStr">
+        <is>
+          <t>https://www.etnews.com/20260430000175</t>
+        </is>
+      </c>
+      <c r="G2540" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 11:17:58 +0900</t>
+        </is>
+      </c>
+      <c r="H2540" t="inlineStr">
+        <is>
+          <t>에이아이스마트워크허브(AI Smartwork Hub, 이하 AISH·대표 백광호)는 지난 27일 금천구청, 서울시립대 산학협력단, 동양미래대 산학협력단, 금천구상공회와 함께 'G밸리 AI 스마트워크 생태계 구축 사업' 추진을 위한 5자 업무협약(MOU)을 체결했다고 밝</t>
+        </is>
+      </c>
+    </row>
+    <row r="2541">
+      <c r="A2541" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2541" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2541" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2541" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2541" t="inlineStr">
+        <is>
+          <t>서울대·인텔리시스·컨슈머인사이트, AI 기반 '디지털 트윈 패널' 공동 개발</t>
+        </is>
+      </c>
+      <c r="F2541" t="inlineStr">
+        <is>
+          <t>https://www.etnews.com/20260430000172</t>
+        </is>
+      </c>
+      <c r="G2541" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 11:14:49 +0900</t>
+        </is>
+      </c>
+      <c r="H2541" t="inlineStr">
+        <is>
+          <t>실제 소비자를 인공지능(AI)으로 복제해 원할 때 언제든 의견을 물을 수 있는 디지털 가상 패널이 연내 10만명 규모로 구축된다. 서울대학교 휴먼 트윈 인텔리전스 연구센터, 인텔리시스, 컨슈머인사이트는 '디지털 트윈 패널(DTP)' 개발에 뜻을 같이하고 29일 서울대</t>
+        </is>
+      </c>
+    </row>
+    <row r="2542">
+      <c r="A2542" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2542" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2542" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2542" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2542" t="inlineStr">
+        <is>
+          <t>코그니텀 'DocuRAG', 재정경제부 AI-ONE 플랫폼 구축 적용</t>
+        </is>
+      </c>
+      <c r="F2542" t="inlineStr">
+        <is>
+          <t>https://www.etnews.com/20260430000134</t>
+        </is>
+      </c>
+      <c r="G2542" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 10:43:22 +0900</t>
+        </is>
+      </c>
+      <c r="H2542" t="inlineStr">
+        <is>
+          <t>코그니텀(대표 정좌연)는 자사 인공지능(AI) 에이전트 플랫폼 'DocuRAG'가 재정경제부 AI-ONE 플랫폼 구축사업에 적용된다고 밝혔다. 재정경제부 AI-ONE 플랫폼 구축사업은 부처 내 분산된 업무 데이터와 문서를 통합 관리하고, 이를 기반으로 행정업무에 활용할</t>
+        </is>
+      </c>
+    </row>
+    <row r="2543">
+      <c r="A2543" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2543" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2543" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2543" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2543" t="inlineStr">
+        <is>
+          <t>해성디에스-인터엑스, AX 자율제조 파트너십…반도체 제조 'AI 자율화' 앞당긴다</t>
+        </is>
+      </c>
+      <c r="F2543" t="inlineStr">
+        <is>
+          <t>https://www.etnews.com/20260430000132</t>
+        </is>
+      </c>
+      <c r="G2543" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 10:41:56 +0900</t>
+        </is>
+      </c>
+      <c r="H2543" t="inlineStr">
+        <is>
+          <t>해성그룹 계열사인 글로벌 반도체 부품 전문기업 해성디에스(HAESUNG DS·대표 최영식)가 인공지능 전환(AX) 자율제조 솔루션 전문기업 인터엑스(INTERX·대표 박정윤)와 반도체 제조 현장의 AX 자율제조 전환을 위한 파트너십을 체결했다고 30일 밝혔다. 반도체</t>
+        </is>
+      </c>
+    </row>
+    <row r="2544">
+      <c r="A2544" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2544" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2544" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2544" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2544" t="inlineStr">
+        <is>
+          <t>인젠트, AI 시대 오픈소스 DB 전략과 인사이트 발표</t>
+        </is>
+      </c>
+      <c r="F2544" t="inlineStr">
+        <is>
+          <t>https://www.etnews.com/20260430000099</t>
+        </is>
+      </c>
+      <c r="G2544" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 10:07:03 +0900</t>
+        </is>
+      </c>
+      <c r="H2544" t="inlineStr">
+        <is>
+          <t>인젠트(대표 이형배)는 테크전문 채널 토크아이티(TalkIT)에서 웨비나를 갖고 오픈소스 데이터베이스 '포스트그레스큐엘(PostgreSQL)'의 역할과 기업 대응 전략을 소개했다고 30일 밝혔다. PostgreSQL 오픈소스 커뮤니티에서 활동 중인 글로벌 컨트리뷰터이자</t>
+        </is>
+      </c>
+    </row>
+    <row r="2545">
+      <c r="A2545" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2545" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2545" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2545" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2545" t="inlineStr">
+        <is>
+          <t>SAS 수석 아키텍트 “양자·AI 결합, 적은 데이터로 머신러닝 가능”</t>
+        </is>
+      </c>
+      <c r="F2545" t="inlineStr">
+        <is>
+          <t>https://www.etnews.com/20260430000013</t>
+        </is>
+      </c>
+      <c r="G2545" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 10:00:00 +0900</t>
+        </is>
+      </c>
+      <c r="H2545" t="inlineStr">
+        <is>
+          <t>“SAS 퀀텀 랩은 사용자가 IBM·구글·마이크로소프트(MS) 등 다양한 기업 시스템과 서비스에 접근할 수 있는 통합 환경을 제공합니다.” 빌 위소츠키 SAS 양자시스템 수석 아키텍트는 29일(현지시간) 전자신문과 미국 텍사스 그레이프바인 인터뷰에서 “기업에서 양자컴퓨</t>
+        </is>
+      </c>
+    </row>
+    <row r="2546">
+      <c r="A2546" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2546" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2546" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2546" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2546" t="inlineStr">
+        <is>
+          <t>“멀티-하이브리드 클라우드 현대화가 경쟁 우위 필수 요소”…델 테크놀로지스 보고서 발간</t>
+        </is>
+      </c>
+      <c r="F2546" t="inlineStr">
+        <is>
+          <t>https://www.etnews.com/20260430000071</t>
+        </is>
+      </c>
+      <c r="G2546" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 09:27:12 +0900</t>
+        </is>
+      </c>
+      <c r="H2546" t="inlineStr">
+        <is>
+          <t>델 테크놀로지스가 멀티-하이브리드 클라우드와 프라이빗 클라우드 현대화가 기업 경쟁력 확보의 핵심 요소라는 분석을 내놨다. 델 테크놀로지스는 30일 한국을 포함한 아시아·태평양 지역 프라이빗 클라우드 현대화 트렌드를 분석한 'IDC 인포브리프-프라이빗 클라우드 현대화를</t>
+        </is>
+      </c>
+    </row>
+    <row r="2547">
+      <c r="A2547" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2547" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2547" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2547" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2547" t="inlineStr">
+        <is>
+          <t>캐나다 총기 사건 유족, 오픈AI 상대로 미국 법원에 소송 제기</t>
+        </is>
+      </c>
+      <c r="F2547" t="inlineStr">
+        <is>
+          <t>https://www.aitimes.com/news/articleView.html?idxno=209977</t>
+        </is>
+      </c>
+      <c r="G2547" t="inlineStr">
+        <is>
+          <t>2026-04-30 14:18:22</t>
+        </is>
+      </c>
+      <c r="H2547" t="inlineStr">
+        <is>
+          <t>캐나다에서 발생한 대형 총기 난사 사건의 피해자 유가족들이 오픈AI와 샘 알트먼 CEO를 상대로 미국 법원에 소송을 제기했다. 이들은 사건 발생 수개월 전 가해자의 위험 징후가 '챗GPT' 대화에서 포착됐음에도 이를 경찰에 알리지 않았다고 주장하고 있다.29일(현지시간...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2548">
+      <c r="A2548" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2548" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2548" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2548" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2548" t="inlineStr">
+        <is>
+          <t>빅테크 AI 투자액 사상 최고치 경신...지난 분기에만 194조 돌파</t>
+        </is>
+      </c>
+      <c r="F2548" t="inlineStr">
+        <is>
+          <t>https://www.aitimes.com/news/articleView.html?idxno=209963</t>
+        </is>
+      </c>
+      <c r="G2548" t="inlineStr">
+        <is>
+          <t>2026-04-30 14:05:35</t>
+        </is>
+      </c>
+      <c r="H2548" t="inlineStr">
+        <is>
+          <t>아마존, 구글, 마이크로소프트(MS), 메타 등 글로벌 빅테크 4사가 AI 패권 경쟁을 위해 지난 분기 사상 최대 규모의 투자에 나선 것으로 밝혀졌다. 또 이들은 올해에만 약 7000억달러(약 1040조원)에 달하는 자금을 AI 인프라 구축에 쏟아부을 계획이다.29일(...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2549">
+      <c r="A2549" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2549" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2549" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2549" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2549" t="inlineStr">
+        <is>
+          <t>전남, 농어민 공익수당 추가 신청 개시</t>
+        </is>
+      </c>
+      <c r="F2549" t="inlineStr">
+        <is>
+          <t>https://www.aitimes.com/news/articleView.html?idxno=209944</t>
+        </is>
+      </c>
+      <c r="G2549" t="inlineStr">
+        <is>
+          <t>2026-04-30 13:56:27</t>
+        </is>
+      </c>
+      <c r="H2549" t="inlineStr">
+        <is>
+          <t>전라남도가 오는 5월20일까지 농어민 공익수당 추가 신청을 받는다고 밝혔다.30일부터 시작된 이번 추가 접수는 지난 2~3월 정기 신청 기간에 개인 사정 등으로 신청하지 못한 농어민을 지원하기 위해 마련됐다.신청 대상은 농어업·임업 경영정보를 등록한 경영체의 경영주나 ...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2550">
+      <c r="A2550" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2550" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2550" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2550" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2550" t="inlineStr">
+        <is>
+          <t>광주, 2026년 개별공시지가 결정·공시…전년 대비 1.70% 상승</t>
+        </is>
+      </c>
+      <c r="F2550" t="inlineStr">
+        <is>
+          <t>https://www.aitimes.com/news/articleView.html?idxno=209958</t>
+        </is>
+      </c>
+      <c r="G2550" t="inlineStr">
+        <is>
+          <t>2026-04-30 13:55:17</t>
+        </is>
+      </c>
+      <c r="H2550" t="inlineStr">
+        <is>
+          <t>광주시가 2026년 1월1일 기준 개별공시지가를 30일 결정·공시했다.개별공시지가는 토지 관련 국세와 지방세, 개발부담금 등의 부과 기준으로 활용되는 자료로, 이번 공시 대상은 총 37만여 필지다.이번 공시는 국토교통부가 조사하는 표준지를 기준으로 개별 필지에 대한 토...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2551">
+      <c r="A2551" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2551" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2551" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2551" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2551" t="inlineStr">
+        <is>
+          <t>머스크, 법정서 “오픈AI 초기 투자는 결국 바보 같았던 선택”</t>
+        </is>
+      </c>
+      <c r="F2551" t="inlineStr">
+        <is>
+          <t>https://www.aitimes.com/news/articleView.html?idxno=209974</t>
+        </is>
+      </c>
+      <c r="G2551" t="inlineStr">
+        <is>
+          <t>2026-04-30 13:39:59</t>
+        </is>
+      </c>
+      <c r="H2551" t="inlineStr">
+        <is>
+          <t>일론 머스크 CEO가 오픈AI를 상대로 한 소송에서 이틀째 직접 증언에 나서며, AI 업계를 대표하는 인물 간 갈등이 정점으로 치닫고 있다. 그는 초기 투자 결정에 대해 “바보 같았던 선택이었다”고 표현하며 오픈AI의 영리 전환을 강하게 비판했다.월스트리트 저널 등에 ...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2552">
+      <c r="A2552" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2552" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2552" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2552" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2552" t="inlineStr">
+        <is>
+          <t>딥시크에 '눈' 달렸다...이미지 인식 기능 소비자에 첫 공개</t>
+        </is>
+      </c>
+      <c r="F2552" t="inlineStr">
+        <is>
+          <t>https://www.aitimes.com/news/articleView.html?idxno=209960</t>
+        </is>
+      </c>
+      <c r="G2552" t="inlineStr">
+        <is>
+          <t>2026-04-30 13:21:08</t>
+        </is>
+      </c>
+      <c r="H2552" t="inlineStr">
+        <is>
+          <t>딥시크가 챗봇에 이미지 인식 기능을 처음 도입하며 멀티모달 경쟁에 뛰어들었다. 딥시크는 29일 웹과 모바일 챗봇 애플리케이션에 ‘이미지 인식 모드(Image Recognition Mode)’를 추가하고 일부 사용자 대상으로 베타 테스트를 시작했다.이 기능은 기존 ‘엑스...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2553">
+      <c r="A2553" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2553" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2553" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2553" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2553" t="inlineStr">
+        <is>
+          <t>LG CNS, 1분기 매출 1조3150억원 달성..."AI·클라우드가 실적 견인"</t>
+        </is>
+      </c>
+      <c r="F2553" t="inlineStr">
+        <is>
+          <t>https://www.aitimes.com/news/articleView.html?idxno=209955</t>
+        </is>
+      </c>
+      <c r="G2553" t="inlineStr">
+        <is>
+          <t>2026-04-30 13:12:25</t>
+        </is>
+      </c>
+      <c r="H2553" t="inlineStr">
+        <is>
+          <t>LG CNS(대표 현신균)는 올해 1분기 매출 1조3150억원, 영업이익 942억원을 달성했다고 30일 밝혔다. 전년 동기 대비 매출은 8.6%, 영업이익은 19.4% 증가한 수치다.AI·클라우드 사업 매출은 전년 동기 대비 6.7% 성장한 7654억원으로 전체 매출의...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2554">
+      <c r="A2554" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2554" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2554" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2554" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2554" t="inlineStr">
+        <is>
+          <t>광양, ‘아동친화업소 존중존’ 참여업소 모집</t>
+        </is>
+      </c>
+      <c r="F2554" t="inlineStr">
+        <is>
+          <t>https://www.aitimes.com/news/articleView.html?idxno=209961</t>
+        </is>
+      </c>
+      <c r="G2554" t="inlineStr">
+        <is>
+          <t>2026-04-30 13:08:53</t>
+        </is>
+      </c>
+      <c r="H2554" t="inlineStr">
+        <is>
+          <t>광양시가 아동과 보호자가 함께 이용하기 편안한 외식 환경을 만들기 위해 ‘아동친화업소 존중존’ 참여업소를 모집한다고 29일 밝혔다.이 사업은 아동 메뉴를 제공하는 외식업소를 아동친화업소로 지정하고, 유아의자와 아동 식기류 등 필요한 물품을 지원한다.광양은 아동친화도시 ...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2555">
+      <c r="A2555" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2555" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2555" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2555" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2555" t="inlineStr">
+        <is>
+          <t>SK건설, ‘친환경 회사’로 불러주세요</t>
+        </is>
+      </c>
+      <c r="F2555" t="inlineStr">
+        <is>
+          <t>http://www.bloter.net/archives/537737</t>
+        </is>
+      </c>
+      <c r="G2555" t="inlineStr">
+        <is>
+          <t>Fri, 26 Mar 2021 03:03:43 +0000</t>
+        </is>
+      </c>
+      <c r="H2555" t="inlineStr">
+        <is>
+          <t>SK&amp;#44148;&amp;#49444;&amp;#51060; &amp;#8216;ESG(&amp;#54872;&amp;#44221;, &amp;#49324;&amp;#54924;, &amp;#51648;&amp;#48176;&amp;#44396;&amp;#51312;)&amp;#8217; &amp;#51473;&amp;#49900;&amp;#51032; &amp;#44221;&amp;#...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2556">
+      <c r="A2556" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2556" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2556" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2556" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2556" t="inlineStr">
+        <is>
+          <t>‘조선史’ 새로 쓴 삼성중공업, 2조8000억 규모 컨테이너선 수주</t>
+        </is>
+      </c>
+      <c r="F2556" t="inlineStr">
+        <is>
+          <t>http://www.bloter.net/archives/537723</t>
+        </is>
+      </c>
+      <c r="G2556" t="inlineStr">
+        <is>
+          <t>Fri, 26 Mar 2021 02:45:51 +0000</t>
+        </is>
+      </c>
+      <c r="H2556" t="inlineStr">
+        <is>
+          <t>&amp;#49340;&amp;#49457;&amp;#51473;&amp;#44277;&amp;#50629;&amp;#51060; &amp;#52968;&amp;#53580;&amp;#51060;&amp;#45320;&amp;#49440; 20&amp;#52377;&amp;#51012; &amp;#54620;&amp;#48264;&amp;#50640; &amp;#49688;&amp;#51452;...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2557">
+      <c r="A2557" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2557" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2557" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2557" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2557" t="inlineStr">
+        <is>
+          <t>[넘버스]현대엘리베이터 창사 후 유동성 ‘최대’…현대그룹 재건에 쓰일까</t>
+        </is>
+      </c>
+      <c r="F2557" t="inlineStr">
+        <is>
+          <t>http://www.bloter.net/archives/537639</t>
+        </is>
+      </c>
+      <c r="G2557" t="inlineStr">
+        <is>
+          <t>Fri, 26 Mar 2021 02:07:10 +0000</t>
+        </is>
+      </c>
+      <c r="H2557" t="inlineStr">
+        <is>
+          <t>&amp;#49707;&amp;#51088;&amp;#46308;(Numbers)&amp;#47196; &amp;#44592;&amp;#50629;&amp;#44284; &amp;#44221;&amp;#51228;,&amp;#160;&amp;#44592;&amp;#49696;&amp;#51012; &amp;#54644;&amp;#49437;&amp;#54644; &amp;#48372;&amp;#...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2558">
+      <c r="A2558" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2558" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2558" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2558" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2558" t="inlineStr">
+        <is>
+          <t>LG 인적분할 통과…’화이트박스’가 반대한 3가지 이유는</t>
+        </is>
+      </c>
+      <c r="F2558" t="inlineStr">
+        <is>
+          <t>http://www.bloter.net/archives/537698</t>
+        </is>
+      </c>
+      <c r="G2558" t="inlineStr">
+        <is>
+          <t>Fri, 26 Mar 2021 01:55:00 +0000</t>
+        </is>
+      </c>
+      <c r="H2558" t="inlineStr">
+        <is>
+          <t>LG&amp;#44536;&amp;#47353;&amp;#51060; &amp;#51648;&amp;#45212;&amp;#54644; 11&amp;#50900;&amp;#48512;&amp;#53552; &amp;#45824;&amp;#50808;&amp;#51201;&amp;#51004;&amp;#47196; &amp;#52628;&amp;#51652;&amp;#54620; &amp;#516...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2559">
+      <c r="A2559" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2559" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2559" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2559" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2559" t="inlineStr">
+        <is>
+          <t>웨이브, 오리지널 콘텐츠 투자 늘린다…”2025년까지 1조원 목표”</t>
+        </is>
+      </c>
+      <c r="F2559" t="inlineStr">
+        <is>
+          <t>http://www.bloter.net/archives/537676</t>
+        </is>
+      </c>
+      <c r="G2559" t="inlineStr">
+        <is>
+          <t>Fri, 26 Mar 2021 01:42:27 +0000</t>
+        </is>
+      </c>
+      <c r="H2559" t="inlineStr">
+        <is>
+          <t>&amp;#50728;&amp;#46972;&amp;#51064;&amp;#50689;&amp;#49345;&amp;#49436;&amp;#48708;&amp;#49828;(OTT) &amp;#8216;&amp;#50920;&amp;#51060;&amp;#48652;(Wavve)&amp;#8217;&amp;#47484; &amp;#50868;&amp;#50689;&amp;#54616;&amp;#...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2560">
+      <c r="A2560" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2560" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2560" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2560" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2560" t="inlineStr">
+        <is>
+          <t>‘시작이 좋다!’ 현대차, 스타리아·아이오닉5 사전계약 흥행 또 흥행</t>
+        </is>
+      </c>
+      <c r="F2560" t="inlineStr">
+        <is>
+          <t>http://www.bloter.net/archives/537683</t>
+        </is>
+      </c>
+      <c r="G2560" t="inlineStr">
+        <is>
+          <t>Fri, 26 Mar 2021 01:41:53 +0000</t>
+        </is>
+      </c>
+      <c r="H2560" t="inlineStr">
+        <is>
+          <t>&amp;#54788;&amp;#45824;&amp;#51088;&amp;#46041;&amp;#52264;&amp;#51032; &amp;#49352; &amp;#47784;&amp;#45944; &amp;#49828;&amp;#53440;&amp;#47532;&amp;#50500;&amp;#50752; &amp;#50500;&amp;#51060;&amp;#50724;&amp;#45769;5&amp;...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2561">
+      <c r="A2561" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2561" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2561" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2561" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2561" t="inlineStr">
+        <is>
+          <t>스냅챗, 틱톡 ‘듀엣’ 유사기능 ‘리믹스’ 테스트</t>
+        </is>
+      </c>
+      <c r="F2561" t="inlineStr">
+        <is>
+          <t>http://www.bloter.net/archives/537673</t>
+        </is>
+      </c>
+      <c r="G2561" t="inlineStr">
+        <is>
+          <t>Fri, 26 Mar 2021 00:47:35 +0000</t>
+        </is>
+      </c>
+      <c r="H2561" t="inlineStr">
+        <is>
+          <t>&amp;#47784;&amp;#48148;&amp;#51068; &amp;#47700;&amp;#49888;&amp;#51200; &amp;#8216;&amp;#49828;&amp;#45253;&amp;#52311;&amp;#8217;&amp;#51060; &amp;#54001;&amp;#53665; &amp;#8216;&amp;#46272;&amp;#50659;&amp;#8217;&amp;#4428...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2562">
+      <c r="A2562" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2562" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2562" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2562" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2562" t="inlineStr">
+        <is>
+          <t>뉴욕타임스 최초 ‘NFT 칼럼’, 56만달러 낙찰</t>
+        </is>
+      </c>
+      <c r="F2562" t="inlineStr">
+        <is>
+          <t>http://www.bloter.net/archives/537664</t>
+        </is>
+      </c>
+      <c r="G2562" t="inlineStr">
+        <is>
+          <t>Thu, 25 Mar 2021 23:49:42 +0000</t>
+        </is>
+      </c>
+      <c r="H2562" t="inlineStr">
+        <is>
+          <t>&amp;#45824;&amp;#52404; &amp;#48520;&amp;#44032;&amp;#45733;&amp;#54620; &amp;#53664;&amp;#53360;(NFT)&amp;#51060; &amp;#51201;&amp;#50857;&amp;#46108; &amp;#60;&amp;#45684;&amp;#50837;&amp;#53440;&amp;#51076;&amp;#49828;...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2563">
+      <c r="A2563" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2563" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2563" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2563" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2563" t="inlineStr">
+        <is>
+          <t>연봉 9000만원 육박, 문과생도 OK…중국 ‘로봇 인재 쟁탈전’ 시작 - v.daum.net</t>
+        </is>
+      </c>
+      <c r="F2563" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTFBxdS1yWGZpRFZUN2UtRGxMU29TSThQRFJ6YUl6Q0Rva09feTFRRU5feUo1dUY4ZFZvcTdid3YyN1JNSkduSTlYMzUyd241Z1E?oc=5</t>
+        </is>
+      </c>
+      <c r="G2563" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 00:08:08 GMT</t>
+        </is>
+      </c>
+      <c r="H2563" t="inlineStr">
+        <is>
+          <t>연봉 9000만원 육박, 문과생도 OK…중국 ‘로봇 인재 쟁탈전’ 시작&amp;nbsp;&amp;nbsp;v.daum.net</t>
+        </is>
+      </c>
+    </row>
+    <row r="2564">
+      <c r="A2564" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2564" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2564" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2564" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2564" t="inlineStr">
+        <is>
+          <t>로보택시 집단 고장 후폭풍... 놀란 중국, 신규 허가 중단 - 조선일보</t>
+        </is>
+      </c>
+      <c r="F2564" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQWUpTZFJoOHVSZTV5TDV2RWE4TFBvWXNiLUJCQlp6a0xLVWMxa2M1MmlCOWNPY1JmRHNvTkdkcFVVV0p5U0pDZ2dXUTVxNDAtbk9nOUZQWk1xY0laYWZQVFVnOW5vWnM2Q0N3YTd5VFdENFY2TnhlS0ZtaFZUYzlQQU14dFluZXVHcmlSMVJ5T01iVVBVX2tpQktKUEZxZw?oc=5</t>
+        </is>
+      </c>
+      <c r="G2564" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 12:39:19 GMT</t>
+        </is>
+      </c>
+      <c r="H2564" t="inlineStr">
+        <is>
+          <t>로보택시 집단 고장 후폭풍... 놀란 중국, 신규 허가 중단&amp;nbsp;&amp;nbsp;조선일보</t>
+        </is>
+      </c>
+    </row>
+    <row r="2565">
+      <c r="A2565" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2565" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2565" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2565" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2565" t="inlineStr">
+        <is>
+          <t>삼성전자 1분기 반도체 영업이익률 66%…2분기 HBM4E 첫 샘플 공급 (종합) - v.daum.net</t>
+        </is>
+      </c>
+      <c r="F2565" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTFBiVWFCMDZfcU01dk1VbmNVY1h2MGJ2MnA0TFp0RDNBOGdNNC1pNHlQdDhJUXRmb0EyYnZ0UU1oYVFnOGo4dEhvRkVGd0Y3TW8?oc=5</t>
+        </is>
+      </c>
+      <c r="G2565" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 00:41:00 GMT</t>
+        </is>
+      </c>
+      <c r="H2565" t="inlineStr">
+        <is>
+          <t>삼성전자 1분기 반도체 영업이익률 66%…2분기 HBM4E 첫 샘플 공급 (종합)&amp;nbsp;&amp;nbsp;v.daum.net</t>
+        </is>
+      </c>
+    </row>
+    <row r="2566">
+      <c r="A2566" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2566" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2566" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2566" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2566" t="inlineStr">
+        <is>
+          <t>욕먹어도 계속 업데이트…카카오, 눈물겨운 돈 벌기 - 네이트</t>
+        </is>
+      </c>
+      <c r="F2566" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTE5mc2JjMXhibFU3TWt6S2VzbVRrSHJac041eXl1YlViWkZUQ2gtemVsMHV0UlVuajJQc21fMmNOZ2xUcWk0cG5ONzhKcWhmaWlDbW5v?oc=5</t>
+        </is>
+      </c>
+      <c r="G2566" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 21:01:00 GMT</t>
+        </is>
+      </c>
+      <c r="H2566" t="inlineStr">
+        <is>
+          <t>욕먹어도 계속 업데이트…카카오, 눈물겨운 돈 벌기&amp;nbsp;&amp;nbsp;네이트</t>
+        </is>
+      </c>
+    </row>
+    <row r="2567">
+      <c r="A2567" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2567" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2567" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2567" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2567" t="inlineStr">
+        <is>
+          <t>“240만원 아이패드가 83만원?”…쿠팡 가격 오류에 ‘주문 대란’ - 조선일보</t>
+        </is>
+      </c>
+      <c r="F2567" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxQRXBhWjRJdzQ0VHVkb1JpaHQzRDl4Z1Q2ZVBlU1NudjNXSVI3a1hMSGV3ekhPWm54ZTBKaGFzcEZTQmZzUHB6MXE0d1BiZVFyR1YwYktPUDljZGJwNDh4bkZ2cHZmc0ZzNnpuaV9nWUIyVklrRkh2VHlUVUZyU1pRQW4xb3FNbjFDRXF3NWRVU2k?oc=5</t>
+        </is>
+      </c>
+      <c r="G2567" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 02:24:55 GMT</t>
+        </is>
+      </c>
+      <c r="H2567" t="inlineStr">
+        <is>
+          <t>“240만원 아이패드가 83만원?”…쿠팡 가격 오류에 ‘주문 대란’&amp;nbsp;&amp;nbsp;조선일보</t>
+        </is>
+      </c>
+    </row>
+    <row r="2568">
+      <c r="A2568" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2568" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2568" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2568" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2568" t="inlineStr">
+        <is>
+          <t>테슬라 HW3용 'FSD 라이트', 국내 적용 가능성 주목 - 네이트</t>
+        </is>
+      </c>
+      <c r="F2568" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTFBHeXphQlJfMHdrS1VGMzk1NFJZLTFGeTNsazhvdGVxOWhLRlEteXFxb0xqbGFyNnRRNUliNVVKdDZ0cVlySE1Hb2ZMSTdpNm1rbXBR?oc=5</t>
+        </is>
+      </c>
+      <c r="G2568" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 03:18:00 GMT</t>
+        </is>
+      </c>
+      <c r="H2568" t="inlineStr">
+        <is>
+          <t>테슬라 HW3용 'FSD 라이트', 국내 적용 가능성 주목&amp;nbsp;&amp;nbsp;네이트</t>
+        </is>
+      </c>
+    </row>
+    <row r="2569">
+      <c r="A2569" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2569" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2569" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2569" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2569" t="inlineStr">
+        <is>
+          <t>130만닉스 세계 시총 16위 됐다…하루 만에 두 계단 '쑥' - 네이트</t>
+        </is>
+      </c>
+      <c r="F2569" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTFBHSGZFeUJQem05b09WeUJKSzgzbmV1eWJVdjFmbklkcmpMdTA4S0F5cXVEbHdMaHdwZHR1cUlDcWpTR3BnWDFJNFBJZXJHVDB3UlE4?oc=5</t>
+        </is>
+      </c>
+      <c r="G2569" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 07:34:00 GMT</t>
+        </is>
+      </c>
+      <c r="H2569" t="inlineStr">
+        <is>
+          <t>130만닉스 세계 시총 16위 됐다…하루 만에 두 계단 '쑥'&amp;nbsp;&amp;nbsp;네이트</t>
+        </is>
+      </c>
+    </row>
+    <row r="2570">
+      <c r="A2570" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2570" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2570" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2570" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2570" t="inlineStr">
+        <is>
+          <t>73조원 전력망 사업 한전 독점 막 내린다 - 대한경제</t>
+        </is>
+      </c>
+      <c r="F2570" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE5DM1RLeGZmZFpNNlRiZlBLRlI2cmNoUGU3T1JDVnhCbU9xd1o2YUdTamNOMjQ4aHcxakd1aVVWZ3BockYwWXNZTURzallSMXBWcHVvWXlVaUZ5UnhWN0VXN1NFMnZGbFhpWmRiS0RyYzF5U0xG?oc=5</t>
+        </is>
+      </c>
+      <c r="G2570" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 21:00:22 GMT</t>
+        </is>
+      </c>
+      <c r="H2570" t="inlineStr">
+        <is>
+          <t>73조원 전력망 사업 한전 독점 막 내린다&amp;nbsp;&amp;nbsp;대한경제</t>
+        </is>
+      </c>
+    </row>
+    <row r="2571">
+      <c r="A2571" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2571" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2571" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2571" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2571" t="inlineStr">
+        <is>
+          <t>조달청, AI 기술 기반 '지능형 예정가격 작성지원시스템' 개통 - 매일경제 마켓</t>
+        </is>
+      </c>
+      <c r="F2571" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiUkFVX3lxTFBfQWpHaHNuQWk5bTF4MzFnZF81WGFobkJLYUxkaG95ekp4b0VfSzIwa0VsTGtkVWFnaXhTLWxXYl8zNDRUMmJ5cS1YdFhGdTNULVE?oc=5</t>
+        </is>
+      </c>
+      <c r="G2571" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 04:50:34 GMT</t>
+        </is>
+      </c>
+      <c r="H2571" t="inlineStr">
+        <is>
+          <t>조달청, AI 기술 기반 '지능형 예정가격 작성지원시스템' 개통&amp;nbsp;&amp;nbsp;매일경제 마켓</t>
+        </is>
+      </c>
+    </row>
+    <row r="2572">
+      <c r="A2572" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2572" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2572" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2572" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2572" t="inlineStr">
+        <is>
+          <t>AI가 제주 돼지 사육 관리…생산성 향상·탄소중립 동시 달성 - 동아사이언스</t>
+        </is>
+      </c>
+      <c r="F2572" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTE1SUlJ0NWVVS2tHMjl4QmVuQl9TNVBVX1NyNlFHNUttSGQzc0hlUWxjelZ5TGNnaUdpTjFldVE5YmZXYkM4Nzc5TlFld3ViaGJqYzBscg?oc=5</t>
+        </is>
+      </c>
+      <c r="G2572" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 02:09:00 GMT</t>
+        </is>
+      </c>
+      <c r="H2572" t="inlineStr">
+        <is>
+          <t>AI가 제주 돼지 사육 관리…생산성 향상·탄소중립 동시 달성&amp;nbsp;&amp;nbsp;동아사이언스</t>
+        </is>
+      </c>
+    </row>
+    <row r="2573">
+      <c r="A2573" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2573" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2573" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2573" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2573" t="inlineStr">
+        <is>
+          <t>번개장터 "AI 기술로 상품 등록 수 42% 증가" - 아시아경제</t>
+        </is>
+      </c>
+      <c r="F2573" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTFBvczVCNk1peEl1eFZSYVJCTzcwUzVzX1FUWkl3aEJGSzZGcEhmMDQ3RU44X2xJdHFUaGRka2M5ZG85aFczYldnODhoS3JUaXRzLWJHLWRiYUloa0hUanhlTg?oc=5</t>
+        </is>
+      </c>
+      <c r="G2573" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 00:08:43 GMT</t>
+        </is>
+      </c>
+      <c r="H2573" t="inlineStr">
+        <is>
+          <t>번개장터 "AI 기술로 상품 등록 수 42% 증가"&amp;nbsp;&amp;nbsp;아시아경제</t>
+        </is>
+      </c>
+    </row>
+    <row r="2574">
+      <c r="A2574" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2574" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2574" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2574" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2574" t="inlineStr">
+        <is>
+          <t>번개장터 “AI 기술로 상품 등록 수 42%↑” - 전자신문</t>
+        </is>
+      </c>
+      <c r="F2574" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiTkFVX3lxTE05bEhvT2U4N0VLN0I3WW1pdHg1c0s4TXEwRkg0N195ejY2UDBTeEl2U1U1MHZLQkthMFhQUU1FX3pld2VkRDBySTUxTE9wdw?oc=5</t>
+        </is>
+      </c>
+      <c r="G2574" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 00:25:53 GMT</t>
+        </is>
+      </c>
+      <c r="H2574" t="inlineStr">
+        <is>
+          <t>번개장터 “AI 기술로 상품 등록 수 42%↑”&amp;nbsp;&amp;nbsp;전자신문</t>
+        </is>
+      </c>
+    </row>
+    <row r="2575">
+      <c r="A2575" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2575" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2575" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2575" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2575" t="inlineStr">
+        <is>
+          <t>“데이터 없는 전장에서도 작동하는 AI”...마음AI, 자기지도학습 기반 수중 기뢰 탐지 AI 기술 공개 - 인공지능신문</t>
+        </is>
+      </c>
+      <c r="F2575" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE5WMC0wY2JQRTBXT0xpTjdwOGVxTi1uUmZlZHNnMEZQUHdGUnRRRFB5OXpwbUstaHpJU3RvbU5PSzVhdFBMQjI4ektlbUVEMjBabUp0bnM4NDhHc3NIdU9vYm5IUUdGQ3M?oc=5</t>
+        </is>
+      </c>
+      <c r="G2575" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 00:28:47 GMT</t>
+        </is>
+      </c>
+      <c r="H2575" t="inlineStr">
+        <is>
+          <t>“데이터 없는 전장에서도 작동하는 AI”...마음AI, 자기지도학습 기반 수중 기뢰 탐지 AI 기술 공개&amp;nbsp;&amp;nbsp;인공지능신문</t>
+        </is>
+      </c>
+    </row>
+    <row r="2576">
+      <c r="A2576" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2576" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2576" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2576" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2576" t="inlineStr">
+        <is>
+          <t>공공조달에 AI기술 접목 스마트한 조달서비스 제공 - 헤럴드경제</t>
+        </is>
+      </c>
+      <c r="F2576" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTFA1ZHJVMGlyMVM3WGZ3ZXJxSFBPYm4tTmQyMDVMV1ExRHlvQ1NsS0VvUndaM0VvV1pFTi0yVjlmb3c5b290STJ1aU9mQWZMSVEtUTlFYURR?oc=5</t>
+        </is>
+      </c>
+      <c r="G2576" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 03:39:54 GMT</t>
+        </is>
+      </c>
+      <c r="H2576" t="inlineStr">
+        <is>
+          <t>공공조달에 AI기술 접목 스마트한 조달서비스 제공&amp;nbsp;&amp;nbsp;헤럴드경제</t>
+        </is>
+      </c>
+    </row>
+    <row r="2577">
+      <c r="A2577" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2577" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2577" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2577" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2577" t="inlineStr">
+        <is>
+          <t>CJ그룹, 인공지능 기술 논문... 국제 표현 학습 학회 ‘최종’ 채택 - 비욘드포스트</t>
+        </is>
+      </c>
+      <c r="F2577" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTFBTRGdlcV9rLWpCLTAzeHgyeEpsdDlZYmszUTZFODFYTVZURWFJbERJcGw0dy16ck1WX2htWEZyN0E1emUtbll3WkpvTUhLZkJFTExtWFNhX1F6SnhtbnEwdVYtUXEzeVppaThLWUZiRVZXZkJONDN6M2w2MDc?oc=5</t>
+        </is>
+      </c>
+      <c r="G2577" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 01:27:00 GMT</t>
+        </is>
+      </c>
+      <c r="H2577" t="inlineStr">
+        <is>
+          <t>CJ그룹, 인공지능 기술 논문... 국제 표현 학습 학회 ‘최종’ 채택&amp;nbsp;&amp;nbsp;비욘드포스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="2578">
+      <c r="A2578" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2578" t="inlineStr">
+        <is>
+          <t>korean_tech</t>
+        </is>
+      </c>
+      <c r="C2578" t="inlineStr">
+        <is>
+          <t>국내 IT·기술</t>
+        </is>
+      </c>
+      <c r="D2578" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="E2578" t="inlineStr">
+        <is>
+          <t>'지역·필수·공공의료' AI 전환으로 의료 격차 줄인다 - v.daum.net</t>
+        </is>
+      </c>
+      <c r="F2578" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE9jYlR5d1BrTjN3WDdzVkVHUUVCc1A0Q0NNSjhQS0hoajhscWRmQWZLT0o4aUZnUlVMa0RhLXNDZnh0NjA3Wnhza1cxWTlTamM?oc=5</t>
+        </is>
+      </c>
+      <c r="G2578" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 02:19:13 GMT</t>
+        </is>
+      </c>
+      <c r="H2578" t="inlineStr">
+        <is>
+          <t>'지역·필수·공공의료' AI 전환으로 의료 격차 줄인다&amp;nbsp;&amp;nbsp;v.daum.net</t>
+        </is>
+      </c>
+    </row>
+    <row r="2579">
+      <c r="A2579" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2579" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2579" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2579" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2579" t="inlineStr">
+        <is>
+          <t>ABC can beat Trump FCC's license threat if owner Disney is willing to fight</t>
+        </is>
+      </c>
+      <c r="F2579" t="inlineStr">
+        <is>
+          <t>https://arstechnica.com/tech-policy/2026/04/abc-can-beat-trump-fccs-license-threat-if-owner-disney-is-willing-to-fight/</t>
+        </is>
+      </c>
+      <c r="G2579" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 19:14:44 +0000</t>
+        </is>
+      </c>
+      <c r="H2579" t="inlineStr">
+        <is>
+          <t>Broadcast license renewals are "all but automatic" due to 1996 change in US law.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2580">
+      <c r="A2580" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2580" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2580" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2580" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2580" t="inlineStr">
+        <is>
+          <t>OpenAI Codex system prompt includes explicit directive to "never talk about goblins"</t>
+        </is>
+      </c>
+      <c r="F2580" t="inlineStr">
+        <is>
+          <t>https://arstechnica.com/ai/2026/04/openai-codex-system-prompt-includes-explicit-directive-to-never-talk-about-goblins/</t>
+        </is>
+      </c>
+      <c r="G2580" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 19:00:58 +0000</t>
+        </is>
+      </c>
+      <c r="H2580" t="inlineStr">
+        <is>
+          <t>Directions also include system instructions to act like "you have a vivid inner life."</t>
+        </is>
+      </c>
+    </row>
+    <row r="2581">
+      <c r="A2581" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2581" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2581" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2581" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2581" t="inlineStr">
+        <is>
+          <t>Howdy's dated $3/month ad-free streaming service said to have 1M subscribers</t>
+        </is>
+      </c>
+      <c r="F2581" t="inlineStr">
+        <is>
+          <t>https://arstechnica.com/gadgets/2026/04/howdys-dated-3-month-ad-free-streaming-service-said-to-have-1m-subscribers/</t>
+        </is>
+      </c>
+      <c r="G2581" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 18:02:20 +0000</t>
+        </is>
+      </c>
+      <c r="H2581" t="inlineStr">
+        <is>
+          <t>Most are keeping their subscriptions after signing up, too, research firm says.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2582">
+      <c r="A2582" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2582" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2582" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2582" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2582" t="inlineStr">
+        <is>
+          <t>New Sam Bankman-Fried trial would be huge waste of court’s time, judge says</t>
+        </is>
+      </c>
+      <c r="F2582" t="inlineStr">
+        <is>
+          <t>https://arstechnica.com/tech-policy/2026/04/new-sam-bankman-fried-trial-would-be-huge-waste-of-courts-time-judge-says/</t>
+        </is>
+      </c>
+      <c r="G2582" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 17:52:52 +0000</t>
+        </is>
+      </c>
+      <c r="H2582" t="inlineStr">
+        <is>
+          <t>FTX fraudster came out as Republican, then tried to claim Biden's DOJ targeted him.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2583">
+      <c r="A2583" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2583" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2583" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2583" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2583" t="inlineStr">
+        <is>
+          <t>Drone strikes on data centers spook Big Tech, halting Middle East projects</t>
+        </is>
+      </c>
+      <c r="F2583" t="inlineStr">
+        <is>
+          <t>https://arstechnica.com/ai/2026/04/data-center-developer-pauses-middle-east-projects-after-war-damage/</t>
+        </is>
+      </c>
+      <c r="G2583" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 17:27:53 +0000</t>
+        </is>
+      </c>
+      <c r="H2583" t="inlineStr">
+        <is>
+          <t>Uninsurable war damage is forcing tech companies to rethink Middle East plans.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2584">
+      <c r="A2584" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2584" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2584" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2584" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2584" t="inlineStr">
+        <is>
+          <t>Motorola reveals 2026 Razr lineup with modest upgrades and higher prices</t>
+        </is>
+      </c>
+      <c r="F2584" t="inlineStr">
+        <is>
+          <t>https://arstechnica.com/gadgets/2026/04/motorola-reveals-2026-razr-lineup-with-modest-upgrades-and-higher-prices/</t>
+        </is>
+      </c>
+      <c r="G2584" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 16:55:58 +0000</t>
+        </is>
+      </c>
+      <c r="H2584" t="inlineStr">
+        <is>
+          <t>Motorola's foldable lineup is bigger and more spendy than ever.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2585">
+      <c r="A2585" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2585" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2585" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2585" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2585" t="inlineStr">
+        <is>
+          <t>Nvidia fixes the 8GB RAM problem with one of its GPUs—if you can pay for it</t>
+        </is>
+      </c>
+      <c r="F2585" t="inlineStr">
+        <is>
+          <t>https://arstechnica.com/gadgets/2026/04/nvidia-fixes-the-8gb-ram-problem-with-one-of-its-gpus-if-you-can-pay-for-it/</t>
+        </is>
+      </c>
+      <c r="G2585" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 16:06:28 +0000</t>
+        </is>
+      </c>
+      <c r="H2585" t="inlineStr">
+        <is>
+          <t>Framework charges nearly double for the 12GB version of the mobile RTX 5070.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2586">
+      <c r="A2586" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2586" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2586" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2586" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2586" t="inlineStr">
+        <is>
+          <t>Professional school grads from diverse classes get higher salaries</t>
+        </is>
+      </c>
+      <c r="F2586" t="inlineStr">
+        <is>
+          <t>https://arstechnica.com/science/2026/04/professional-school-grads-from-diverse-classes-get-higher-salaries/</t>
+        </is>
+      </c>
+      <c r="G2586" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 15:55:55 +0000</t>
+        </is>
+      </c>
+      <c r="H2586" t="inlineStr">
+        <is>
+          <t>Study authors say courts should reconsider rulings in light of this new evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2587">
+      <c r="A2587" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2587" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2587" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2587" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2587" t="inlineStr">
+        <is>
+          <t>Elon Musk’s worst enemy in court is Elon Musk</t>
+        </is>
+      </c>
+      <c r="F2587" t="inlineStr">
+        <is>
+          <t>https://www.theverge.com/tech/921022/elon-musk-cross-openai-altman</t>
+        </is>
+      </c>
+      <c r="G2587" t="inlineStr">
+        <is>
+          <t>2026-04-29T20:01:24-04:00</t>
+        </is>
+      </c>
+      <c r="H2587" t="inlineStr">
+        <is>
+          <t>About five hours into Elon Musk's testimony, I typed the following sentence into my notes: "I have never been more sympathetic to Sam Altman in my lif...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2588">
+      <c r="A2588" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2588" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2588" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2588" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2588" t="inlineStr">
+        <is>
+          <t>Grindr — yes, Grindr — won the WHCD party circuit</t>
+        </is>
+      </c>
+      <c r="F2588" t="inlineStr">
+        <is>
+          <t>https://www.theverge.com/column/920845/grindr-whcd-party-2026</t>
+        </is>
+      </c>
+      <c r="G2588" t="inlineStr">
+        <is>
+          <t>2026-04-29T18:00:00-04:00</t>
+        </is>
+      </c>
+      <c r="H2588" t="inlineStr">
+        <is>
+          <t>Hello and welcome to Regulator, a newsletter for Verge subscribers about technology, politics, and technology learning how to politick. If you're not ...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2589">
+      <c r="A2589" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2589" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2589" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2589" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2589" t="inlineStr">
+        <is>
+          <t>Splatoon Raiders preorders for the Switch 2 are nearly 20 percent off</t>
+        </is>
+      </c>
+      <c r="F2589" t="inlineStr">
+        <is>
+          <t>https://www.theverge.com/gadgets/920848/splatoon-raiders-physical-edition-preorder-switch-2-walmart-deal-sale</t>
+        </is>
+      </c>
+      <c r="G2589" t="inlineStr">
+        <is>
+          <t>2026-04-29T17:19:39-04:00</t>
+        </is>
+      </c>
+      <c r="H2589" t="inlineStr">
+        <is>
+          <t>Nintendo recently announced a new pricing policy, which knocks $10 off the cost of digital versions of future first-party titles exclusive to the Nint...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2590">
+      <c r="A2590" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2590" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2590" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2590" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2590" t="inlineStr">
+        <is>
+          <t>Microsoft reports sinking Xbox revenue as its cloud business climbs</t>
+        </is>
+      </c>
+      <c r="F2590" t="inlineStr">
+        <is>
+          <t>https://www.theverge.com/tech/920785/microsoft-xbox-revenue-q3-2026-earnings</t>
+        </is>
+      </c>
+      <c r="G2590" t="inlineStr">
+        <is>
+          <t>2026-04-29T16:43:37-04:00</t>
+        </is>
+      </c>
+      <c r="H2590" t="inlineStr">
+        <is>
+          <t>Microsoft's Xbox hardware revenue continues to tumble, with the company revealing a 33 percent decline as part of its earnings report released on Wedn...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2591">
+      <c r="A2591" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2591" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2591" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2591" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2591" t="inlineStr">
+        <is>
+          <t>Google Search queries hit an ‘all time high’ last quarter</t>
+        </is>
+      </c>
+      <c r="F2591" t="inlineStr">
+        <is>
+          <t>https://www.theverge.com/tech/920815/google-alphabet-q1-2026-earnings-sundar-pichai</t>
+        </is>
+      </c>
+      <c r="G2591" t="inlineStr">
+        <is>
+          <t>2026-04-29T16:28:11-04:00</t>
+        </is>
+      </c>
+      <c r="H2591" t="inlineStr">
+        <is>
+          <t>Google Search queries hit an "all time high" in the first quarter of 2026, according to a statement from CEO Sundar Pichai published as part of Alphab...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2592">
+      <c r="A2592" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2592" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2592" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2592" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2592" t="inlineStr">
+        <is>
+          <t>All the evidence unveiled so far in Musk v. Altman</t>
+        </is>
+      </c>
+      <c r="F2592" t="inlineStr">
+        <is>
+          <t>https://www.theverge.com/ai-artificial-intelligence/920775/evidence-exhibits-elon-musk-sam-altman-openai-trial</t>
+        </is>
+      </c>
+      <c r="G2592" t="inlineStr">
+        <is>
+          <t>2026-04-29T14:03:05-04:00</t>
+        </is>
+      </c>
+      <c r="H2592" t="inlineStr">
+        <is>
+          <t>The Musk v. Altman trial is underway, and that means exhibits, or the evidence to be presented in court, are being revealed piece by piece. So far, em...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2593">
+      <c r="A2593" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2593" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2593" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2593" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2593" t="inlineStr">
+        <is>
+          <t>Ubuntu’s AI plans have Linux users looking for a &amp;#8216;kill switch&amp;#8217;</t>
+        </is>
+      </c>
+      <c r="F2593" t="inlineStr">
+        <is>
+          <t>https://www.theverge.com/tech/920723/linux-ubuntu-ai-features-ai-kill-switch</t>
+        </is>
+      </c>
+      <c r="G2593" t="inlineStr">
+        <is>
+          <t>2026-04-29T13:32:02-04:00</t>
+        </is>
+      </c>
+      <c r="H2593" t="inlineStr">
+        <is>
+          <t>Canonical's plan to add AI features to Ubuntu has some users asking for "a version of Ubuntu that does not include these features," while others say t...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2594">
+      <c r="A2594" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2594" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2594" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2594" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2594" t="inlineStr">
+        <is>
+          <t>Motorola just revealed the Razr Fold’s price and hoo boy</t>
+        </is>
+      </c>
+      <c r="F2594" t="inlineStr">
+        <is>
+          <t>https://www.theverge.com/gadgets/919460/motorola-razr-2026-price-availability</t>
+        </is>
+      </c>
+      <c r="G2594" t="inlineStr">
+        <is>
+          <t>2026-04-29T12:00:00-04:00</t>
+        </is>
+      </c>
+      <c r="H2594" t="inlineStr">
+        <is>
+          <t>2026 is shaping up to be a tough year to launch a high-end phone. The memory crisis has phone prices rising across the board, so an already expensive ...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2595">
+      <c r="A2595" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2595" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2595" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2595" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2595" t="inlineStr">
+        <is>
+          <t>SoftBank is creating a robotics company that builds data centers — and already eyeing a $100B IPO</t>
+        </is>
+      </c>
+      <c r="F2595" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/04/29/softbank-is-creating-a-robotics-company-that-builds-data-centers-and-already-eyeing-a-100b-ipo/</t>
+        </is>
+      </c>
+      <c r="G2595" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 03:58:22 +0000</t>
+        </is>
+      </c>
+      <c r="H2595" t="inlineStr">
+        <is>
+          <t>You need infrastructure to build AI a and robots, but apparently you also need AI and robots to build infrastructure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2596">
+      <c r="A2596" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2596" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2596" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2596" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2596" t="inlineStr">
+        <is>
+          <t>Amazon, Meta join fight to end Google Pay, PhonePe dominance in India</t>
+        </is>
+      </c>
+      <c r="F2596" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/04/29/amazon-meta-join-fight-to-end-google-pay-phonepe-dominance-in-india/</t>
+        </is>
+      </c>
+      <c r="G2596" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 01:00:00 +0000</t>
+        </is>
+      </c>
+      <c r="H2596" t="inlineStr">
+        <is>
+          <t>PhonePe and Google Pay command 80% of India's UPI instant payments network. Rivals are set to meet with regulators to lobby for restrictions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2597">
+      <c r="A2597" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2597" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2597" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2597" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2597" t="inlineStr">
+        <is>
+          <t>Amazon’s cloud business is surging — and so is its capital spending</t>
+        </is>
+      </c>
+      <c r="F2597" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/04/29/amazons-cloud-business-is-surging-and-so-is-its-capital-spending/</t>
+        </is>
+      </c>
+      <c r="G2597" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 00:14:23 +0000</t>
+        </is>
+      </c>
+      <c r="H2597" t="inlineStr">
+        <is>
+          <t>The e-commerce giant is making more money than expected from AWS but it's also spending a lot, and will continue to do so in the near term, its chief ...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2598">
+      <c r="A2598" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2598" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2598" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2598" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2598" t="inlineStr">
+        <is>
+          <t>Sources: Anthropic could raise a new $50B round at a valuation of $900B</t>
+        </is>
+      </c>
+      <c r="F2598" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/04/29/sources-anthropic-could-raise-a-new-50b-round-at-a-valuation-of-900b/</t>
+        </is>
+      </c>
+      <c r="G2598" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 00:07:15 +0000</t>
+        </is>
+      </c>
+      <c r="H2598" t="inlineStr">
+        <is>
+          <t>The maker of Claude has received multiple pre-emptive offers at valuations in the $850 billion to $900 billion range, according to sources familiar wi...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2599">
+      <c r="A2599" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2599" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2599" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2599" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2599" t="inlineStr">
+        <is>
+          <t>On the stand, Elon Musk can’t escape his own tweets</t>
+        </is>
+      </c>
+      <c r="F2599" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/04/29/on-the-stand-elon-musk-cant-escape-his-own-tweets/</t>
+        </is>
+      </c>
+      <c r="G2599" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 23:58:36 +0000</t>
+        </is>
+      </c>
+      <c r="H2599" t="inlineStr">
+        <is>
+          <t>Elon Musk took the stand for the second day for his attempt to legally dismantle OpenAI.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2600">
+      <c r="A2600" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2600" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2600" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2600" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2600" t="inlineStr">
+        <is>
+          <t>Meta is still burning money on AR/VR</t>
+        </is>
+      </c>
+      <c r="F2600" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/04/29/meta-is-still-burning-money-on-ar-vr/</t>
+        </is>
+      </c>
+      <c r="G2600" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 23:58:26 +0000</t>
+        </is>
+      </c>
+      <c r="H2600" t="inlineStr">
+        <is>
+          <t>Meta is losing billions on Reality Labs each quarter, and its AI expenditures are only going to increase its spending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2601">
+      <c r="A2601" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2601" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2601" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2601" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2601" t="inlineStr">
+        <is>
+          <t>Satya Nadella says he’s ready to ‘exploit’ the new OpenAI deal</t>
+        </is>
+      </c>
+      <c r="F2601" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/04/29/satya-nadella-says-hes-ready-to-exploit-the-new-openai-deal/</t>
+        </is>
+      </c>
+      <c r="G2601" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 23:55:23 +0000</t>
+        </is>
+      </c>
+      <c r="H2601" t="inlineStr">
+        <is>
+          <t>Microsoft gets to offer OpenAI's tech to its cloud customers and doesn't have to pay for it. "We fully plan to exploit it," Nadella said.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2602">
+      <c r="A2602" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2602" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2602" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2602" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2602" t="inlineStr">
+        <is>
+          <t>Microsoft says it has over 20M paid Copilot users, and they really are using it</t>
+        </is>
+      </c>
+      <c r="F2602" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2026/04/29/microsoft-says-it-has-over-20m-paid-copilot-users-and-they-really-are-using-it/</t>
+        </is>
+      </c>
+      <c r="G2602" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 23:02:23 +0000</t>
+        </is>
+      </c>
+      <c r="H2602" t="inlineStr">
+        <is>
+          <t>Despite the lingering perception that no one really uses Copilot, Microsoft said on Wednesday that the number of users and engagement is growing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2603">
+      <c r="A2603" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2603" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2603" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2603" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2603" t="inlineStr">
+        <is>
+          <t>The Download: storing nuclear waste and orchestrating agents</t>
+        </is>
+      </c>
+      <c r="F2603" t="inlineStr">
+        <is>
+          <t>https://www.technologyreview.com/2026/04/29/1136666/the-download-nuclear-waste-orchestrated-ai-agents/</t>
+        </is>
+      </c>
+      <c r="G2603" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 12:10:00 +0000</t>
+        </is>
+      </c>
+      <c r="H2603" t="inlineStr">
+        <is>
+          <t>This is today&amp;#8217;s edition of The Download, our weekday newsletter that provides a daily dose of what&amp;#8217;s going on in the world of technology. ...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2604">
+      <c r="A2604" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2604" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2604" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2604" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2604" t="inlineStr">
+        <is>
+          <t>Privacy in the AI era is possible, says Proton's CEO, but one thing keeps him up at night</t>
+        </is>
+      </c>
+      <c r="F2604" t="inlineStr">
+        <is>
+          <t>https://www.zdnet.com/article/proton-ceo-andy-yen-interview-ai-privacy-security-semafor/</t>
+        </is>
+      </c>
+      <c r="G2604" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 02:00:35 GMT</t>
+        </is>
+      </c>
+      <c r="H2604" t="inlineStr">
+        <is>
+          <t>At Semafor World Economy, I spoke with Andy Yen about mass surveillance, protecting children, local AI, and the one thing Proton can't save users from...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2605">
+      <c r="A2605" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2605" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2605" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2605" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2605" t="inlineStr">
+        <is>
+          <t>This simple Linux tweak fixes crashes automatically - and it costs me nothing</t>
+        </is>
+      </c>
+      <c r="F2605" t="inlineStr">
+        <is>
+          <t>https://www.zdnet.com/article/how-linux-watchdog-reboots-my-frozen-system/</t>
+        </is>
+      </c>
+      <c r="G2605" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 01:01:04 GMT</t>
+        </is>
+      </c>
+      <c r="H2605" t="inlineStr">
+        <is>
+          <t>If your Linux PC becomes unresponsive, you might want to consider a 'Watchdog' that can monitor it and reboot when problems arise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2606">
+      <c r="A2606" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2606" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2606" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2606" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2606" t="inlineStr">
+        <is>
+          <t>Windows changes are coming: Here's how to get a sneak peek at what's next</t>
+        </is>
+      </c>
+      <c r="F2606" t="inlineStr">
+        <is>
+          <t>https://www.zdnet.com/article/microsoft-windows-insider-program-simplified/</t>
+        </is>
+      </c>
+      <c r="G2606" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 01:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H2606" t="inlineStr">
+        <is>
+          <t>Microsoft is finally making its Windows Insider Program less complicated. Here's everything that's being fixed - and what you have to do to see the ch...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2607">
+      <c r="A2607" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2607" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2607" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2607" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2607" t="inlineStr">
+        <is>
+          <t>Eero Signal keeps your business online during internet outages</t>
+        </is>
+      </c>
+      <c r="F2607" t="inlineStr">
+        <is>
+          <t>https://www.zdnet.com/article/eero-signal-keeps-your-business-online-during-internet-outages/</t>
+        </is>
+      </c>
+      <c r="G2607" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 21:55:00 GMT</t>
+        </is>
+      </c>
+      <c r="H2607" t="inlineStr">
+        <is>
+          <t>A cellular backup device that connects to your Eero mesh Wi-Fi system, Eero Signal provides backup internet when your primary wired connection goes do...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2608">
+      <c r="A2608" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2608" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2608" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2608" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2608" t="inlineStr">
+        <is>
+          <t>Motorola Razr Ultra (2026) vs. Samsung Galaxy Z Flip 7: I tried both, and there's a clear winner</t>
+        </is>
+      </c>
+      <c r="F2608" t="inlineStr">
+        <is>
+          <t>https://www.zdnet.com/article/samsung-galaxy-z-flip-7-vs-motorola-razr-ultra-2026/</t>
+        </is>
+      </c>
+      <c r="G2608" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 19:15:42 GMT</t>
+        </is>
+      </c>
+      <c r="H2608" t="inlineStr">
+        <is>
+          <t>Samsung focuses on durability and AI, while the new Motorola phone is all about the hardware. Here's which one I think is better.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2609">
+      <c r="A2609" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2609" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2609" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2609" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2609" t="inlineStr">
+        <is>
+          <t>Forget Samsung Galaxy S26 Ultra: I found alternatives that are nearly as good for less money</t>
+        </is>
+      </c>
+      <c r="F2609" t="inlineStr">
+        <is>
+          <t>https://www.zdnet.com/article/best-phones-you-can-buy-in-2026-are-from-2025/</t>
+        </is>
+      </c>
+      <c r="G2609" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 18:59:00 GMT</t>
+        </is>
+      </c>
+      <c r="H2609" t="inlineStr">
+        <is>
+          <t>After reviewing the latest Google, Samsung, and Motorola phones, I have a newfound appreciation for last year's models.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2610">
+      <c r="A2610" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2610" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2610" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2610" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2610" t="inlineStr">
+        <is>
+          <t>HP vs. Dell: I've tested dozens of laptops from both brands, and here's my advice</t>
+        </is>
+      </c>
+      <c r="F2610" t="inlineStr">
+        <is>
+          <t>https://www.zdnet.com/article/hp-vs-dell-laptops-comparison/</t>
+        </is>
+      </c>
+      <c r="G2610" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 17:08:00 GMT</t>
+        </is>
+      </c>
+      <c r="H2610" t="inlineStr">
+        <is>
+          <t>Dell and HP both sell excellent laptops, but their models stand out in different ways. Let's break down the biggest differences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2611">
+      <c r="A2611" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2611" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2611" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2611" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2611" t="inlineStr">
+        <is>
+          <t>Our readers can't stop buying these 10 gadgets - and No. 4 really surprised us</t>
+        </is>
+      </c>
+      <c r="F2611" t="inlineStr">
+        <is>
+          <t>https://www.zdnet.com/article/zdnet-most-popular-gadgets-from-readers-2026/</t>
+        </is>
+      </c>
+      <c r="G2611" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 16:52:04 GMT</t>
+        </is>
+      </c>
+      <c r="H2611" t="inlineStr">
+        <is>
+          <t>These gadgets and gizmos are the most popular among ZDNET readers so far this year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2612">
+      <c r="A2612" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2612" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2612" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2612" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2612" t="inlineStr">
+        <is>
+          <t>YouTube Bringing Free Picture-in-Picture to iPhone Users Outside the U.S. - MacRumors</t>
+        </is>
+      </c>
+      <c r="F2612" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE15Nk1fTXhyRjl6aG53SWtnTzdoLWNrMFZ3MEJhMFZZVjNiQ2ZxUmdvWmVlamhkQ2xDMFZnZFZVVWo4anNVeHF5dG5vSk1tc2l5Tm5GcHZHOElPWDBRZkw1RW5kVmc5M3dQcDhOVnB0dnVKMHJJRHJiSWY4TFI?oc=5</t>
+        </is>
+      </c>
+      <c r="G2612" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 00:01:14 GMT</t>
+        </is>
+      </c>
+      <c r="H2612" t="inlineStr">
+        <is>
+          <t>YouTube Bringing Free Picture-in-Picture to iPhone Users Outside the U.S.&amp;nbsp;&amp;nbsp;MacRumorsYouTube starts rolling out free picture-in-picture (PiP)...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2613">
+      <c r="A2613" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2613" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2613" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2613" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2613" t="inlineStr">
+        <is>
+          <t>Motorola and Google announce two new Google Photos features with the launch of the new razr - Motorola News</t>
+        </is>
+      </c>
+      <c r="F2613" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOMzJWVXdOVXAzLTFwSjVDekpQNXRyWVZTUW1pRkt5X18tb19sRUNVN09vOURkSTM4SW1BNDJUYTg4MDl4anZsd2FGdUhhby1uX0ZJbVU3MkIzSkFHS3RNN3JtUzZyYUNOMGZjLTVteWx4NGxSTUtzSE1BMlNVX0k4dng3WGJ2OVpuUTZlQXdSV1RPVmFtRlE1YVlWb1ZsMFRON1JyQmZKWjVJTDJWSEdYZ0pyeFJxRi1h?oc=5</t>
+        </is>
+      </c>
+      <c r="G2613" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 16:03:18 GMT</t>
+        </is>
+      </c>
+      <c r="H2613" t="inlineStr">
+        <is>
+          <t>Motorola and Google announce two new Google Photos features with the launch of the new razr&amp;nbsp;&amp;nbsp;Motorola NewsA new way to create a digital ward...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2614">
+      <c r="A2614" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2614" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2614" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2614" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2614" t="inlineStr">
+        <is>
+          <t>Friendly AI chatbots more likely to support conspiracy theories, study finds - The Guardian</t>
+        </is>
+      </c>
+      <c r="F2614" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQVTNjbXpSRGJuNl9XQnZLZGdQWTJaZHRPb0hRZ3hZU3pVcUVoQi1NanJ6dUlRR24wQkxxM24yR2ZsSkJXa29WQW1TdWFqU3FCQmZZYmxoZTEweVFiMTg5WUVLTERGUDdGdnhNT2F2ZTllRGVpQmlnZk9QdzZ6ZnlFNHluTlNlazZuN0o2M3YtY1dqWnV4bGNEVGVOWUZaR3JXd2FpWXZmZHQ0aGkzVmV3UEY1RVZ0TUFLMGgyRVc0TkVYUFVBSmdqbEpoSjZoX1VZMUJVVXBsaw?oc=5</t>
+        </is>
+      </c>
+      <c r="G2614" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 15:46:00 GMT</t>
+        </is>
+      </c>
+      <c r="H2614" t="inlineStr">
+        <is>
+          <t>Friendly AI chatbots more likely to support conspiracy theories, study finds&amp;nbsp;&amp;nbsp;The GuardianTraining language models to be warm can reduce acc...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2615">
+      <c r="A2615" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2615" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2615" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2615" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2615" t="inlineStr">
+        <is>
+          <t>More Gemini features are coming to Google TV - TechCrunch</t>
+        </is>
+      </c>
+      <c r="F2615" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxQTzJmQ1ZGcm9Na0dXa3dGazRjUWllMFlPNlRabC1IOEI5WnJJUVVTQzd6NUIya2FDdW9PMk5JSUE3YVhHeXN4aVY4YkV6OEFxeHV4eW94ZGdicEpJT0htTW02QkY3b0I3S3U1dWJrblZjQVdDWDN0elROcXd1Rk9SckJuNEZTdw?oc=5</t>
+        </is>
+      </c>
+      <c r="G2615" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 16:40:49 GMT</t>
+        </is>
+      </c>
+      <c r="H2615" t="inlineStr">
+        <is>
+          <t>More Gemini features are coming to Google TV&amp;nbsp;&amp;nbsp;TechCrunchEnjoy new ways to create, search and stream on Google TV&amp;nbsp;&amp;nbsp;blog.googleGoogl...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2616">
+      <c r="A2616" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2616" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2616" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2616" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2616" t="inlineStr">
+        <is>
+          <t>Nvidia fixes the 8GB RAM problem with one of its GPUs—if you can pay for it - Ars Technica</t>
+        </is>
+      </c>
+      <c r="F2616" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPVDQ5aWo5NkZDbEdFU1UzeDBYYzZaaTkzY1RYRzVRWFZnMlhmSE10Mno2R0x5UjF6OVRnYVBIaUdvQl9BYlN4UU1mVmhqRWZSaUNrWE5IaEhnWFhrVGxNMkJhQkh0alFZU3JFX1VxbmtYMTkwQUdLQVl1ZHpWamdaY0VubExxWWh0VmhxR0M2TWU5N2kxVXV6QnJ0LUpNZ19UVXY4MHZqSEtkM09pMy1melF2SHktc1k?oc=5</t>
+        </is>
+      </c>
+      <c r="G2616" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 16:06:28 GMT</t>
+        </is>
+      </c>
+      <c r="H2616" t="inlineStr">
+        <is>
+          <t>Nvidia fixes the 8GB RAM problem with one of its GPUs—if you can pay for it&amp;nbsp;&amp;nbsp;Ars TechnicaNVIDIA starts offering a 12GB version of the 5070 f...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2617">
+      <c r="A2617" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2617" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2617" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2617" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2617" t="inlineStr">
+        <is>
+          <t>Apple Weather App Experiencing Outage [Update: Fixed] - MacRumors</t>
+        </is>
+      </c>
+      <c r="F2617" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE1Hdk9nSl9EcUxCSklNVmNHQ1M3U2pjRWxTUllpMkV3MUNkc2d6UGVNOFR0UlBHanMwTVYxcWg5SXFOWFNzY2RZcnBKczBMM3ZacFlnNi12YmxlTWR4bGtJcllzaFFsR0VTaVZLWHZTYw?oc=5</t>
+        </is>
+      </c>
+      <c r="G2617" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 18:00:35 GMT</t>
+        </is>
+      </c>
+      <c r="H2617" t="inlineStr">
+        <is>
+          <t>Apple Weather App Experiencing Outage [Update: Fixed]&amp;nbsp;&amp;nbsp;MacRumorsApple confirms Weather app outage. Here's what we know&amp;nbsp;&amp;nbsp;MashableAp...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2618">
+      <c r="A2618" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2618" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2618" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2618" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2618" t="inlineStr">
+        <is>
+          <t>GitHub rushed to fix a critical vulnerability in less than six hours - The Verge</t>
+        </is>
+      </c>
+      <c r="F2618" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNNXhzZUZZMkxUbmpZTkpiZk9ZS0xfMmRZb185Zk1Ob2lTcW81TWl6ZU5US2RlOTBjenZXQ0t3dmVPMWI5dDVHR2xwdVZlRzZLQVNEYTE0amZjWGhBREt5bUVJV01nWmxYc0xEX1VJcGFRS1lkRUNscjNZNmhHQnlWTFh4dWwwM19BUVRz?oc=5</t>
+        </is>
+      </c>
+      <c r="G2618" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 10:04:25 GMT</t>
+        </is>
+      </c>
+      <c r="H2618" t="inlineStr">
+        <is>
+          <t>GitHub rushed to fix a critical vulnerability in less than six hours&amp;nbsp;&amp;nbsp;The VergeCritical GitHub Vulnerability Exposed Millions of Repositorie...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2619">
+      <c r="A2619" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2619" t="inlineStr">
+        <is>
+          <t>technology</t>
+        </is>
+      </c>
+      <c r="C2619" t="inlineStr">
+        <is>
+          <t>글로벌 기술</t>
+        </is>
+      </c>
+      <c r="D2619" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2619" t="inlineStr">
+        <is>
+          <t>Motorola Razr Fold officially costs $1,899 in the US, available in May - 9to5Google</t>
+        </is>
+      </c>
+      <c r="F2619" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQSUg3NHRyM3dKbWEtY1VUNUJBalVZbUlGZW9ua1ZJbHFLd2hhZDJMcXllV2NEdlEyUlZOQzFMekVsbGFlRlZGVmd5dlFsTFM0R1JWM1ppNG1kWU1naTZNNV9oZHJCUS1zMXJCNmhEeU9NVG56YkNVZzFudVhGbjl6RlMycjRLUEhoMGRjNk9wWW5xejh5MWNjVA?oc=5</t>
+        </is>
+      </c>
+      <c r="G2619" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 16:01:00 GMT</t>
+        </is>
+      </c>
+      <c r="H2619" t="inlineStr">
+        <is>
+          <t>Motorola Razr Fold officially costs $1,899 in the US, available in May&amp;nbsp;&amp;nbsp;9to5GoogleMotorola just revealed the Razr Fold’s price and hoo boy&amp;n...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2620">
+      <c r="A2620" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2620" t="inlineStr">
+        <is>
+          <t>ai_ml</t>
+        </is>
+      </c>
+      <c r="C2620" t="inlineStr">
+        <is>
+          <t>AI·ML</t>
+        </is>
+      </c>
+      <c r="D2620" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2620" t="inlineStr">
+        <is>
+          <t>IDC: How EMEA CIOs can jumpstart AI rollouts</t>
+        </is>
+      </c>
+      <c r="F2620" t="inlineStr">
+        <is>
+          <t>https://www.artificialintelligence-news.com/news/idc-how-emea-cios-can-jumpstart-ai-rollouts/</t>
+        </is>
+      </c>
+      <c r="G2620" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 14:02:45 +0000</t>
+        </is>
+      </c>
+      <c r="H2620" t="inlineStr">
+        <is>
+          <t>Getting stalled enterprise AI rollouts in the EMEA region moving again will require CIOs to aggressively audit their systems. Over the past 18 months,...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2621">
+      <c r="A2621" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2621" t="inlineStr">
+        <is>
+          <t>ai_ml</t>
+        </is>
+      </c>
+      <c r="C2621" t="inlineStr">
+        <is>
+          <t>AI·ML</t>
+        </is>
+      </c>
+      <c r="D2621" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2621" t="inlineStr">
+        <is>
+          <t>GPT-5.5 is OpenAI’s most capable agentic AI model yet</t>
+        </is>
+      </c>
+      <c r="F2621" t="inlineStr">
+        <is>
+          <t>https://www.artificialintelligence-news.com/news/gpt-5-5-is-openais-most-capable-agentic-ai-model-yet-at-twice-the-api-price/</t>
+        </is>
+      </c>
+      <c r="G2621" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 09:08:13 +0000</t>
+        </is>
+      </c>
+      <c r="H2621" t="inlineStr">
+        <is>
+          <t>OpenAI launched GPT-5.5 on April 23 as what it calls &amp;#8220;a new class of intelligence for real work and powering agents,&amp;#8221; and the framing is d...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2622">
+      <c r="A2622" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2622" t="inlineStr">
+        <is>
+          <t>ai_ml</t>
+        </is>
+      </c>
+      <c r="C2622" t="inlineStr">
+        <is>
+          <t>AI·ML</t>
+        </is>
+      </c>
+      <c r="D2622" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2622" t="inlineStr">
+        <is>
+          <t>IBM launches AI platform Bob to regulate SDLC costs</t>
+        </is>
+      </c>
+      <c r="F2622" t="inlineStr">
+        <is>
+          <t>https://www.artificialintelligence-news.com/news/ibm-launches-ai-platform-bob-to-regulate-sdlc-costs/</t>
+        </is>
+      </c>
+      <c r="G2622" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 17:34:21 +0000</t>
+        </is>
+      </c>
+      <c r="H2622" t="inlineStr">
+        <is>
+          <t>To regulate software delivery costs and SDLC governance, IBM is launching Bob, an AI platform built to anchor enterprise engineering. Accumulated tech...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2623">
+      <c r="A2623" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2623" t="inlineStr">
+        <is>
+          <t>ai_ml</t>
+        </is>
+      </c>
+      <c r="C2623" t="inlineStr">
+        <is>
+          <t>AI·ML</t>
+        </is>
+      </c>
+      <c r="D2623" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2623" t="inlineStr">
+        <is>
+          <t>The evolution of encoders: From simple models to multimodal AI</t>
+        </is>
+      </c>
+      <c r="F2623" t="inlineStr">
+        <is>
+          <t>https://www.artificialintelligence-news.com/news/the-evolution-of-encoders-from-simple-models-to-multimodal-ai/</t>
+        </is>
+      </c>
+      <c r="G2623" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 13:01:51 +0000</t>
+        </is>
+      </c>
+      <c r="H2623" t="inlineStr">
+        <is>
+          <t>When people talk about artificial intelligence, they usually focus on what it produces: Human-like text, stunning images, or eerily accurate recommend...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2624">
+      <c r="A2624" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2624" t="inlineStr">
+        <is>
+          <t>ai_ml</t>
+        </is>
+      </c>
+      <c r="C2624" t="inlineStr">
+        <is>
+          <t>AI·ML</t>
+        </is>
+      </c>
+      <c r="D2624" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2624" t="inlineStr">
+        <is>
+          <t>Kakao Mobility details Level 4 autonomous driving roadmap for physical AI</t>
+        </is>
+      </c>
+      <c r="F2624" t="inlineStr">
+        <is>
+          <t>https://www.artificialintelligence-news.com/news/kakao-mobility-level-4-autonomous-driving-roadmap/</t>
+        </is>
+      </c>
+      <c r="G2624" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 10:00:00 +0000</t>
+        </is>
+      </c>
+      <c r="H2624" t="inlineStr">
+        <is>
+          <t>Kakao Mobility has set out plans to develop Level 4 autonomous driving technologies in-house as part of its physical AI strategy. Kim Jin-kyu, vice pr...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2625">
+      <c r="A2625" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2625" t="inlineStr">
+        <is>
+          <t>ai_ml</t>
+        </is>
+      </c>
+      <c r="C2625" t="inlineStr">
+        <is>
+          <t>AI·ML</t>
+        </is>
+      </c>
+      <c r="D2625" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2625" t="inlineStr">
+        <is>
+          <t>Lightelligence’s 400% debut is a bet that AI’s next bottleneck is the optical interconnect</t>
+        </is>
+      </c>
+      <c r="F2625" t="inlineStr">
+        <is>
+          <t>https://www.artificialintelligence-news.com/news/lightelligence-ipo-optical-interconnect-ai-infrastructure/</t>
+        </is>
+      </c>
+      <c r="G2625" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 10:00:00 +0000</t>
+        </is>
+      </c>
+      <c r="H2625" t="inlineStr">
+        <is>
+          <t>When a company with US$15.5 million in annual revenue debuts on a stock exchange and its market capitalisation briefly hits US$10 billion, the obvious...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2626">
+      <c r="A2626" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2626" t="inlineStr">
+        <is>
+          <t>ai_ml</t>
+        </is>
+      </c>
+      <c r="C2626" t="inlineStr">
+        <is>
+          <t>AI·ML</t>
+        </is>
+      </c>
+      <c r="D2626" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2626" t="inlineStr">
+        <is>
+          <t>Google warns malicious web pages are poisoning AI agents</t>
+        </is>
+      </c>
+      <c r="F2626" t="inlineStr">
+        <is>
+          <t>https://www.artificialintelligence-news.com/news/google-warns-malicious-web-pages-poisoning-ai-agents/</t>
+        </is>
+      </c>
+      <c r="G2626" t="inlineStr">
+        <is>
+          <t>Mon, 27 Apr 2026 11:12:52 +0000</t>
+        </is>
+      </c>
+      <c r="H2626" t="inlineStr">
+        <is>
+          <t>Public web pages are actively hijacking enterprise AI agents via indirect prompt injections, Google researchers warn. Security teams scanning the Comm...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2627">
+      <c r="A2627" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2627" t="inlineStr">
+        <is>
+          <t>ai_ml</t>
+        </is>
+      </c>
+      <c r="C2627" t="inlineStr">
+        <is>
+          <t>AI·ML</t>
+        </is>
+      </c>
+      <c r="D2627" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2627" t="inlineStr">
+        <is>
+          <t>Why AI agents need interaction infrastructure</t>
+        </is>
+      </c>
+      <c r="F2627" t="inlineStr">
+        <is>
+          <t>https://www.artificialintelligence-news.com/news/why-ai-agents-need-interaction-infrastructure/</t>
+        </is>
+      </c>
+      <c r="G2627" t="inlineStr">
+        <is>
+          <t>Fri, 24 Apr 2026 16:24:17 +0000</t>
+        </is>
+      </c>
+      <c r="H2627" t="inlineStr">
+        <is>
+          <t>To stop automation waste, enterprises must deploy interaction infrastructure that physically governs how independent AI agents operate. AI agents now ...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2628">
+      <c r="A2628" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2628" t="inlineStr">
+        <is>
+          <t>ai_ml</t>
+        </is>
+      </c>
+      <c r="C2628" t="inlineStr">
+        <is>
+          <t>AI·ML</t>
+        </is>
+      </c>
+      <c r="D2628" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2628" t="inlineStr">
+        <is>
+          <t>How Elon Musk Squeezed OpenAI: They 'Are Gonna Want to Kill Me’</t>
+        </is>
+      </c>
+      <c r="F2628" t="inlineStr">
+        <is>
+          <t>https://www.wired.com/story/model-behavior-elon-musk-cross-examined-sam-altman/</t>
+        </is>
+      </c>
+      <c r="G2628" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 23:41:51 +0000</t>
+        </is>
+      </c>
+      <c r="H2628" t="inlineStr">
+        <is>
+          <t>Tensions flared on the third day of trial in Musk v. Altman as OpenAI’s lawyers cross-examined Musk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2629">
+      <c r="A2629" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2629" t="inlineStr">
+        <is>
+          <t>ai_ml</t>
+        </is>
+      </c>
+      <c r="C2629" t="inlineStr">
+        <is>
+          <t>AI·ML</t>
+        </is>
+      </c>
+      <c r="D2629" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2629" t="inlineStr">
+        <is>
+          <t>Emergency First Responders Say Waymos Are Getting Worse</t>
+        </is>
+      </c>
+      <c r="F2629" t="inlineStr">
+        <is>
+          <t>https://www.wired.com/story/emergency-first-responders-say-waymos-are-getting-worse/</t>
+        </is>
+      </c>
+      <c r="G2629" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 20:45:37 +0000</t>
+        </is>
+      </c>
+      <c r="H2629" t="inlineStr">
+        <is>
+          <t>“I believe the technology was deployed too quickly in too vast amounts, with hundreds of vehicles, when it wasn’t really ready,” one police official t...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2630">
+      <c r="A2630" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2630" t="inlineStr">
+        <is>
+          <t>ai_ml</t>
+        </is>
+      </c>
+      <c r="C2630" t="inlineStr">
+        <is>
+          <t>AI·ML</t>
+        </is>
+      </c>
+      <c r="D2630" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2630" t="inlineStr">
+        <is>
+          <t>Taylor Swift Wants to Trademark Her Likeness. These TikTok Deepfake Ads Show Why</t>
+        </is>
+      </c>
+      <c r="F2630" t="inlineStr">
+        <is>
+          <t>https://www.wired.com/story/taylor-swift-rihanna-tiktok-deepfake-ads/</t>
+        </is>
+      </c>
+      <c r="G2630" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 20:36:53 +0000</t>
+        </is>
+      </c>
+      <c r="H2630" t="inlineStr">
+        <is>
+          <t>Researchers show scammers are using AI-manipulated footage of celebrity interviews to trick users into sharing their personal data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2631">
+      <c r="A2631" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2631" t="inlineStr">
+        <is>
+          <t>ai_ml</t>
+        </is>
+      </c>
+      <c r="C2631" t="inlineStr">
+        <is>
+          <t>AI·ML</t>
+        </is>
+      </c>
+      <c r="D2631" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2631" t="inlineStr">
+        <is>
+          <t>Sanctioned Chinese AI Firm SenseTime Releases Image Model Built for Speed</t>
+        </is>
+      </c>
+      <c r="F2631" t="inlineStr">
+        <is>
+          <t>https://www.wired.com/story/chinese-ai-giant-sensetime-is-running-its-new-model-on-chinese-chips/</t>
+        </is>
+      </c>
+      <c r="G2631" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 17:23:52 +0000</t>
+        </is>
+      </c>
+      <c r="H2631" t="inlineStr">
+        <is>
+          <t>With US restrictions limiting its access to advanced tech, SenseTime is doubling down on open source with a new model optimized to run on Chinese-made...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2632">
+      <c r="A2632" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2632" t="inlineStr">
+        <is>
+          <t>ai_ml</t>
+        </is>
+      </c>
+      <c r="C2632" t="inlineStr">
+        <is>
+          <t>AI·ML</t>
+        </is>
+      </c>
+      <c r="D2632" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2632" t="inlineStr">
+        <is>
+          <t>High-Quality Data is Worth a Thousand LLMs in Resolving Ambiguities About UFOs - Avi Loeb – Medium</t>
+        </is>
+      </c>
+      <c r="F2632" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOODM3ZHlDd28zaVMtclFkYm1nUXhfV1k5NHphMlF2UWQwVjVIQkgxeWtNdlNUby1hTW1ManRRXzFSTmg0RTZSVUthWHhYRy1XV3Rlc05aNWNUWTZBeWt1OC1uZGlnNDVSSVFoUGFrbEJHZURJWFBnY0FadWcyU2c5TFZVSU9sNXlkdVA5SzVxbG1iTFE2MnFncXI4MG5KQnFKam9Kb3ZpRVA2V2UxMlpGdm1hWmJuV1NWRGpj?oc=5</t>
+        </is>
+      </c>
+      <c r="G2632" t="inlineStr">
+        <is>
+          <t>Mon, 27 Apr 2026 09:33:28 GMT</t>
+        </is>
+      </c>
+      <c r="H2632" t="inlineStr">
+        <is>
+          <t>High-Quality Data is Worth a Thousand LLMs in Resolving Ambiguities About UFOs&amp;nbsp;&amp;nbsp;Avi Loeb – Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="2633">
+      <c r="A2633" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2633" t="inlineStr">
+        <is>
+          <t>ai_ml</t>
+        </is>
+      </c>
+      <c r="C2633" t="inlineStr">
+        <is>
+          <t>AI·ML</t>
+        </is>
+      </c>
+      <c r="D2633" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2633" t="inlineStr">
+        <is>
+          <t>An AI hater’s guide to keeping LLMs as far from your workflow as possible in 2026 - GeekWire</t>
+        </is>
+      </c>
+      <c r="F2633" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPaVpWMmJTUVhQME1JOXlkNER1dmZEbjNEd2pJTmVvZHVWbmhNT0gxQl80QmVqZXdEU0pEeXZHTkxPQWt4bVMxa2RKaXNtR0NnZ1BLYVBVOUtuYmRyd0RtMjh4ZVVOSXNPc1p2OE1Yc1F2WDVRR0VaNmZvR3dvMzJhT29yTTBNQUFHcGwwTVpXRmc4cFI5Wm5EODFrTkdkdXlLWWd4SURZWWMxTHhmNkNDUg?oc=5</t>
+        </is>
+      </c>
+      <c r="G2633" t="inlineStr">
+        <is>
+          <t>Sun, 26 Apr 2026 13:36:51 GMT</t>
+        </is>
+      </c>
+      <c r="H2633" t="inlineStr">
+        <is>
+          <t>An AI hater’s guide to keeping LLMs as far from your workflow as possible in 2026&amp;nbsp;&amp;nbsp;GeekWire</t>
+        </is>
+      </c>
+    </row>
+    <row r="2634">
+      <c r="A2634" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2634" t="inlineStr">
+        <is>
+          <t>ai_ml</t>
+        </is>
+      </c>
+      <c r="C2634" t="inlineStr">
+        <is>
+          <t>AI·ML</t>
+        </is>
+      </c>
+      <c r="D2634" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2634" t="inlineStr">
+        <is>
+          <t>Introducing the IBM Granite 4.1 family of models - IBM Research</t>
+        </is>
+      </c>
+      <c r="F2634" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE4yRlAxQk5KX0s5eDRjci00ZU9CZXMyZ1k3UDRHeWdVQzhOOFQ5TzQxYWVGeGpLOFBuVHV5akg1MjZ4bDlIZXFzcjl1ejhROXZzdDlxYUxXLUE4cHdvbko1M01Ea0ZNLWV3MzN5ekFiSQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G2634" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 15:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H2634" t="inlineStr">
+        <is>
+          <t>Introducing the IBM Granite 4.1 family of models&amp;nbsp;&amp;nbsp;IBM Research</t>
+        </is>
+      </c>
+    </row>
+    <row r="2635">
+      <c r="A2635" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2635" t="inlineStr">
+        <is>
+          <t>ai_ml</t>
+        </is>
+      </c>
+      <c r="C2635" t="inlineStr">
+        <is>
+          <t>AI·ML</t>
+        </is>
+      </c>
+      <c r="D2635" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2635" t="inlineStr">
+        <is>
+          <t>Talkie Is a ‘Vintage LLM’ Trained on Pre-1930 Data to Help Facilitate ‘Time Travel’ - Gizmodo</t>
+        </is>
+      </c>
+      <c r="F2635" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPbldpRnlNTlV0ZkdTcUJZbEdfWkJVSGRLYnZLdkhXR0d5X1poZFBzX1c1ZkhYaWZpekxSZlBIb285TVBMaTNrMXJYaTU4VF84ZUpQeVE5SlZpdGpqR1NyZG9KVlRIdFplXzd1S0RaZmx1NTdjS3JXdXR5b08ySkVNZFc5QkxqS1d0aG1ibWRLU21BVlhxREJJTWtGNTFtR2FmYy13S2Mtc2d3eWw2R2k4?oc=5</t>
+        </is>
+      </c>
+      <c r="G2635" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 18:35:23 GMT</t>
+        </is>
+      </c>
+      <c r="H2635" t="inlineStr">
+        <is>
+          <t>Talkie Is a ‘Vintage LLM’ Trained on Pre-1930 Data to Help Facilitate ‘Time Travel’&amp;nbsp;&amp;nbsp;Gizmodo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2636">
+      <c r="A2636" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2636" t="inlineStr">
+        <is>
+          <t>ai_ml</t>
+        </is>
+      </c>
+      <c r="C2636" t="inlineStr">
+        <is>
+          <t>AI·ML</t>
+        </is>
+      </c>
+      <c r="D2636" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2636" t="inlineStr">
+        <is>
+          <t>DOE is Advancing the AI Innovation Ecosystem - Department of Energy (.gov)</t>
+        </is>
+      </c>
+      <c r="F2636" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE85c3M4aEpKX1doZDY5T1FaOF9IUDlaMlZrZTk0d1lJTHFLU3ZiQmVHcEEzTjlqeEFmV29kZEhpUEk2NDZwZndVdDdzMHNyRUxiUUtNdTYxTU9KUVRNa21nSjVPR2ZNalRfM2xtVW1yTjFnUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G2636" t="inlineStr">
+        <is>
+          <t>Thu, 23 Apr 2026 13:51:53 GMT</t>
+        </is>
+      </c>
+      <c r="H2636" t="inlineStr">
+        <is>
+          <t>DOE is Advancing the AI Innovation Ecosystem&amp;nbsp;&amp;nbsp;Department of Energy (.gov)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2637">
+      <c r="A2637" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2637" t="inlineStr">
+        <is>
+          <t>ai_ml</t>
+        </is>
+      </c>
+      <c r="C2637" t="inlineStr">
+        <is>
+          <t>AI·ML</t>
+        </is>
+      </c>
+      <c r="D2637" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2637" t="inlineStr">
+        <is>
+          <t>Why Model Collapse In LLMs Is Inevitable With Self-Learning - Hackaday</t>
+        </is>
+      </c>
+      <c r="F2637" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOTVVJUWkwTVlqOURqeGxacHdjQkZ5aFMySmpyUlJfVEY5NEJKeGxuUTlCTk1CbDBrQ0lEZXNMejM0TnF4T2hDUlZZbU96UmFBZWR1ZnRVWlNMOEI4eWtvTnk5ajl1MEcxXzBraUhoU1lzN1EzSmVrT3dKS2NkOGRERkVzbWJpeTk0UzlzS1JyaTJ2V19YM21r?oc=5</t>
+        </is>
+      </c>
+      <c r="G2637" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 02:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H2637" t="inlineStr">
+        <is>
+          <t>Why Model Collapse In LLMs Is Inevitable With Self-Learning&amp;nbsp;&amp;nbsp;Hackaday</t>
+        </is>
+      </c>
+    </row>
+    <row r="2638">
+      <c r="A2638" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2638" t="inlineStr">
+        <is>
+          <t>ai_ml</t>
+        </is>
+      </c>
+      <c r="C2638" t="inlineStr">
+        <is>
+          <t>AI·ML</t>
+        </is>
+      </c>
+      <c r="D2638" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2638" t="inlineStr">
+        <is>
+          <t>OpenObserve Introduces AI-Native Observability Platform with Autonomous AI SRE Agent to Unify Infrastructure, Application and LLM Monitoring - Business Wire</t>
+        </is>
+      </c>
+      <c r="F2638" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogJBVV95cUxPeXlWdUgwNmJDVElIczh4V0hDS3ZmcHBxcFQ5cE5hV0ZmYjhvN21hUVpVOURJd1I4NGFEc1A1UTNYanZPS29Cc2dDX3lEdkp2b01YTldLZmFtbk5MR0ZYVzhjN240UWZYTVpQOGVmb2NXcU9ud3dIMUM2ZlF6bkpHeWU0QVJjVWowbGZScDhaTzI5ekZXaXIxLThOZ2lmemUxazdXS3FqeDBlYTJVMEs0QWg5a2ExWEtJTGVzM1N6cVB4N2FIdm5SV24xcmxtdmNwNndpQXJoenRfZV9hbjZONXRWQkpFTVc1ZkQyTlNVTU1Bdld3YlpjcWVFaTlDT3ZST3FyS25MSlBGWnh6RE1ISzdoZmV5MGFfQXFVUnZKVmJodw?oc=5</t>
+        </is>
+      </c>
+      <c r="G2638" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 13:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H2638" t="inlineStr">
+        <is>
+          <t>OpenObserve Introduces AI-Native Observability Platform with Autonomous AI SRE Agent to Unify Infrastructure, Application and LLM Monitoring&amp;nbsp;&amp;nbs...</t>
+        </is>
+      </c>
+    </row>
+    <row r="2639">
+      <c r="A2639" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B2639" t="inlineStr">
+        <is>
+          <t>ai_ml</t>
+        </is>
+      </c>
+      <c r="C2639" t="inlineStr">
+        <is>
+          <t>AI·ML</t>
+        </is>
+      </c>
+      <c r="D2639" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2639" t="inlineStr">
+        <is>
+          <t>CIS extends security controls to AI agents and MCP access - TechInformed</t>
+        </is>
+      </c>
+      <c r="F2639" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQc2dGVG0yZmNsUVJxN0d4NmRwXy1fWkZlX29Zelg3cVJ1X3RPNWZILTlSZ0pieFBlb2V1V21JcEZGRkFKU0c2T1BHTHphdU5QaXYwamRUM2EzNk9UMUZYazhnN2tWRlZBVmNweFhCWjktVkM4WGNidk1ZNnJEeThKRDlXdkRiNGVOMklZ?oc=5</t>
+        </is>
+      </c>
+      <c r="G2639" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 12:09:26 GMT</t>
+        </is>
+      </c>
+      <c r="H2639" t="inlineStr">
+        <is>
+          <t>CIS extends security controls to AI agents and MCP access&amp;nbsp;&amp;nbsp;TechInformed</t>
         </is>
       </c>
     </row>
